--- a/$PAR.xlsx
+++ b/$PAR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffe\Documents\GitHub\martinshkreli-models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C30F20-C8EE-434A-9D03-DD1EEF6B9B45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F0918FB-7973-4354-B380-B9D143ABF9B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17295" yWindow="90" windowWidth="23130" windowHeight="20805" activeTab="1" xr2:uid="{8F193AD5-4822-438A-B757-2B234AE27955}"/>
+    <workbookView xWindow="-15" yWindow="90" windowWidth="14370" windowHeight="20805" activeTab="1" xr2:uid="{8F193AD5-4822-438A-B757-2B234AE27955}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="2" r:id="rId1"/>
@@ -234,7 +234,7 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -344,11 +344,11 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
@@ -361,10 +361,10 @@
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
@@ -385,10 +385,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1152,31 +1148,31 @@
       </c>
       <c r="J9" s="27"/>
       <c r="K9" s="27">
-        <f>K14/K12</f>
+        <f t="shared" ref="K9:Q9" si="2">K14/K12</f>
         <v>0.24821078114533499</v>
       </c>
       <c r="L9" s="27">
-        <f>L14/L12</f>
+        <f t="shared" si="2"/>
         <v>0.23077171839123842</v>
       </c>
       <c r="M9" s="27">
-        <f>M14/M12</f>
+        <f t="shared" si="2"/>
         <v>0.26780337941628274</v>
       </c>
       <c r="N9" s="27">
-        <f>N14/N12</f>
+        <f t="shared" si="2"/>
         <v>0.23092087577287265</v>
       </c>
       <c r="O9" s="27">
-        <f>O14/O12</f>
+        <f t="shared" si="2"/>
         <v>0.20418921069382562</v>
       </c>
       <c r="P9" s="27">
-        <f>P14/P12</f>
+        <f t="shared" si="2"/>
         <v>0.2630910821961282</v>
       </c>
       <c r="Q9" s="27">
-        <f>Q14/Q12</f>
+        <f t="shared" si="2"/>
         <v>0.2451164258922271</v>
       </c>
       <c r="Z9" s="25"/>
@@ -1212,31 +1208,31 @@
       </c>
       <c r="J10" s="22"/>
       <c r="K10" s="27">
-        <f>K8+K9</f>
+        <f t="shared" ref="K10:Q10" si="3">K8+K9</f>
         <v>0.33583117109130622</v>
       </c>
       <c r="L10" s="27">
-        <f>L8+L9</f>
+        <f t="shared" si="3"/>
         <v>0.31802873782968349</v>
       </c>
       <c r="M10" s="27">
-        <f>M8+M9</f>
+        <f t="shared" si="3"/>
         <v>0.37658367341707732</v>
       </c>
       <c r="N10" s="27">
-        <f>N8+N9</f>
+        <f t="shared" si="3"/>
         <v>0.23296330088395187</v>
       </c>
       <c r="O10" s="27">
-        <f>O8+O9</f>
+        <f t="shared" si="3"/>
         <v>0.29026108625255975</v>
       </c>
       <c r="P10" s="27">
-        <f>P8+P9</f>
+        <f t="shared" si="3"/>
         <v>0.29571981919072848</v>
       </c>
       <c r="Q10" s="27">
-        <f>Q8+Q9</f>
+        <f t="shared" si="3"/>
         <v>0.29402756321965107</v>
       </c>
       <c r="Z10" s="25"/>
@@ -1324,35 +1320,35 @@
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="24">
-        <f>SUM(J3:J6)</f>
+        <f t="shared" ref="J12:Q12" si="4">SUM(J3:J6)</f>
         <v>80.284999999999997</v>
       </c>
       <c r="K12" s="24">
-        <f>SUM(K3:K6)</f>
+        <f t="shared" si="4"/>
         <v>85.092999999999989</v>
       </c>
       <c r="L12" s="24">
-        <f>SUM(L3:L6)</f>
+        <f t="shared" si="4"/>
         <v>92.76700000000001</v>
       </c>
       <c r="M12" s="24">
-        <f>SUM(M3:M6)</f>
+        <f t="shared" si="4"/>
         <v>97.65</v>
       </c>
       <c r="N12" s="24">
-        <f>SUM(N3:N6)</f>
+        <f t="shared" si="4"/>
         <v>100.43700000000001</v>
       </c>
       <c r="O12" s="24">
-        <f>SUM(O3:O6)</f>
+        <f t="shared" si="4"/>
         <v>100.544</v>
       </c>
       <c r="P12" s="24">
-        <f>SUM(P3:P6)</f>
+        <f t="shared" si="4"/>
         <v>107.13399999999999</v>
       </c>
       <c r="Q12" s="24">
-        <f>SUM(Q3:Q6)</f>
+        <f t="shared" si="4"/>
         <v>107.708</v>
       </c>
       <c r="Y12" s="4">
@@ -1370,328 +1366,328 @@
         <v>415.82299999999998</v>
       </c>
       <c r="AC12" s="4">
-        <f>AB12*(1+$X$30)</f>
-        <v>498.98759999999993</v>
+        <f t="shared" ref="AC12:AI12" si="5">AB12*(1+$X$30)</f>
+        <v>478.19644999999991</v>
       </c>
       <c r="AD12" s="4">
-        <f>AC12*(1+$X$30)</f>
-        <v>598.78511999999989</v>
+        <f t="shared" si="5"/>
+        <v>549.92591749999985</v>
       </c>
       <c r="AE12" s="4">
-        <f>AD12*(1+$X$30)</f>
-        <v>718.54214399999989</v>
+        <f t="shared" si="5"/>
+        <v>632.41480512499982</v>
       </c>
       <c r="AF12" s="4">
-        <f>AE12*(1+$X$30)</f>
-        <v>862.25057279999987</v>
+        <f t="shared" si="5"/>
+        <v>727.27702589374974</v>
       </c>
       <c r="AG12" s="4">
-        <f>AF12*(1+$X$30)</f>
-        <v>1034.7006873599998</v>
+        <f t="shared" si="5"/>
+        <v>836.3685797778121</v>
       </c>
       <c r="AH12" s="4">
-        <f>AG12*(1+$X$30)</f>
-        <v>1241.6408248319997</v>
+        <f t="shared" si="5"/>
+        <v>961.82386674448389</v>
       </c>
       <c r="AI12" s="4">
-        <f>AH12*(1+$X$30)</f>
-        <v>1489.9689897983997</v>
+        <f t="shared" si="5"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="AJ12" s="4">
         <f>AI12*(1+$X$31)</f>
-        <v>1475.0692999004157</v>
+        <v>1106.0974467561564</v>
       </c>
       <c r="AK12" s="4">
-        <f t="shared" ref="AK12:CV12" si="2">AJ12*(1+$X$31)</f>
-        <v>1460.3186069014116</v>
+        <f t="shared" ref="AK12:CV12" si="6">AJ12*(1+$X$31)</f>
+        <v>1106.0974467561564</v>
       </c>
       <c r="AL12" s="4">
-        <f t="shared" si="2"/>
-        <v>1445.7154208323975</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="AM12" s="4">
-        <f t="shared" si="2"/>
-        <v>1431.2582666240735</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="AN12" s="4">
-        <f t="shared" si="2"/>
-        <v>1416.9456839578327</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="AO12" s="4">
-        <f t="shared" si="2"/>
-        <v>1402.7762271182544</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="AP12" s="4">
-        <f t="shared" si="2"/>
-        <v>1388.7484648470718</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="AQ12" s="4">
-        <f t="shared" si="2"/>
-        <v>1374.8609801986011</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="AR12" s="4">
-        <f t="shared" si="2"/>
-        <v>1361.112370396615</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="AS12" s="4">
-        <f t="shared" si="2"/>
-        <v>1347.5012466926489</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="AT12" s="4">
-        <f t="shared" si="2"/>
-        <v>1334.0262342257224</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="AU12" s="4">
-        <f t="shared" si="2"/>
-        <v>1320.6859718834651</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="AV12" s="4">
-        <f t="shared" si="2"/>
-        <v>1307.4791121646304</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="AW12" s="4">
-        <f t="shared" si="2"/>
-        <v>1294.4043210429841</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="AX12" s="4">
-        <f t="shared" si="2"/>
-        <v>1281.4602778325543</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="AY12" s="4">
-        <f t="shared" si="2"/>
-        <v>1268.6456750542288</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="AZ12" s="4">
-        <f t="shared" si="2"/>
-        <v>1255.9592183036866</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="BA12" s="4">
-        <f t="shared" si="2"/>
-        <v>1243.3996261206498</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="BB12" s="4">
-        <f t="shared" si="2"/>
-        <v>1230.9656298594434</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="BC12" s="4">
-        <f t="shared" si="2"/>
-        <v>1218.6559735608489</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="BD12" s="4">
-        <f t="shared" si="2"/>
-        <v>1206.4694138252405</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="BE12" s="4">
-        <f t="shared" si="2"/>
-        <v>1194.4047196869881</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="BF12" s="4">
-        <f t="shared" si="2"/>
-        <v>1182.4606724901182</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="BG12" s="4">
-        <f t="shared" si="2"/>
-        <v>1170.6360657652169</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="BH12" s="4">
-        <f t="shared" si="2"/>
-        <v>1158.9297051075648</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="BI12" s="4">
-        <f t="shared" si="2"/>
-        <v>1147.3404080564892</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="BJ12" s="4">
-        <f t="shared" si="2"/>
-        <v>1135.8670039759243</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="BK12" s="4">
-        <f t="shared" si="2"/>
-        <v>1124.5083339361649</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="BL12" s="4">
-        <f t="shared" si="2"/>
-        <v>1113.2632505968033</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="BM12" s="4">
-        <f t="shared" si="2"/>
-        <v>1102.1306180908352</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="BN12" s="4">
-        <f t="shared" si="2"/>
-        <v>1091.1093119099269</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="BO12" s="4">
-        <f t="shared" si="2"/>
-        <v>1080.1982187908277</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="BP12" s="4">
-        <f t="shared" si="2"/>
-        <v>1069.3962366029193</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="BQ12" s="4">
-        <f t="shared" si="2"/>
-        <v>1058.7022742368902</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="BR12" s="4">
-        <f t="shared" si="2"/>
-        <v>1048.1152514945213</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="BS12" s="4">
-        <f t="shared" si="2"/>
-        <v>1037.634098979576</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="BT12" s="4">
-        <f t="shared" si="2"/>
-        <v>1027.2577579897802</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="BU12" s="4">
-        <f t="shared" si="2"/>
-        <v>1016.9851804098824</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="BV12" s="4">
-        <f t="shared" si="2"/>
-        <v>1006.8153286057836</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="BW12" s="4">
-        <f t="shared" si="2"/>
-        <v>996.74717531972578</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="BX12" s="4">
-        <f t="shared" si="2"/>
-        <v>986.7797035665285</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="BY12" s="4">
-        <f t="shared" si="2"/>
-        <v>976.91190653086323</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="BZ12" s="4">
-        <f t="shared" si="2"/>
-        <v>967.14278746555465</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="CA12" s="4">
-        <f t="shared" si="2"/>
-        <v>957.47135959089906</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="CB12" s="4">
-        <f t="shared" si="2"/>
-        <v>947.89664599499008</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="CC12" s="4">
-        <f t="shared" si="2"/>
-        <v>938.41767953504018</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="CD12" s="4">
-        <f t="shared" si="2"/>
-        <v>929.03350273968977</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="CE12" s="4">
-        <f t="shared" si="2"/>
-        <v>919.74316771229292</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="CF12" s="4">
-        <f t="shared" si="2"/>
-        <v>910.54573603516997</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="CG12" s="4">
-        <f t="shared" si="2"/>
-        <v>901.44027867481827</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="CH12" s="4">
-        <f t="shared" si="2"/>
-        <v>892.4258758880701</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="CI12" s="4">
-        <f t="shared" si="2"/>
-        <v>883.50161712918941</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="CJ12" s="4">
-        <f t="shared" si="2"/>
-        <v>874.66660095789746</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="CK12" s="4">
-        <f t="shared" si="2"/>
-        <v>865.91993494831843</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="CL12" s="4">
-        <f t="shared" si="2"/>
-        <v>857.26073559883525</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="CM12" s="4">
-        <f t="shared" si="2"/>
-        <v>848.68812824284691</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="CN12" s="4">
-        <f t="shared" si="2"/>
-        <v>840.20124696041842</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="CO12" s="4">
-        <f t="shared" si="2"/>
-        <v>831.79923449081423</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="CP12" s="4">
-        <f t="shared" si="2"/>
-        <v>823.48124214590609</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="CQ12" s="4">
-        <f t="shared" si="2"/>
-        <v>815.24642972444701</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="CR12" s="4">
-        <f t="shared" si="2"/>
-        <v>807.09396542720253</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="CS12" s="4">
-        <f t="shared" si="2"/>
-        <v>799.02302577293051</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="CT12" s="4">
-        <f t="shared" si="2"/>
-        <v>791.0327955152012</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="CU12" s="4">
-        <f t="shared" si="2"/>
-        <v>783.12246756004913</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="CV12" s="4">
-        <f t="shared" si="2"/>
-        <v>775.29124288444859</v>
+        <f t="shared" si="6"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="CW12" s="4">
-        <f t="shared" ref="CW12:DE12" si="3">CV12*(1+$X$31)</f>
-        <v>767.53833045560407</v>
+        <f t="shared" ref="CW12:DE12" si="7">CV12*(1+$X$31)</f>
+        <v>1106.0974467561564</v>
       </c>
       <c r="CX12" s="4">
-        <f t="shared" si="3"/>
-        <v>759.86294715104805</v>
+        <f t="shared" si="7"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="CY12" s="4">
-        <f t="shared" si="3"/>
-        <v>752.26431767953761</v>
+        <f t="shared" si="7"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="CZ12" s="4">
-        <f t="shared" si="3"/>
-        <v>744.74167450274228</v>
+        <f t="shared" si="7"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="DA12" s="4">
-        <f t="shared" si="3"/>
-        <v>737.29425775771483</v>
+        <f t="shared" si="7"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="DB12" s="4">
-        <f t="shared" si="3"/>
-        <v>729.92131518013764</v>
+        <f t="shared" si="7"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="DC12" s="4">
-        <f t="shared" si="3"/>
-        <v>722.62210202833626</v>
+        <f t="shared" si="7"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="DD12" s="4">
-        <f t="shared" si="3"/>
-        <v>715.39588100805292</v>
+        <f t="shared" si="7"/>
+        <v>1106.0974467561564</v>
       </c>
       <c r="DE12" s="4">
-        <f t="shared" si="3"/>
-        <v>708.24192219797237</v>
+        <f t="shared" si="7"/>
+        <v>1106.0974467561564</v>
       </c>
     </row>
     <row r="13" spans="1:109" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -1737,6 +1733,26 @@
       <c r="Q13" s="23">
         <v>81.307000000000002</v>
       </c>
+      <c r="Y13" s="25">
+        <f>(Z12-Y12)/Y12</f>
+        <v>0.32317364093065015</v>
+      </c>
+      <c r="Z13" s="25">
+        <f>(AA12-Z12)/Z12</f>
+        <v>0.25777725929382483</v>
+      </c>
+      <c r="AA13" s="25">
+        <f>(AB12-AA12)/AA12</f>
+        <v>0.1687151309040319</v>
+      </c>
+      <c r="AB13" s="25">
+        <f>(AC12-AB12)/AB12</f>
+        <v>0.14999999999999986</v>
+      </c>
+      <c r="AC13" s="25">
+        <f>(AD12-AC12)/AC12</f>
+        <v>0.14999999999999991</v>
+      </c>
     </row>
     <row r="14" spans="1:109" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
@@ -1751,35 +1767,35 @@
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
       <c r="J14" s="23">
-        <f>J12-J13</f>
+        <f t="shared" ref="J14:Q14" si="8">J12-J13</f>
         <v>20.613</v>
       </c>
       <c r="K14" s="23">
-        <f>K12-K13</f>
+        <f t="shared" si="8"/>
         <v>21.120999999999988</v>
       </c>
       <c r="L14" s="23">
-        <f>L12-L13</f>
+        <f t="shared" si="8"/>
         <v>21.408000000000015</v>
       </c>
       <c r="M14" s="23">
-        <f>M12-M13</f>
+        <f t="shared" si="8"/>
         <v>26.15100000000001</v>
       </c>
       <c r="N14" s="23">
-        <f>N12-N13</f>
+        <f t="shared" si="8"/>
         <v>23.193000000000012</v>
       </c>
       <c r="O14" s="23">
-        <f>O12-O13</f>
+        <f t="shared" si="8"/>
         <v>20.53</v>
       </c>
       <c r="P14" s="23">
-        <f>P12-P13</f>
+        <f t="shared" si="8"/>
         <v>28.185999999999993</v>
       </c>
       <c r="Q14" s="23">
-        <f>Q12-Q13</f>
+        <f t="shared" si="8"/>
         <v>26.400999999999996</v>
       </c>
     </row>
@@ -1962,35 +1978,35 @@
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
       <c r="J19" s="23">
-        <f>SUM(J15:J18)</f>
+        <f t="shared" ref="J19:Q19" si="9">SUM(J15:J18)</f>
         <v>33.208999999999996</v>
       </c>
       <c r="K19" s="23">
-        <f>SUM(K15:K18)</f>
+        <f t="shared" si="9"/>
         <v>37.22</v>
       </c>
       <c r="L19" s="23">
-        <f>SUM(L15:L18)</f>
+        <f t="shared" si="9"/>
         <v>39.385999999999996</v>
       </c>
       <c r="M19" s="23">
-        <f>SUM(M15:M18)</f>
+        <f t="shared" si="9"/>
         <v>36.467000000000006</v>
       </c>
       <c r="N19" s="23">
-        <f>SUM(N15:N18)</f>
+        <f t="shared" si="9"/>
         <v>37.057000000000002</v>
       </c>
       <c r="O19" s="23">
-        <f>SUM(O15:O18)</f>
+        <f t="shared" si="9"/>
         <v>38.183</v>
       </c>
       <c r="P19" s="23">
-        <f>SUM(P15:P18)</f>
+        <f t="shared" si="9"/>
         <v>41.372999999999998</v>
       </c>
       <c r="Q19" s="23">
-        <f>SUM(Q15:Q18)</f>
+        <f t="shared" si="9"/>
         <v>41.405999999999999</v>
       </c>
     </row>
@@ -2007,35 +2023,35 @@
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
       <c r="J20" s="23">
-        <f>J14-J19</f>
+        <f t="shared" ref="J20:Q20" si="10">J14-J19</f>
         <v>-12.595999999999997</v>
       </c>
       <c r="K20" s="23">
-        <f>K14-K19</f>
+        <f t="shared" si="10"/>
         <v>-16.099000000000011</v>
       </c>
       <c r="L20" s="23">
-        <f>L14-L19</f>
+        <f t="shared" si="10"/>
         <v>-17.97799999999998</v>
       </c>
       <c r="M20" s="23">
-        <f>M14-M19</f>
+        <f t="shared" si="10"/>
         <v>-10.315999999999995</v>
       </c>
       <c r="N20" s="23">
-        <f>N14-N19</f>
+        <f t="shared" si="10"/>
         <v>-13.86399999999999</v>
       </c>
       <c r="O20" s="23">
-        <f>O14-O19</f>
+        <f t="shared" si="10"/>
         <v>-17.652999999999999</v>
       </c>
       <c r="P20" s="23">
-        <f>P14-P19</f>
+        <f t="shared" si="10"/>
         <v>-13.187000000000005</v>
       </c>
       <c r="Q20" s="23">
-        <f>Q14-Q19</f>
+        <f t="shared" si="10"/>
         <v>-15.005000000000003</v>
       </c>
     </row>
@@ -2097,35 +2113,35 @@
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
       <c r="J22" s="23">
-        <f>J20+J21</f>
+        <f t="shared" ref="J22:Q22" si="11">J20+J21</f>
         <v>-15.426999999999996</v>
       </c>
       <c r="K22" s="23">
-        <f>K20+K21</f>
+        <f t="shared" si="11"/>
         <v>-18.807000000000009</v>
       </c>
       <c r="L22" s="23">
-        <f>L20+L21</f>
+        <f t="shared" si="11"/>
         <v>-20.296999999999979</v>
       </c>
       <c r="M22" s="23">
-        <f>M20+M21</f>
+        <f t="shared" si="11"/>
         <v>-12.482999999999995</v>
       </c>
       <c r="N22" s="23">
-        <f>N20+N21</f>
+        <f t="shared" si="11"/>
         <v>-15.589999999999989</v>
       </c>
       <c r="O22" s="23">
-        <f>O20+O21</f>
+        <f t="shared" si="11"/>
         <v>-19.387999999999998</v>
       </c>
       <c r="P22" s="23">
-        <f>P20+P21</f>
+        <f t="shared" si="11"/>
         <v>-15.310000000000006</v>
       </c>
       <c r="Q22" s="23">
-        <f>Q20+Q21</f>
+        <f t="shared" si="11"/>
         <v>-16.784000000000002</v>
       </c>
     </row>
@@ -2186,35 +2202,35 @@
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
       <c r="J24" s="23">
-        <f>J22+J23</f>
+        <f t="shared" ref="J24:Q24" si="12">J22+J23</f>
         <v>-15.436999999999996</v>
       </c>
       <c r="K24" s="23">
-        <f>K22+K23</f>
+        <f t="shared" si="12"/>
         <v>-18.84800000000001</v>
       </c>
       <c r="L24" s="23">
-        <f>L22+L23</f>
+        <f t="shared" si="12"/>
         <v>-20.874999999999979</v>
       </c>
       <c r="M24" s="23">
-        <f>M22+M23</f>
+        <f t="shared" si="12"/>
         <v>-13.105999999999995</v>
       </c>
       <c r="N24" s="23">
-        <f>N22+N23</f>
+        <f t="shared" si="12"/>
         <v>-15.904999999999989</v>
       </c>
       <c r="O24" s="23">
-        <f>O22+O23</f>
+        <f t="shared" si="12"/>
         <v>-19.796999999999997</v>
       </c>
       <c r="P24" s="23">
-        <f>P22+P23</f>
+        <f t="shared" si="12"/>
         <v>-15.516000000000005</v>
       </c>
       <c r="Q24" s="23">
-        <f>Q22+Q23</f>
+        <f t="shared" si="12"/>
         <v>-17.842000000000002</v>
       </c>
     </row>
@@ -2231,35 +2247,35 @@
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
       <c r="J25" s="23">
-        <f>J24/J26</f>
+        <f t="shared" ref="J25:Q25" si="13">J24/J26</f>
         <v>-0.57237671486837216</v>
       </c>
       <c r="K25" s="23">
-        <f>K24/K26</f>
+        <f t="shared" si="13"/>
         <v>-0.69853976725224265</v>
       </c>
       <c r="L25" s="23">
-        <f>L24/L26</f>
+        <f t="shared" si="13"/>
         <v>-0.77001106602729541</v>
       </c>
       <c r="M25" s="23">
-        <f>M24/M26</f>
+        <f t="shared" si="13"/>
         <v>-0.48329522826167104</v>
       </c>
       <c r="N25" s="23">
-        <f>N24/N26</f>
+        <f t="shared" si="13"/>
         <v>-0.58166325336454028</v>
       </c>
       <c r="O25" s="23">
-        <f>O24/O26</f>
+        <f t="shared" si="13"/>
         <v>-0.72365390941989249</v>
       </c>
       <c r="P25" s="23">
-        <f>P24/P26</f>
+        <f t="shared" si="13"/>
         <v>-0.56479324403028552</v>
       </c>
       <c r="Q25" s="23">
-        <f>Q24/Q26</f>
+        <f t="shared" si="13"/>
         <v>-0.63794336384439365</v>
       </c>
     </row>
@@ -2338,31 +2354,31 @@
         <v>28</v>
       </c>
       <c r="D29" s="13" t="e">
-        <f t="shared" ref="D29:J29" si="4">+D14/D12</f>
+        <f t="shared" ref="D29:J29" si="14">+D14/D12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E29" s="13" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F29" s="13" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G29" s="13" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H29" s="13" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I29" s="13" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J29" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>0.2567478358348384</v>
       </c>
       <c r="K29" s="13">
@@ -2370,27 +2386,27 @@
         <v>0.24821078114533499</v>
       </c>
       <c r="L29" s="13">
-        <f t="shared" ref="L29:Q29" si="5">+L14/L12</f>
+        <f t="shared" ref="L29:Q29" si="15">+L14/L12</f>
         <v>0.23077171839123842</v>
       </c>
       <c r="M29" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="15"/>
         <v>0.26780337941628274</v>
       </c>
       <c r="N29" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="15"/>
         <v>0.23092087577287265</v>
       </c>
       <c r="O29" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="15"/>
         <v>0.20418921069382562</v>
       </c>
       <c r="P29" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="15"/>
         <v>0.2630910821961282</v>
       </c>
       <c r="Q29" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="15"/>
         <v>0.2451164258922271</v>
       </c>
     </row>
@@ -2399,7 +2415,7 @@
         <v>29</v>
       </c>
       <c r="X30" s="15">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="31" spans="1:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2419,7 +2435,7 @@
         <v>31</v>
       </c>
       <c r="X31" s="17">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2439,7 +2455,7 @@
         <v>32</v>
       </c>
       <c r="X32" s="17">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="33" spans="2:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2460,7 +2476,7 @@
       </c>
       <c r="X33" s="26">
         <f>NPV(X32,Y12:DE12)</f>
-        <v>7506.5856306166661</v>
+        <v>4120.6585220078041</v>
       </c>
     </row>
     <row r="34" spans="2:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2489,8 +2505,7 @@
         <v>26</v>
       </c>
       <c r="X34" s="19">
-        <f>Main!L6</f>
-        <v>28.02</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="35" spans="2:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2511,7 +2526,7 @@
       </c>
       <c r="X35" s="20">
         <f>X33/X34</f>
-        <v>267.9009861033785</v>
+        <v>144.58450954413348</v>
       </c>
     </row>
     <row r="36" spans="2:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2532,7 +2547,7 @@
       </c>
       <c r="X36" s="15">
         <f>(X35-Main!L5)/Main!L5</f>
-        <v>5.1572279040077804</v>
+        <v>2.323017916436072</v>
       </c>
     </row>
     <row r="37" spans="2:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2553,7 +2568,7 @@
       </c>
       <c r="X37" s="18">
         <f>X34*X35</f>
-        <v>7506.5856306166652</v>
+        <v>4120.6585220078041</v>
       </c>
     </row>
     <row r="38" spans="2:24" s="6" customFormat="1" x14ac:dyDescent="0.25">

--- a/$PAR.xlsx
+++ b/$PAR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffe\Documents\GitHub\martinshkreli-models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F0918FB-7973-4354-B380-B9D143ABF9B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68083993-078D-4D11-B934-DBE90321755F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="90" windowWidth="14370" windowHeight="20805" activeTab="1" xr2:uid="{8F193AD5-4822-438A-B757-2B234AE27955}"/>
+    <workbookView xWindow="20685" yWindow="150" windowWidth="26190" windowHeight="20805" activeTab="1" xr2:uid="{8F193AD5-4822-438A-B757-2B234AE27955}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="64">
   <si>
     <t>FY</t>
   </si>
@@ -223,6 +223,12 @@
   </si>
   <si>
     <t>ARR</t>
+  </si>
+  <si>
+    <t>Restaurant Rev</t>
+  </si>
+  <si>
+    <t>Restaurant Rev Y/Y</t>
   </si>
 </sst>
 </file>
@@ -236,7 +242,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -257,6 +263,14 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -303,7 +317,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -367,6 +381,12 @@
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -692,7 +712,7 @@
         <v>41</v>
       </c>
       <c r="L5" s="8">
-        <v>43.51</v>
+        <v>46.49</v>
       </c>
     </row>
     <row r="6" spans="11:12" x14ac:dyDescent="0.25">
@@ -700,7 +720,7 @@
         <v>26</v>
       </c>
       <c r="L6" s="6">
-        <v>28.02</v>
+        <v>29.515999999999998</v>
       </c>
     </row>
     <row r="7" spans="11:12" x14ac:dyDescent="0.25">
@@ -709,7 +729,7 @@
       </c>
       <c r="L7" s="6">
         <f>+L5*L6</f>
-        <v>1219.1501999999998</v>
+        <v>1372.19884</v>
       </c>
     </row>
     <row r="8" spans="11:12" x14ac:dyDescent="0.25">
@@ -734,7 +754,7 @@
       </c>
       <c r="L10" s="6">
         <f>+L7-L8+L9</f>
-        <v>1439.7771999999998</v>
+        <v>1592.82584</v>
       </c>
     </row>
   </sheetData>
@@ -744,10 +764,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE7FAD33-99C5-4121-980B-8556C8EA76DD}">
-  <dimension ref="A1:DE61"/>
+  <dimension ref="A1:DE63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="9.140625" style="1"/>
     <col min="4" max="4" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="1" bestFit="1" customWidth="1"/>
@@ -759,6 +779,8 @@
     <col min="14" max="14" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -929,6 +951,9 @@
       </c>
       <c r="Q3" s="23">
         <v>24.4</v>
+      </c>
+      <c r="R3" s="23">
+        <v>18.225999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:109" x14ac:dyDescent="0.25">
@@ -967,6 +992,9 @@
       <c r="Q4" s="32">
         <v>32.896999999999998</v>
       </c>
+      <c r="R4" s="32">
+        <v>38.378999999999998</v>
+      </c>
       <c r="U4">
         <f>1.15*Q4</f>
         <v>37.831549999999993</v>
@@ -1010,6 +1038,9 @@
       <c r="Q5" s="23">
         <v>12.603</v>
       </c>
+      <c r="R5" s="23">
+        <v>13.468</v>
+      </c>
     </row>
     <row r="6" spans="1:109" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -1038,6 +1069,9 @@
       </c>
       <c r="Q6" s="23">
         <v>37.808</v>
+      </c>
+      <c r="R6" s="23">
+        <v>35.423999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:109" x14ac:dyDescent="0.25">
@@ -1072,6 +1106,10 @@
         <f>(Q4-M4)/M4</f>
         <v>0.17876594524867412</v>
       </c>
+      <c r="R7" s="33">
+        <f>(R4-N4)/N4</f>
+        <v>0.3723940640085821</v>
+      </c>
     </row>
     <row r="8" spans="1:109" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -1083,7 +1121,7 @@
         <v>8.7620389945971267E-2</v>
       </c>
       <c r="L8" s="27">
-        <f t="shared" ref="L8:Q8" si="1">(L4-K4)/K4</f>
+        <f t="shared" ref="L8:R8" si="1">(L4-K4)/K4</f>
         <v>8.7257019438445063E-2</v>
       </c>
       <c r="M8" s="27">
@@ -1106,16 +1144,20 @@
         <f t="shared" si="1"/>
         <v>4.8911137327423998E-2</v>
       </c>
+      <c r="R8" s="27">
+        <f t="shared" si="1"/>
+        <v>0.16664133507614676</v>
+      </c>
       <c r="Z8" s="25">
-        <f>(Z12-Y12)/Y12</f>
+        <f>(Z13-Y13)/Y13</f>
         <v>0.32317364093065015</v>
       </c>
       <c r="AA8" s="25">
-        <f>(AA12-Z12)/Z12</f>
+        <f>(AA13-Z13)/Z13</f>
         <v>0.25777725929382483</v>
       </c>
       <c r="AB8" s="25">
-        <f>(AB12-AA12)/AA12</f>
+        <f>(AB13-AA13)/AA13</f>
         <v>0.1687151309040319</v>
       </c>
       <c r="AC8" s="25"/>
@@ -1148,7 +1190,7 @@
       </c>
       <c r="J9" s="27"/>
       <c r="K9" s="27">
-        <f t="shared" ref="K9:Q9" si="2">K14/K12</f>
+        <f t="shared" ref="K9:R9" si="2">K15/K13</f>
         <v>0.24821078114533499</v>
       </c>
       <c r="L9" s="27">
@@ -1174,6 +1216,10 @@
       <c r="Q9" s="27">
         <f t="shared" si="2"/>
         <v>0.2451164258922271</v>
+      </c>
+      <c r="R9" s="27">
+        <f t="shared" si="2"/>
+        <v>0.27074703546072393</v>
       </c>
       <c r="Z9" s="25"/>
       <c r="AA9" s="25"/>
@@ -1208,7 +1254,7 @@
       </c>
       <c r="J10" s="22"/>
       <c r="K10" s="27">
-        <f t="shared" ref="K10:Q10" si="3">K8+K9</f>
+        <f t="shared" ref="K10:R10" si="3">K8+K9</f>
         <v>0.33583117109130622</v>
       </c>
       <c r="L10" s="27">
@@ -1234,6 +1280,10 @@
       <c r="Q10" s="27">
         <f t="shared" si="3"/>
         <v>0.29402756321965107</v>
+      </c>
+      <c r="R10" s="27">
+        <f t="shared" si="3"/>
+        <v>0.43738837053687069</v>
       </c>
       <c r="Z10" s="25"/>
       <c r="AA10" s="25"/>
@@ -1280,483 +1330,793 @@
       <c r="AB11" s="34">
         <v>136.9</v>
       </c>
-      <c r="AC11" s="34"/>
-      <c r="AD11" s="34"/>
-      <c r="AE11" s="34"/>
-      <c r="AF11" s="34"/>
-      <c r="AG11" s="34"/>
-      <c r="AH11" s="34"/>
-      <c r="AI11" s="34"/>
-      <c r="AJ11" s="34"/>
-      <c r="AK11" s="34"/>
-      <c r="AL11" s="34"/>
-      <c r="AM11" s="34"/>
-      <c r="AN11" s="34"/>
-      <c r="AO11" s="34"/>
-      <c r="AP11" s="34"/>
-      <c r="AQ11" s="34"/>
-      <c r="AR11" s="34"/>
-      <c r="AS11" s="34"/>
-      <c r="AT11" s="34"/>
-      <c r="AU11" s="34"/>
-      <c r="AV11" s="34"/>
-      <c r="AW11" s="34"/>
-      <c r="AX11" s="34"/>
-      <c r="AY11" s="34"/>
-      <c r="AZ11" s="34"/>
-      <c r="BA11" s="34"/>
-      <c r="BB11" s="34"/>
-    </row>
-    <row r="12" spans="1:109" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
+      <c r="AC11" s="25"/>
+      <c r="AD11" s="25"/>
+      <c r="AE11" s="25"/>
+      <c r="AF11" s="25"/>
+      <c r="AG11" s="25"/>
+      <c r="AH11" s="25"/>
+      <c r="AI11" s="25"/>
+      <c r="AJ11" s="25"/>
+      <c r="AK11" s="25"/>
+      <c r="AL11" s="25"/>
+      <c r="AM11" s="25"/>
+      <c r="AN11" s="25"/>
+      <c r="AO11" s="25"/>
+      <c r="AP11" s="25"/>
+      <c r="AQ11" s="25"/>
+      <c r="AR11" s="25"/>
+      <c r="AS11" s="25"/>
+      <c r="AT11" s="25"/>
+      <c r="AU11" s="25"/>
+      <c r="AV11" s="25"/>
+      <c r="AW11" s="25"/>
+      <c r="AX11" s="25"/>
+      <c r="AY11" s="25"/>
+    </row>
+    <row r="12" spans="1:109" x14ac:dyDescent="0.25">
+      <c r="A12" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="J12" s="36">
+        <f>SUM(J3:J5)</f>
+        <v>58.846000000000004</v>
+      </c>
+      <c r="K12" s="36">
+        <f>SUM(K3:K5)</f>
+        <v>64.170999999999992</v>
+      </c>
+      <c r="L12" s="36">
+        <f>SUM(L3:L5)</f>
+        <v>68.353000000000009</v>
+      </c>
+      <c r="M12" s="36">
+        <f>SUM(M3:M5)</f>
+        <v>70.977000000000004</v>
+      </c>
+      <c r="N12" s="36">
+        <f>SUM(N3:N5)</f>
+        <v>68.584000000000003</v>
+      </c>
+      <c r="O12" s="36">
+        <f>SUM(O3:O5)</f>
+        <v>69.528999999999996</v>
+      </c>
+      <c r="P12" s="36">
+        <f>SUM(P3:P5)</f>
+        <v>68.700999999999993</v>
+      </c>
+      <c r="Q12" s="36">
+        <f>SUM(Q3:Q5)</f>
+        <v>69.899999999999991</v>
+      </c>
+      <c r="R12" s="36">
+        <f>SUM(R3:R5)</f>
+        <v>70.072999999999993</v>
+      </c>
+      <c r="AA12" s="38">
+        <f>SUM(J12:M12)</f>
+        <v>262.34699999999998</v>
+      </c>
+      <c r="AB12" s="38">
+        <f>SUM(N12:Q12)</f>
+        <v>276.714</v>
+      </c>
+      <c r="AC12" s="4">
+        <f>AB12*(1+$AA$32)</f>
+        <v>304.3854</v>
+      </c>
+      <c r="AD12" s="4">
+        <f t="shared" ref="AD12:AI12" si="4">AC12*(1+$AA$32)</f>
+        <v>334.82394000000005</v>
+      </c>
+      <c r="AE12" s="4">
+        <f t="shared" si="4"/>
+        <v>368.30633400000011</v>
+      </c>
+      <c r="AF12" s="4">
+        <f t="shared" si="4"/>
+        <v>405.13696740000017</v>
+      </c>
+      <c r="AG12" s="4">
+        <f t="shared" si="4"/>
+        <v>445.65066414000023</v>
+      </c>
+      <c r="AH12" s="4">
+        <f t="shared" si="4"/>
+        <v>490.21573055400029</v>
+      </c>
+      <c r="AI12" s="4">
+        <f t="shared" si="4"/>
+        <v>539.23730360940033</v>
+      </c>
+      <c r="AJ12" s="4">
+        <f>AI12*(1+$AA$33)</f>
+        <v>544.62967664549433</v>
+      </c>
+      <c r="AK12" s="4">
+        <f t="shared" ref="AK12:CV12" si="5">AJ12*(1+$AA$33)</f>
+        <v>550.07597341194924</v>
+      </c>
+      <c r="AL12" s="4">
+        <f t="shared" si="5"/>
+        <v>555.5767331460687</v>
+      </c>
+      <c r="AM12" s="4">
+        <f t="shared" si="5"/>
+        <v>561.13250047752945</v>
+      </c>
+      <c r="AN12" s="4">
+        <f t="shared" si="5"/>
+        <v>566.74382548230471</v>
+      </c>
+      <c r="AO12" s="4">
+        <f t="shared" si="5"/>
+        <v>572.4112637371278</v>
+      </c>
+      <c r="AP12" s="4">
+        <f t="shared" si="5"/>
+        <v>578.13537637449906</v>
+      </c>
+      <c r="AQ12" s="4">
+        <f t="shared" si="5"/>
+        <v>583.91673013824402</v>
+      </c>
+      <c r="AR12" s="4">
+        <f t="shared" si="5"/>
+        <v>589.75589743962644</v>
+      </c>
+      <c r="AS12" s="4">
+        <f t="shared" si="5"/>
+        <v>595.65345641402268</v>
+      </c>
+      <c r="AT12" s="4">
+        <f t="shared" si="5"/>
+        <v>601.60999097816295</v>
+      </c>
+      <c r="AU12" s="4">
+        <f t="shared" si="5"/>
+        <v>607.62609088794454</v>
+      </c>
+      <c r="AV12" s="4">
+        <f t="shared" si="5"/>
+        <v>613.70235179682402</v>
+      </c>
+      <c r="AW12" s="4">
+        <f t="shared" si="5"/>
+        <v>619.83937531479228</v>
+      </c>
+      <c r="AX12" s="4">
+        <f t="shared" si="5"/>
+        <v>626.03776906794019</v>
+      </c>
+      <c r="AY12" s="4">
+        <f t="shared" si="5"/>
+        <v>632.29814675861962</v>
+      </c>
+      <c r="AZ12" s="4">
+        <f t="shared" si="5"/>
+        <v>638.62112822620577</v>
+      </c>
+      <c r="BA12" s="4">
+        <f t="shared" si="5"/>
+        <v>645.00733950846779</v>
+      </c>
+      <c r="BB12" s="4">
+        <f t="shared" si="5"/>
+        <v>651.45741290355249</v>
+      </c>
+      <c r="BC12" s="4">
+        <f t="shared" si="5"/>
+        <v>657.971987032588</v>
+      </c>
+      <c r="BD12" s="4">
+        <f t="shared" si="5"/>
+        <v>664.55170690291391</v>
+      </c>
+      <c r="BE12" s="4">
+        <f t="shared" si="5"/>
+        <v>671.197223971943</v>
+      </c>
+      <c r="BF12" s="4">
+        <f t="shared" si="5"/>
+        <v>677.90919621166245</v>
+      </c>
+      <c r="BG12" s="4">
+        <f t="shared" si="5"/>
+        <v>684.68828817377903</v>
+      </c>
+      <c r="BH12" s="4">
+        <f t="shared" si="5"/>
+        <v>691.5351710555168</v>
+      </c>
+      <c r="BI12" s="4">
+        <f t="shared" si="5"/>
+        <v>698.45052276607203</v>
+      </c>
+      <c r="BJ12" s="4">
+        <f t="shared" si="5"/>
+        <v>705.43502799373277</v>
+      </c>
+      <c r="BK12" s="4">
+        <f t="shared" si="5"/>
+        <v>712.48937827367013</v>
+      </c>
+      <c r="BL12" s="4">
+        <f t="shared" si="5"/>
+        <v>719.61427205640689</v>
+      </c>
+      <c r="BM12" s="4">
+        <f t="shared" si="5"/>
+        <v>726.81041477697102</v>
+      </c>
+      <c r="BN12" s="4">
+        <f t="shared" si="5"/>
+        <v>734.07851892474071</v>
+      </c>
+      <c r="BO12" s="4">
+        <f t="shared" si="5"/>
+        <v>741.41930411398812</v>
+      </c>
+      <c r="BP12" s="4">
+        <f t="shared" si="5"/>
+        <v>748.83349715512804</v>
+      </c>
+      <c r="BQ12" s="4">
+        <f t="shared" si="5"/>
+        <v>756.32183212667928</v>
+      </c>
+      <c r="BR12" s="4">
+        <f t="shared" si="5"/>
+        <v>763.88505044794613</v>
+      </c>
+      <c r="BS12" s="4">
+        <f t="shared" si="5"/>
+        <v>771.52390095242561</v>
+      </c>
+      <c r="BT12" s="4">
+        <f t="shared" si="5"/>
+        <v>779.23913996194983</v>
+      </c>
+      <c r="BU12" s="4">
+        <f t="shared" si="5"/>
+        <v>787.03153136156936</v>
+      </c>
+      <c r="BV12" s="4">
+        <f t="shared" si="5"/>
+        <v>794.90184667518508</v>
+      </c>
+      <c r="BW12" s="4">
+        <f t="shared" si="5"/>
+        <v>802.85086514193699</v>
+      </c>
+      <c r="BX12" s="4">
+        <f t="shared" si="5"/>
+        <v>810.87937379335642</v>
+      </c>
+      <c r="BY12" s="4">
+        <f t="shared" si="5"/>
+        <v>818.98816753128995</v>
+      </c>
+      <c r="BZ12" s="4">
+        <f t="shared" si="5"/>
+        <v>827.17804920660285</v>
+      </c>
+      <c r="CA12" s="4">
+        <f t="shared" si="5"/>
+        <v>835.44982969866885</v>
+      </c>
+      <c r="CB12" s="4">
+        <f t="shared" si="5"/>
+        <v>843.80432799565551</v>
+      </c>
+      <c r="CC12" s="4">
+        <f t="shared" si="5"/>
+        <v>852.24237127561207</v>
+      </c>
+      <c r="CD12" s="4">
+        <f t="shared" si="5"/>
+        <v>860.76479498836818</v>
+      </c>
+      <c r="CE12" s="4">
+        <f t="shared" si="5"/>
+        <v>869.37244293825188</v>
+      </c>
+      <c r="CF12" s="4">
+        <f t="shared" si="5"/>
+        <v>878.06616736763442</v>
+      </c>
+      <c r="CG12" s="4">
+        <f t="shared" si="5"/>
+        <v>886.8468290413108</v>
+      </c>
+      <c r="CH12" s="4">
+        <f t="shared" si="5"/>
+        <v>895.71529733172395</v>
+      </c>
+      <c r="CI12" s="4">
+        <f t="shared" si="5"/>
+        <v>904.67245030504114</v>
+      </c>
+      <c r="CJ12" s="4">
+        <f t="shared" si="5"/>
+        <v>913.71917480809157</v>
+      </c>
+      <c r="CK12" s="4">
+        <f t="shared" si="5"/>
+        <v>922.85636655617247</v>
+      </c>
+      <c r="CL12" s="4">
+        <f t="shared" si="5"/>
+        <v>932.08493022173423</v>
+      </c>
+      <c r="CM12" s="4">
+        <f t="shared" si="5"/>
+        <v>941.40577952395154</v>
+      </c>
+      <c r="CN12" s="4">
+        <f t="shared" si="5"/>
+        <v>950.81983731919104</v>
+      </c>
+      <c r="CO12" s="4">
+        <f t="shared" si="5"/>
+        <v>960.32803569238297</v>
+      </c>
+      <c r="CP12" s="4">
+        <f t="shared" si="5"/>
+        <v>969.93131604930682</v>
+      </c>
+      <c r="CQ12" s="4">
+        <f t="shared" si="5"/>
+        <v>979.63062920979985</v>
+      </c>
+      <c r="CR12" s="4">
+        <f t="shared" si="5"/>
+        <v>989.4269355018979</v>
+      </c>
+      <c r="CS12" s="4">
+        <f t="shared" si="5"/>
+        <v>999.32120485691689</v>
+      </c>
+      <c r="CT12" s="4">
+        <f t="shared" si="5"/>
+        <v>1009.314416905486</v>
+      </c>
+      <c r="CU12" s="4">
+        <f t="shared" si="5"/>
+        <v>1019.4075610745409</v>
+      </c>
+      <c r="CV12" s="4">
+        <f t="shared" si="5"/>
+        <v>1029.6016366852864</v>
+      </c>
+      <c r="CW12" s="4">
+        <f t="shared" ref="CW12:DE12" si="6">CV12*(1+$AA$33)</f>
+        <v>1039.8976530521393</v>
+      </c>
+      <c r="CX12" s="4">
+        <f t="shared" si="6"/>
+        <v>1050.2966295826607</v>
+      </c>
+      <c r="CY12" s="4">
+        <f t="shared" si="6"/>
+        <v>1060.7995958784873</v>
+      </c>
+      <c r="CZ12" s="4">
+        <f t="shared" si="6"/>
+        <v>1071.4075918372721</v>
+      </c>
+      <c r="DA12" s="4">
+        <f t="shared" si="6"/>
+        <v>1082.1216677556449</v>
+      </c>
+      <c r="DB12" s="4">
+        <f t="shared" si="6"/>
+        <v>1092.9428844332015</v>
+      </c>
+      <c r="DC12" s="4">
+        <f t="shared" si="6"/>
+        <v>1103.8723132775335</v>
+      </c>
+      <c r="DD12" s="4">
+        <f t="shared" si="6"/>
+        <v>1114.911036410309</v>
+      </c>
+      <c r="DE12" s="4">
+        <f t="shared" si="6"/>
+        <v>1126.060146774412</v>
+      </c>
+    </row>
+    <row r="13" spans="1:109" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="24">
-        <f t="shared" ref="J12:Q12" si="4">SUM(J3:J6)</f>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="24">
+        <f t="shared" ref="J13:R13" si="7">SUM(J3:J6)</f>
         <v>80.284999999999997</v>
       </c>
-      <c r="K12" s="24">
-        <f t="shared" si="4"/>
+      <c r="K13" s="24">
+        <f t="shared" si="7"/>
         <v>85.092999999999989</v>
       </c>
-      <c r="L12" s="24">
-        <f t="shared" si="4"/>
+      <c r="L13" s="24">
+        <f t="shared" si="7"/>
         <v>92.76700000000001</v>
       </c>
-      <c r="M12" s="24">
-        <f t="shared" si="4"/>
+      <c r="M13" s="24">
+        <f t="shared" si="7"/>
         <v>97.65</v>
       </c>
-      <c r="N12" s="24">
-        <f t="shared" si="4"/>
+      <c r="N13" s="24">
+        <f t="shared" si="7"/>
         <v>100.43700000000001</v>
       </c>
-      <c r="O12" s="24">
-        <f t="shared" si="4"/>
+      <c r="O13" s="24">
+        <f t="shared" si="7"/>
         <v>100.544</v>
       </c>
-      <c r="P12" s="24">
-        <f t="shared" si="4"/>
+      <c r="P13" s="24">
+        <f t="shared" si="7"/>
         <v>107.13399999999999</v>
       </c>
-      <c r="Q12" s="24">
-        <f t="shared" si="4"/>
+      <c r="Q13" s="24">
+        <f t="shared" si="7"/>
         <v>107.708</v>
       </c>
-      <c r="Y12" s="4">
+      <c r="R13" s="24">
+        <f t="shared" si="7"/>
+        <v>105.49699999999999</v>
+      </c>
+      <c r="Y13" s="4">
         <v>213.786</v>
       </c>
-      <c r="Z12" s="4">
+      <c r="Z13" s="4">
         <v>282.87599999999998</v>
       </c>
-      <c r="AA12" s="4">
-        <f>SUM(J12:M12)</f>
+      <c r="AA13" s="4">
+        <f>SUM(J13:M13)</f>
         <v>355.79499999999996</v>
       </c>
-      <c r="AB12" s="4">
-        <f>SUM(N12:Q12)</f>
+      <c r="AB13" s="4">
+        <f>SUM(N13:Q13)</f>
         <v>415.82299999999998</v>
       </c>
-      <c r="AC12" s="4">
-        <f t="shared" ref="AC12:AI12" si="5">AB12*(1+$X$30)</f>
+      <c r="AC13" s="4">
+        <f t="shared" ref="AC12:AI13" si="8">AB13*(1+$X$32)</f>
         <v>478.19644999999991</v>
       </c>
-      <c r="AD12" s="4">
-        <f t="shared" si="5"/>
+      <c r="AD13" s="4">
+        <f t="shared" si="8"/>
         <v>549.92591749999985</v>
       </c>
-      <c r="AE12" s="4">
-        <f t="shared" si="5"/>
+      <c r="AE13" s="4">
+        <f t="shared" si="8"/>
         <v>632.41480512499982</v>
       </c>
-      <c r="AF12" s="4">
-        <f t="shared" si="5"/>
+      <c r="AF13" s="4">
+        <f t="shared" si="8"/>
         <v>727.27702589374974</v>
       </c>
-      <c r="AG12" s="4">
-        <f t="shared" si="5"/>
+      <c r="AG13" s="4">
+        <f t="shared" si="8"/>
         <v>836.3685797778121</v>
       </c>
-      <c r="AH12" s="4">
-        <f t="shared" si="5"/>
+      <c r="AH13" s="4">
+        <f t="shared" si="8"/>
         <v>961.82386674448389</v>
       </c>
-      <c r="AI12" s="4">
-        <f t="shared" si="5"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="AJ12" s="4">
-        <f>AI12*(1+$X$31)</f>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="AK12" s="4">
-        <f t="shared" ref="AK12:CV12" si="6">AJ12*(1+$X$31)</f>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="AL12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="AM12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="AN12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="AO12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="AP12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="AQ12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="AR12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="AS12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="AT12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="AU12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="AV12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="AW12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="AX12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="AY12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="AZ12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="BA12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="BB12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="BC12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="BD12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="BE12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="BF12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="BG12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="BH12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="BI12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="BJ12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="BK12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="BL12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="BM12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="BN12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="BO12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="BP12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="BQ12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="BR12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="BS12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="BT12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="BU12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="BV12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="BW12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="BX12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="BY12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="BZ12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="CA12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="CB12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="CC12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="CD12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="CE12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="CF12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="CG12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="CH12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="CI12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="CJ12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="CK12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="CL12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="CM12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="CN12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="CO12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="CP12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="CQ12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="CR12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="CS12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="CT12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="CU12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="CV12" s="4">
-        <f t="shared" si="6"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="CW12" s="4">
-        <f t="shared" ref="CW12:DE12" si="7">CV12*(1+$X$31)</f>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="CX12" s="4">
-        <f t="shared" si="7"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="CY12" s="4">
-        <f t="shared" si="7"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="CZ12" s="4">
-        <f t="shared" si="7"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="DA12" s="4">
-        <f t="shared" si="7"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="DB12" s="4">
-        <f t="shared" si="7"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="DC12" s="4">
-        <f t="shared" si="7"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="DD12" s="4">
-        <f t="shared" si="7"/>
-        <v>1106.0974467561564</v>
-      </c>
-      <c r="DE12" s="4">
-        <f t="shared" si="7"/>
-        <v>1106.0974467561564</v>
-      </c>
-    </row>
-    <row r="13" spans="1:109" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="22">
-        <f>59.672</f>
-        <v>59.671999999999997</v>
-      </c>
-      <c r="K13" s="22">
-        <f>63.972</f>
-        <v>63.972000000000001</v>
-      </c>
-      <c r="L13" s="22">
-        <f>71.359</f>
-        <v>71.358999999999995</v>
-      </c>
-      <c r="M13" s="22">
-        <f>71.499</f>
-        <v>71.498999999999995</v>
-      </c>
-      <c r="N13" s="23">
-        <f>77.244</f>
-        <v>77.244</v>
-      </c>
-      <c r="O13" s="23">
-        <f>80.014</f>
-        <v>80.013999999999996</v>
-      </c>
-      <c r="P13" s="23">
-        <f>78.948</f>
-        <v>78.947999999999993</v>
-      </c>
-      <c r="Q13" s="23">
-        <v>81.307000000000002</v>
-      </c>
-      <c r="Y13" s="25">
-        <f>(Z12-Y12)/Y12</f>
-        <v>0.32317364093065015</v>
-      </c>
-      <c r="Z13" s="25">
-        <f>(AA12-Z12)/Z12</f>
-        <v>0.25777725929382483</v>
-      </c>
-      <c r="AA13" s="25">
-        <f>(AB12-AA12)/AA12</f>
-        <v>0.1687151309040319</v>
-      </c>
-      <c r="AB13" s="25">
-        <f>(AC12-AB12)/AB12</f>
-        <v>0.14999999999999986</v>
-      </c>
-      <c r="AC13" s="25">
-        <f>(AD12-AC12)/AC12</f>
-        <v>0.14999999999999991</v>
+      <c r="AI13" s="4">
+        <f t="shared" si="8"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="AJ13" s="4">
+        <f>AI13*(1+$X$33)</f>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="AK13" s="4">
+        <f t="shared" ref="AK13:CV13" si="9">AJ13*(1+$X$33)</f>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="AL13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="AM13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="AN13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="AO13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="AP13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="AQ13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="AR13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="AS13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="AT13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="AU13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="AV13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="AW13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="AX13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="AY13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="AZ13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="BA13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="BB13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="BC13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="BD13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="BE13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="BF13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="BG13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="BH13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="BI13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="BJ13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="BK13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="BL13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="BM13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="BN13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="BO13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="BP13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="BQ13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="BR13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="BS13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="BT13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="BU13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="BV13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="BW13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="BX13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="BY13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="BZ13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="CA13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="CB13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="CC13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="CD13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="CE13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="CF13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="CG13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="CH13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="CI13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="CJ13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="CK13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="CL13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="CM13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="CN13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="CO13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="CP13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="CQ13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="CR13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="CS13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="CT13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="CU13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="CV13" s="4">
+        <f t="shared" si="9"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="CW13" s="4">
+        <f t="shared" ref="CW13:DE13" si="10">CV13*(1+$X$33)</f>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="CX13" s="4">
+        <f t="shared" si="10"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="CY13" s="4">
+        <f t="shared" si="10"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="CZ13" s="4">
+        <f t="shared" si="10"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="DA13" s="4">
+        <f t="shared" si="10"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="DB13" s="4">
+        <f t="shared" si="10"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="DC13" s="4">
+        <f t="shared" si="10"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="DD13" s="4">
+        <f t="shared" si="10"/>
+        <v>1106.0974467561564</v>
+      </c>
+      <c r="DE13" s="4">
+        <f t="shared" si="10"/>
+        <v>1106.0974467561564</v>
       </c>
     </row>
     <row r="14" spans="1:109" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -1766,42 +2126,64 @@
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
-      <c r="J14" s="23">
-        <f t="shared" ref="J14:Q14" si="8">J12-J13</f>
-        <v>20.613</v>
-      </c>
-      <c r="K14" s="23">
-        <f t="shared" si="8"/>
-        <v>21.120999999999988</v>
-      </c>
-      <c r="L14" s="23">
-        <f t="shared" si="8"/>
-        <v>21.408000000000015</v>
-      </c>
-      <c r="M14" s="23">
-        <f t="shared" si="8"/>
-        <v>26.15100000000001</v>
+      <c r="J14" s="22">
+        <f>59.672</f>
+        <v>59.671999999999997</v>
+      </c>
+      <c r="K14" s="22">
+        <f>63.972</f>
+        <v>63.972000000000001</v>
+      </c>
+      <c r="L14" s="22">
+        <f>71.359</f>
+        <v>71.358999999999995</v>
+      </c>
+      <c r="M14" s="22">
+        <f>71.499</f>
+        <v>71.498999999999995</v>
       </c>
       <c r="N14" s="23">
-        <f t="shared" si="8"/>
-        <v>23.193000000000012</v>
+        <f>77.244</f>
+        <v>77.244</v>
       </c>
       <c r="O14" s="23">
-        <f t="shared" si="8"/>
-        <v>20.53</v>
+        <f>80.014</f>
+        <v>80.013999999999996</v>
       </c>
       <c r="P14" s="23">
-        <f t="shared" si="8"/>
-        <v>28.185999999999993</v>
+        <f>78.948</f>
+        <v>78.947999999999993</v>
       </c>
       <c r="Q14" s="23">
-        <f t="shared" si="8"/>
-        <v>26.400999999999996</v>
+        <v>81.307000000000002</v>
+      </c>
+      <c r="R14" s="6">
+        <v>76.933999999999997</v>
+      </c>
+      <c r="Y14" s="25">
+        <f>(Z13-Y13)/Y13</f>
+        <v>0.32317364093065015</v>
+      </c>
+      <c r="Z14" s="25">
+        <f>(AA13-Z13)/Z13</f>
+        <v>0.25777725929382483</v>
+      </c>
+      <c r="AA14" s="25">
+        <f>(AB13-AA13)/AA13</f>
+        <v>0.1687151309040319</v>
+      </c>
+      <c r="AB14" s="25">
+        <f>(AC13-AB13)/AB13</f>
+        <v>0.14999999999999986</v>
+      </c>
+      <c r="AC14" s="25">
+        <f>(AD13-AC13)/AC13</f>
+        <v>0.14999999999999991</v>
       </c>
     </row>
     <row r="15" spans="1:109" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -1811,39 +2193,46 @@
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
-      <c r="J15" s="22">
-        <f>10.841</f>
-        <v>10.840999999999999</v>
-      </c>
-      <c r="K15" s="22">
-        <f>10.101</f>
-        <v>10.101000000000001</v>
-      </c>
-      <c r="L15" s="22">
-        <f>12.843</f>
-        <v>12.843</v>
+      <c r="J15" s="23">
+        <f t="shared" ref="J15:R15" si="11">J13-J14</f>
+        <v>20.613</v>
+      </c>
+      <c r="K15" s="23">
+        <f t="shared" si="11"/>
+        <v>21.120999999999988</v>
+      </c>
+      <c r="L15" s="23">
+        <f t="shared" si="11"/>
+        <v>21.408000000000015</v>
       </c>
       <c r="M15" s="23">
-        <v>14.493</v>
+        <f t="shared" si="11"/>
+        <v>26.15100000000001</v>
       </c>
       <c r="N15" s="23">
-        <f>14.315</f>
-        <v>14.315</v>
+        <f t="shared" si="11"/>
+        <v>23.193000000000012</v>
       </c>
       <c r="O15" s="23">
-        <f>14.888</f>
-        <v>14.888</v>
+        <f t="shared" si="11"/>
+        <v>20.53</v>
       </c>
       <c r="P15" s="23">
-        <v>14.66</v>
+        <f t="shared" si="11"/>
+        <v>28.185999999999993</v>
       </c>
       <c r="Q15" s="23">
-        <v>14.493</v>
+        <f t="shared" si="11"/>
+        <v>26.400999999999996</v>
+      </c>
+      <c r="R15" s="23">
+        <f t="shared" si="11"/>
+        <v>28.562999999999988</v>
       </c>
     </row>
     <row r="16" spans="1:109" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -1853,36 +2242,43 @@
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
-      <c r="J16" s="23">
-        <v>0</v>
-      </c>
-      <c r="K16" s="23">
-        <v>0</v>
-      </c>
-      <c r="L16" s="23">
-        <v>0</v>
-      </c>
-      <c r="M16" s="22">
-        <v>9.2100000000000009</v>
+      <c r="J16" s="22">
+        <f>10.841</f>
+        <v>10.840999999999999</v>
+      </c>
+      <c r="K16" s="22">
+        <f>10.101</f>
+        <v>10.101000000000001</v>
+      </c>
+      <c r="L16" s="22">
+        <f>12.843</f>
+        <v>12.843</v>
+      </c>
+      <c r="M16" s="23">
+        <v>14.493</v>
       </c>
       <c r="N16" s="23">
-        <f>0</f>
-        <v>0</v>
+        <f>14.315</f>
+        <v>14.315</v>
       </c>
       <c r="O16" s="23">
-        <f>25.63</f>
-        <v>25.63</v>
+        <f>14.888</f>
+        <v>14.888</v>
       </c>
       <c r="P16" s="23">
-        <v>0</v>
+        <v>14.66</v>
       </c>
       <c r="Q16" s="23">
-        <v>9.5079999999999991</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>14.493</v>
+      </c>
+      <c r="R16" s="6">
+        <f>15.768</f>
+        <v>15.768000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -1892,39 +2288,40 @@
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
-      <c r="J17" s="22">
-        <f>22.368</f>
-        <v>22.367999999999999</v>
-      </c>
-      <c r="K17" s="22">
-        <f>26.398</f>
-        <v>26.398</v>
-      </c>
-      <c r="L17" s="22">
-        <f>26.543</f>
-        <v>26.542999999999999</v>
+      <c r="J17" s="23">
+        <v>0</v>
+      </c>
+      <c r="K17" s="23">
+        <v>0</v>
+      </c>
+      <c r="L17" s="23">
+        <v>0</v>
       </c>
       <c r="M17" s="22">
-        <v>16.7</v>
+        <v>9.2100000000000009</v>
       </c>
       <c r="N17" s="23">
-        <f>27.478</f>
-        <v>27.478000000000002</v>
+        <f>0</f>
+        <v>0</v>
       </c>
       <c r="O17" s="23">
+        <f>25.63</f>
+        <v>25.63</v>
+      </c>
+      <c r="P17" s="23">
         <v>0</v>
       </c>
-      <c r="P17" s="23">
-        <v>26.248999999999999</v>
-      </c>
       <c r="Q17" s="23">
-        <f>18.64</f>
-        <v>18.64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>9.5079999999999991</v>
+      </c>
+      <c r="R17" s="6">
+        <f>10.926</f>
+        <v>10.926</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1935,39 +2332,42 @@
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
       <c r="J18" s="22">
+        <f>22.368</f>
+        <v>22.367999999999999</v>
+      </c>
+      <c r="K18" s="22">
+        <f>26.398</f>
+        <v>26.398</v>
+      </c>
+      <c r="L18" s="22">
+        <f>26.543</f>
+        <v>26.542999999999999</v>
+      </c>
+      <c r="M18" s="22">
+        <v>16.7</v>
+      </c>
+      <c r="N18" s="23">
+        <f>27.478</f>
+        <v>27.478000000000002</v>
+      </c>
+      <c r="O18" s="23">
         <v>0</v>
       </c>
-      <c r="K18" s="22">
-        <v>0.72099999999999997</v>
-      </c>
-      <c r="L18" s="22">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="M18" s="22">
-        <f>-4.4+0.464</f>
-        <v>-3.9360000000000004</v>
-      </c>
-      <c r="N18" s="23">
-        <f>-5.2+0.464</f>
-        <v>-4.7359999999999998</v>
-      </c>
-      <c r="O18" s="23">
-        <f>-2.3+0.465-0.5</f>
-        <v>-2.335</v>
-      </c>
       <c r="P18" s="23">
-        <f>0.464</f>
-        <v>0.46400000000000002</v>
+        <v>26.248999999999999</v>
       </c>
       <c r="Q18" s="23">
-        <f>-1.7+0.465</f>
-        <v>-1.2349999999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" s="6" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <f>18.64</f>
+        <v>18.64</v>
+      </c>
+      <c r="R18" s="6">
+        <f>25.608</f>
+        <v>25.608000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -1977,42 +2377,44 @@
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
-      <c r="J19" s="23">
-        <f t="shared" ref="J19:Q19" si="9">SUM(J15:J18)</f>
-        <v>33.208999999999996</v>
-      </c>
-      <c r="K19" s="23">
-        <f t="shared" si="9"/>
-        <v>37.22</v>
-      </c>
-      <c r="L19" s="23">
-        <f t="shared" si="9"/>
-        <v>39.385999999999996</v>
-      </c>
-      <c r="M19" s="23">
-        <f t="shared" si="9"/>
-        <v>36.467000000000006</v>
+      <c r="J19" s="22">
+        <v>0</v>
+      </c>
+      <c r="K19" s="22">
+        <v>0.72099999999999997</v>
+      </c>
+      <c r="L19" s="22">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="22">
+        <f>-4.4+0.464</f>
+        <v>-3.9360000000000004</v>
       </c>
       <c r="N19" s="23">
-        <f t="shared" si="9"/>
-        <v>37.057000000000002</v>
+        <f>-5.2+0.464</f>
+        <v>-4.7359999999999998</v>
       </c>
       <c r="O19" s="23">
-        <f t="shared" si="9"/>
-        <v>38.183</v>
+        <f>-2.3+0.465-0.5</f>
+        <v>-2.335</v>
       </c>
       <c r="P19" s="23">
-        <f t="shared" si="9"/>
-        <v>41.372999999999998</v>
+        <f>0.464</f>
+        <v>0.46400000000000002</v>
       </c>
       <c r="Q19" s="23">
-        <f t="shared" si="9"/>
-        <v>41.405999999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <f>-1.7+0.465</f>
+        <v>-1.2349999999999999</v>
+      </c>
+      <c r="R19" s="6">
+        <f>0+0.932</f>
+        <v>0.93200000000000005</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" s="6" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -2023,41 +2425,45 @@
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
       <c r="J20" s="23">
-        <f t="shared" ref="J20:Q20" si="10">J14-J19</f>
-        <v>-12.595999999999997</v>
+        <f t="shared" ref="J20:R20" si="12">SUM(J16:J19)</f>
+        <v>33.208999999999996</v>
       </c>
       <c r="K20" s="23">
-        <f t="shared" si="10"/>
-        <v>-16.099000000000011</v>
+        <f t="shared" si="12"/>
+        <v>37.22</v>
       </c>
       <c r="L20" s="23">
-        <f t="shared" si="10"/>
-        <v>-17.97799999999998</v>
+        <f t="shared" si="12"/>
+        <v>39.385999999999996</v>
       </c>
       <c r="M20" s="23">
-        <f t="shared" si="10"/>
-        <v>-10.315999999999995</v>
+        <f t="shared" si="12"/>
+        <v>36.467000000000006</v>
       </c>
       <c r="N20" s="23">
-        <f t="shared" si="10"/>
-        <v>-13.86399999999999</v>
+        <f t="shared" si="12"/>
+        <v>37.057000000000002</v>
       </c>
       <c r="O20" s="23">
-        <f t="shared" si="10"/>
-        <v>-17.652999999999999</v>
+        <f t="shared" si="12"/>
+        <v>38.183</v>
       </c>
       <c r="P20" s="23">
-        <f t="shared" si="10"/>
-        <v>-13.187000000000005</v>
+        <f t="shared" si="12"/>
+        <v>41.372999999999998</v>
       </c>
       <c r="Q20" s="23">
-        <f t="shared" si="10"/>
-        <v>-15.005000000000003</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>41.405999999999999</v>
+      </c>
+      <c r="R20" s="23">
+        <f t="shared" si="12"/>
+        <v>53.234000000000009</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -2067,42 +2473,46 @@
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
-      <c r="J21" s="22">
-        <f>-2.463-0.368</f>
-        <v>-2.831</v>
-      </c>
-      <c r="K21" s="22">
-        <f>-2.451+-0.257</f>
-        <v>-2.7080000000000002</v>
-      </c>
-      <c r="L21" s="22">
-        <f>-2.14-0.179</f>
-        <v>-2.319</v>
-      </c>
-      <c r="M21" s="22">
-        <f>-1.747+-0.42</f>
-        <v>-2.1670000000000003</v>
+      <c r="J21" s="23">
+        <f t="shared" ref="J21:R21" si="13">J15-J20</f>
+        <v>-12.595999999999997</v>
+      </c>
+      <c r="K21" s="23">
+        <f t="shared" si="13"/>
+        <v>-16.099000000000011</v>
+      </c>
+      <c r="L21" s="23">
+        <f t="shared" si="13"/>
+        <v>-17.97799999999998</v>
+      </c>
+      <c r="M21" s="23">
+        <f t="shared" si="13"/>
+        <v>-10.315999999999995</v>
       </c>
       <c r="N21" s="23">
-        <f>-1.667-0.059</f>
-        <v>-1.726</v>
+        <f t="shared" si="13"/>
+        <v>-13.86399999999999</v>
       </c>
       <c r="O21" s="23">
-        <f>-1.735</f>
-        <v>-1.7350000000000001</v>
+        <f t="shared" si="13"/>
+        <v>-17.652999999999999</v>
       </c>
       <c r="P21" s="23">
-        <f>-1.75-0.373</f>
-        <v>-2.1230000000000002</v>
+        <f t="shared" si="13"/>
+        <v>-13.187000000000005</v>
       </c>
       <c r="Q21" s="23">
-        <f>-1.779</f>
-        <v>-1.7789999999999999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>-15.005000000000003</v>
+      </c>
+      <c r="R21" s="23">
+        <f t="shared" si="13"/>
+        <v>-24.671000000000021</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -2112,42 +2522,46 @@
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
-      <c r="J22" s="23">
-        <f t="shared" ref="J22:Q22" si="11">J20+J21</f>
-        <v>-15.426999999999996</v>
-      </c>
-      <c r="K22" s="23">
-        <f t="shared" si="11"/>
-        <v>-18.807000000000009</v>
-      </c>
-      <c r="L22" s="23">
-        <f t="shared" si="11"/>
-        <v>-20.296999999999979</v>
-      </c>
-      <c r="M22" s="23">
-        <f t="shared" si="11"/>
-        <v>-12.482999999999995</v>
+      <c r="J22" s="22">
+        <f>-2.463-0.368</f>
+        <v>-2.831</v>
+      </c>
+      <c r="K22" s="22">
+        <f>-2.451+-0.257</f>
+        <v>-2.7080000000000002</v>
+      </c>
+      <c r="L22" s="22">
+        <f>-2.14-0.179</f>
+        <v>-2.319</v>
+      </c>
+      <c r="M22" s="22">
+        <f>-1.747+-0.42</f>
+        <v>-2.1670000000000003</v>
       </c>
       <c r="N22" s="23">
-        <f t="shared" si="11"/>
-        <v>-15.589999999999989</v>
+        <f>-1.667-0.059</f>
+        <v>-1.726</v>
       </c>
       <c r="O22" s="23">
-        <f t="shared" si="11"/>
-        <v>-19.387999999999998</v>
+        <f>-1.735</f>
+        <v>-1.7350000000000001</v>
       </c>
       <c r="P22" s="23">
-        <f t="shared" si="11"/>
-        <v>-15.310000000000006</v>
+        <f>-1.75-0.373</f>
+        <v>-2.1230000000000002</v>
       </c>
       <c r="Q22" s="23">
-        <f t="shared" si="11"/>
-        <v>-16.784000000000002</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <f>-1.779</f>
+        <v>-1.7789999999999999</v>
+      </c>
+      <c r="R22" s="6">
+        <f>-1.708+0.306</f>
+        <v>-1.4019999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -2157,41 +2571,46 @@
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
-      <c r="J23" s="22">
-        <f>-0.01</f>
-        <v>-0.01</v>
-      </c>
-      <c r="K23" s="22">
-        <f>-0.041</f>
-        <v>-4.1000000000000002E-2</v>
-      </c>
-      <c r="L23" s="22">
-        <f>-0.578</f>
-        <v>-0.57799999999999996</v>
-      </c>
-      <c r="M23" s="22">
-        <f>-0.623</f>
-        <v>-0.623</v>
+      <c r="J23" s="23">
+        <f t="shared" ref="J23:R23" si="14">J21+J22</f>
+        <v>-15.426999999999996</v>
+      </c>
+      <c r="K23" s="23">
+        <f t="shared" si="14"/>
+        <v>-18.807000000000009</v>
+      </c>
+      <c r="L23" s="23">
+        <f t="shared" si="14"/>
+        <v>-20.296999999999979</v>
+      </c>
+      <c r="M23" s="23">
+        <f t="shared" si="14"/>
+        <v>-12.482999999999995</v>
       </c>
       <c r="N23" s="23">
-        <f>-0.315</f>
-        <v>-0.315</v>
+        <f t="shared" si="14"/>
+        <v>-15.589999999999989</v>
       </c>
       <c r="O23" s="23">
-        <f>-0.409</f>
-        <v>-0.40899999999999997</v>
+        <f t="shared" si="14"/>
+        <v>-19.387999999999998</v>
       </c>
       <c r="P23" s="23">
-        <f>-0.206</f>
-        <v>-0.20599999999999999</v>
+        <f t="shared" si="14"/>
+        <v>-15.310000000000006</v>
       </c>
       <c r="Q23" s="23">
-        <v>-1.0580000000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="14"/>
+        <v>-16.784000000000002</v>
+      </c>
+      <c r="R23" s="23">
+        <f t="shared" si="14"/>
+        <v>-26.073000000000022</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -2201,264 +2620,322 @@
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
-      <c r="J24" s="23">
-        <f t="shared" ref="J24:Q24" si="12">J22+J23</f>
+      <c r="J24" s="22">
+        <f>-0.01</f>
+        <v>-0.01</v>
+      </c>
+      <c r="K24" s="22">
+        <f>-0.041</f>
+        <v>-4.1000000000000002E-2</v>
+      </c>
+      <c r="L24" s="22">
+        <f>-0.578</f>
+        <v>-0.57799999999999996</v>
+      </c>
+      <c r="M24" s="22">
+        <f>-0.623</f>
+        <v>-0.623</v>
+      </c>
+      <c r="N24" s="23">
+        <f>-0.315</f>
+        <v>-0.315</v>
+      </c>
+      <c r="O24" s="23">
+        <f>-0.409</f>
+        <v>-0.40899999999999997</v>
+      </c>
+      <c r="P24" s="23">
+        <f>-0.206</f>
+        <v>-0.20599999999999999</v>
+      </c>
+      <c r="Q24" s="23">
+        <v>-1.0580000000000001</v>
+      </c>
+      <c r="R24" s="6">
+        <f>7.785</f>
+        <v>7.7850000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="23">
+        <f t="shared" ref="J25:R25" si="15">J23+J24</f>
         <v>-15.436999999999996</v>
       </c>
-      <c r="K24" s="23">
-        <f t="shared" si="12"/>
+      <c r="K25" s="23">
+        <f t="shared" si="15"/>
         <v>-18.84800000000001</v>
       </c>
-      <c r="L24" s="23">
-        <f t="shared" si="12"/>
+      <c r="L25" s="23">
+        <f t="shared" si="15"/>
         <v>-20.874999999999979</v>
       </c>
-      <c r="M24" s="23">
-        <f t="shared" si="12"/>
+      <c r="M25" s="23">
+        <f t="shared" si="15"/>
         <v>-13.105999999999995</v>
       </c>
-      <c r="N24" s="23">
-        <f t="shared" si="12"/>
+      <c r="N25" s="23">
+        <f t="shared" si="15"/>
         <v>-15.904999999999989</v>
       </c>
-      <c r="O24" s="23">
-        <f t="shared" si="12"/>
+      <c r="O25" s="23">
+        <f t="shared" si="15"/>
         <v>-19.796999999999997</v>
       </c>
-      <c r="P24" s="23">
-        <f t="shared" si="12"/>
+      <c r="P25" s="23">
+        <f t="shared" si="15"/>
         <v>-15.516000000000005</v>
       </c>
-      <c r="Q24" s="23">
-        <f t="shared" si="12"/>
+      <c r="Q25" s="23">
+        <f t="shared" si="15"/>
         <v>-17.842000000000002</v>
       </c>
-    </row>
-    <row r="25" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
+      <c r="R25" s="23">
+        <f t="shared" si="15"/>
+        <v>-18.288000000000022</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="23">
-        <f t="shared" ref="J25:Q25" si="13">J24/J26</f>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="23">
+        <f t="shared" ref="J26:R26" si="16">J25/J27</f>
         <v>-0.57237671486837216</v>
       </c>
-      <c r="K25" s="23">
-        <f t="shared" si="13"/>
+      <c r="K26" s="23">
+        <f t="shared" si="16"/>
         <v>-0.69853976725224265</v>
       </c>
-      <c r="L25" s="23">
-        <f t="shared" si="13"/>
+      <c r="L26" s="23">
+        <f t="shared" si="16"/>
         <v>-0.77001106602729541</v>
       </c>
-      <c r="M25" s="23">
-        <f t="shared" si="13"/>
+      <c r="M26" s="23">
+        <f t="shared" si="16"/>
         <v>-0.48329522826167104</v>
       </c>
-      <c r="N25" s="23">
-        <f t="shared" si="13"/>
+      <c r="N26" s="23">
+        <f t="shared" si="16"/>
         <v>-0.58166325336454028</v>
       </c>
-      <c r="O25" s="23">
-        <f t="shared" si="13"/>
+      <c r="O26" s="23">
+        <f t="shared" si="16"/>
         <v>-0.72365390941989249</v>
       </c>
-      <c r="P25" s="23">
-        <f t="shared" si="13"/>
+      <c r="P26" s="23">
+        <f t="shared" si="16"/>
         <v>-0.56479324403028552</v>
       </c>
-      <c r="Q25" s="23">
-        <f t="shared" si="13"/>
+      <c r="Q26" s="23">
+        <f t="shared" si="16"/>
         <v>-0.63794336384439365</v>
       </c>
-    </row>
-    <row r="26" spans="1:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
+      <c r="R26" s="23">
+        <f t="shared" si="16"/>
+        <v>-0.61959615124000622</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="22">
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="22">
         <v>26.97</v>
       </c>
-      <c r="K26" s="22">
+      <c r="K27" s="22">
         <v>26.981999999999999</v>
       </c>
-      <c r="L26" s="22">
+      <c r="L27" s="22">
         <v>27.11</v>
       </c>
-      <c r="M26" s="22">
+      <c r="M27" s="22">
         <v>27.117999999999999</v>
       </c>
-      <c r="N26" s="23">
+      <c r="N27" s="23">
         <v>27.344000000000001</v>
       </c>
-      <c r="O26" s="23">
+      <c r="O27" s="23">
         <v>27.356999999999999</v>
       </c>
-      <c r="P26" s="23">
+      <c r="P27" s="23">
         <v>27.472000000000001</v>
       </c>
-      <c r="Q26" s="23">
+      <c r="Q27" s="23">
         <v>27.968</v>
       </c>
-    </row>
-    <row r="28" spans="1:24" s="12" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A28" s="4" t="s">
+      <c r="R27" s="6">
+        <v>29.515999999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A29" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="N29" s="11">
+        <f>+N12/J12-1</f>
+        <v>0.16548278557591001</v>
+      </c>
+      <c r="O29" s="11">
+        <f>+O12/K12-1</f>
+        <v>8.3495660033348518E-2</v>
+      </c>
+      <c r="P29" s="11">
+        <f>+P12/L12-1</f>
+        <v>5.091217649554336E-3</v>
+      </c>
+      <c r="Q29" s="11">
+        <f>+Q12/M12-1</f>
+        <v>-1.517392958282282E-2</v>
+      </c>
+      <c r="R29" s="11">
+        <f>+R12/N12-1</f>
+        <v>2.1710603056106281E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" s="12" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="11">
-        <f>+N12/J12-1</f>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11">
+        <f>+N13/J13-1</f>
         <v>0.25100579186647587</v>
       </c>
-      <c r="O28" s="11">
-        <f>+O12/K12-1</f>
+      <c r="O30" s="11">
+        <f>+O13/K13-1</f>
         <v>0.18157780310953919</v>
       </c>
-      <c r="P28" s="11">
-        <f>+P12/L12-1</f>
+      <c r="P30" s="11">
+        <f>+P13/L13-1</f>
         <v>0.15487188332057711</v>
       </c>
-      <c r="Q28" s="11">
-        <f>+Q12/M12-1</f>
+      <c r="Q30" s="11">
+        <f>+Q13/M13-1</f>
         <v>0.10300051203276994</v>
       </c>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
+      <c r="R30" s="11">
+        <f>+R13/N13-1</f>
+        <v>5.0379840098768058E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="13" t="e">
-        <f t="shared" ref="D29:J29" si="14">+D14/D12</f>
+      <c r="D31" s="13" t="e">
+        <f t="shared" ref="D31:J31" si="17">+D15/D13</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E29" s="13" t="e">
-        <f t="shared" si="14"/>
+      <c r="E31" s="13" t="e">
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F29" s="13" t="e">
-        <f t="shared" si="14"/>
+      <c r="F31" s="13" t="e">
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G29" s="13" t="e">
-        <f t="shared" si="14"/>
+      <c r="G31" s="13" t="e">
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H29" s="13" t="e">
-        <f t="shared" si="14"/>
+      <c r="H31" s="13" t="e">
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I29" s="13" t="e">
-        <f t="shared" si="14"/>
+      <c r="I31" s="13" t="e">
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J29" s="13">
-        <f t="shared" si="14"/>
+      <c r="J31" s="13">
+        <f t="shared" si="17"/>
         <v>0.2567478358348384</v>
       </c>
-      <c r="K29" s="13">
-        <f>+K14/K12</f>
+      <c r="K31" s="13">
+        <f>+K15/K13</f>
         <v>0.24821078114533499</v>
       </c>
-      <c r="L29" s="13">
-        <f t="shared" ref="L29:Q29" si="15">+L14/L12</f>
+      <c r="L31" s="13">
+        <f t="shared" ref="L31:R31" si="18">+L15/L13</f>
         <v>0.23077171839123842</v>
       </c>
-      <c r="M29" s="13">
-        <f t="shared" si="15"/>
+      <c r="M31" s="13">
+        <f t="shared" si="18"/>
         <v>0.26780337941628274</v>
       </c>
-      <c r="N29" s="13">
-        <f t="shared" si="15"/>
+      <c r="N31" s="13">
+        <f t="shared" si="18"/>
         <v>0.23092087577287265</v>
       </c>
-      <c r="O29" s="13">
-        <f t="shared" si="15"/>
+      <c r="O31" s="13">
+        <f t="shared" si="18"/>
         <v>0.20418921069382562</v>
       </c>
-      <c r="P29" s="13">
-        <f t="shared" si="15"/>
+      <c r="P31" s="13">
+        <f t="shared" si="18"/>
         <v>0.2630910821961282</v>
       </c>
-      <c r="Q29" s="13">
-        <f t="shared" si="15"/>
+      <c r="Q31" s="13">
+        <f t="shared" si="18"/>
         <v>0.2451164258922271</v>
       </c>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="W30" s="14" t="s">
+      <c r="R31" s="13">
+        <f t="shared" si="18"/>
+        <v>0.27074703546072393</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="W32" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="X30" s="15">
+      <c r="X32" s="15">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="31" spans="1:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-      <c r="W31" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="X31" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="W32" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="X32" s="17">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="33" spans="2:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z32" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA32" s="15">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -2472,14 +2949,19 @@
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="W33" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="X33" s="26">
-        <f>NPV(X32,Y12:DE12)</f>
-        <v>4120.6585220078041</v>
-      </c>
-    </row>
-    <row r="34" spans="2:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="X33" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA33" s="17">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
@@ -2492,23 +2974,20 @@
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
       <c r="M34" s="7"/>
-      <c r="Q34" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="R34" s="6">
-        <v>23</v>
-      </c>
-      <c r="S34" s="6" t="s">
-        <v>58</v>
-      </c>
       <c r="W34" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="X34" s="19">
-        <v>28.5</v>
-      </c>
-    </row>
-    <row r="35" spans="2:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="X34" s="17">
+        <v>0.15</v>
+      </c>
+      <c r="Z34" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA34" s="17">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
@@ -2522,14 +3001,21 @@
       <c r="L35" s="7"/>
       <c r="M35" s="7"/>
       <c r="W35" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="X35" s="20">
-        <f>X33/X34</f>
-        <v>144.58450954413348</v>
-      </c>
-    </row>
-    <row r="36" spans="2:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="X35" s="26">
+        <f>NPV(X34,Y13:DE13)</f>
+        <v>4120.6585220078041</v>
+      </c>
+      <c r="Z35" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA35" s="26">
+        <f>NPV(AA34,AA12:DH12)</f>
+        <v>2774.0440873876159</v>
+      </c>
+    </row>
+    <row r="36" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
@@ -2542,15 +3028,31 @@
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
+      <c r="Q36" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="R36" s="6">
+        <v>23</v>
+      </c>
+      <c r="S36" s="6" t="s">
+        <v>58</v>
+      </c>
       <c r="W36" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="X36" s="15">
-        <f>(X35-Main!L5)/Main!L5</f>
-        <v>2.323017916436072</v>
-      </c>
-    </row>
-    <row r="37" spans="2:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="X36" s="19">
+        <f>$R$27</f>
+        <v>29.515999999999998</v>
+      </c>
+      <c r="Z36" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA36" s="19">
+        <f>$R$27</f>
+        <v>29.515999999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
@@ -2564,14 +3066,21 @@
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="W37" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="X37" s="18">
-        <f>X34*X35</f>
-        <v>4120.6585220078041</v>
-      </c>
-    </row>
-    <row r="38" spans="2:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="X37" s="20">
+        <f>X35/X36</f>
+        <v>139.60762034177409</v>
+      </c>
+      <c r="Z37" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA37" s="20">
+        <f>AA35/AA36</f>
+        <v>93.984418193102599</v>
+      </c>
+    </row>
+    <row r="38" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
@@ -2584,8 +3093,22 @@
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
-    </row>
-    <row r="39" spans="2:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="W38" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="X38" s="15">
+        <f>(X37-Main!L5)/Main!L5</f>
+        <v>2.0029602138475817</v>
+      </c>
+      <c r="Z38" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA38" s="15">
+        <f>(AA37-Main!L5)/Main!L5</f>
+        <v>1.0216050374941406</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
@@ -2598,8 +3121,36 @@
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
       <c r="M39" s="7"/>
-    </row>
-    <row r="41" spans="2:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="W39" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="X39" s="18">
+        <f>X36*X37</f>
+        <v>4120.6585220078041</v>
+      </c>
+      <c r="Z39" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA39" s="18">
+        <f>AA36*AA37</f>
+        <v>2774.0440873876159</v>
+      </c>
+    </row>
+    <row r="40" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7"/>
+      <c r="J40" s="7"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="7"/>
+      <c r="M40" s="7"/>
+    </row>
+    <row r="41" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
@@ -2613,21 +3164,7 @@
       <c r="L41" s="7"/>
       <c r="M41" s="7"/>
     </row>
-    <row r="42" spans="2:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="7"/>
-      <c r="J42" s="7"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
-      <c r="M42" s="7"/>
-    </row>
-    <row r="43" spans="2:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
@@ -2641,7 +3178,7 @@
       <c r="L43" s="7"/>
       <c r="M43" s="7"/>
     </row>
-    <row r="44" spans="2:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
@@ -2655,7 +3192,7 @@
       <c r="L44" s="7"/>
       <c r="M44" s="7"/>
     </row>
-    <row r="45" spans="2:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
@@ -2669,7 +3206,7 @@
       <c r="L45" s="7"/>
       <c r="M45" s="7"/>
     </row>
-    <row r="46" spans="2:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
@@ -2683,7 +3220,7 @@
       <c r="L46" s="7"/>
       <c r="M46" s="7"/>
     </row>
-    <row r="47" spans="2:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
@@ -2697,7 +3234,7 @@
       <c r="L47" s="7"/>
       <c r="M47" s="7"/>
     </row>
-    <row r="48" spans="2:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
@@ -2710,6 +3247,20 @@
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
       <c r="M48" s="7"/>
+    </row>
+    <row r="49" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="7"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="7"/>
+      <c r="M49" s="7"/>
     </row>
     <row r="50" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B50" s="7"/>
@@ -2725,20 +3276,6 @@
       <c r="L50" s="7"/>
       <c r="M50" s="7"/>
     </row>
-    <row r="51" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7"/>
-      <c r="L51" s="7"/>
-      <c r="M51" s="7"/>
-    </row>
     <row r="52" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
@@ -2879,6 +3416,34 @@
       <c r="L61" s="7"/>
       <c r="M61" s="7"/>
     </row>
+    <row r="62" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="7"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
+      <c r="G62" s="7"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="7"/>
+      <c r="J62" s="7"/>
+      <c r="K62" s="7"/>
+      <c r="L62" s="7"/>
+      <c r="M62" s="7"/>
+    </row>
+    <row r="63" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="7"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="7"/>
+      <c r="G63" s="7"/>
+      <c r="H63" s="7"/>
+      <c r="I63" s="7"/>
+      <c r="J63" s="7"/>
+      <c r="K63" s="7"/>
+      <c r="L63" s="7"/>
+      <c r="M63" s="7"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/$PAR.xlsx
+++ b/$PAR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffe\Documents\GitHub\martinshkreli-models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68083993-078D-4D11-B934-DBE90321755F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD4D5C4-6009-4351-B61A-789FCA30AAB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20685" yWindow="150" windowWidth="26190" windowHeight="20805" activeTab="1" xr2:uid="{8F193AD5-4822-438A-B757-2B234AE27955}"/>
+    <workbookView xWindow="-15" yWindow="90" windowWidth="27270" windowHeight="20805" activeTab="1" xr2:uid="{8F193AD5-4822-438A-B757-2B234AE27955}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="2" r:id="rId1"/>
@@ -36,8 +36,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Jefferson Hwang</author>
+  </authors>
+  <commentList>
+    <comment ref="S6" authorId="0" shapeId="0" xr:uid="{0589989D-7AAA-4DF0-B645-F7329CE92812}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Jefferson Hwang:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Sold their Government Business Unit</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
   <si>
     <t>FY</t>
   </si>
@@ -186,9 +220,6 @@
     <t>G&amp;A</t>
   </si>
   <si>
-    <t>CCL</t>
-  </si>
-  <si>
     <t>Seq Sub Growth %</t>
   </si>
   <si>
@@ -229,6 +260,18 @@
   </si>
   <si>
     <t>Restaurant Rev Y/Y</t>
+  </si>
+  <si>
+    <t>Q424</t>
+  </si>
+  <si>
+    <t>Q125</t>
+  </si>
+  <si>
+    <t>Misc (CCL, etc.)</t>
+  </si>
+  <si>
+    <t>Rest Rev</t>
   </si>
 </sst>
 </file>
@@ -242,7 +285,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -271,6 +314,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -712,7 +768,7 @@
         <v>41</v>
       </c>
       <c r="L5" s="8">
-        <v>46.49</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="11:12" x14ac:dyDescent="0.25">
@@ -720,7 +776,7 @@
         <v>26</v>
       </c>
       <c r="L6" s="6">
-        <v>29.515999999999998</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="11:12" x14ac:dyDescent="0.25">
@@ -729,7 +785,7 @@
       </c>
       <c r="L7" s="6">
         <f>+L5*L6</f>
-        <v>1372.19884</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="8" spans="11:12" x14ac:dyDescent="0.25">
@@ -754,7 +810,7 @@
       </c>
       <c r="L10" s="6">
         <f>+L7-L8+L9</f>
-        <v>1592.82584</v>
+        <v>2773.627</v>
       </c>
     </row>
   </sheetData>
@@ -763,8 +819,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE7FAD33-99C5-4121-980B-8556C8EA76DD}">
-  <dimension ref="A1:DE63"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE7FAD33-99C5-4121-980B-8556C8EA76DD}">
+  <dimension ref="A1:DH63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
@@ -776,15 +832,21 @@
     <col min="10" max="10" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:109" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:112" x14ac:dyDescent="0.25">
       <c r="D1" s="2">
         <v>44104</v>
       </c>
@@ -806,11 +868,35 @@
       <c r="N1" s="3">
         <v>45016</v>
       </c>
-      <c r="W1" t="s">
+      <c r="O1" s="2">
+        <v>45107</v>
+      </c>
+      <c r="P1" s="3">
+        <v>45199</v>
+      </c>
+      <c r="Q1" s="2">
+        <v>45291</v>
+      </c>
+      <c r="R1" s="3">
+        <v>45382</v>
+      </c>
+      <c r="S1" s="2">
+        <v>45473</v>
+      </c>
+      <c r="T1" s="3">
+        <v>45565</v>
+      </c>
+      <c r="U1" s="2">
+        <v>45657</v>
+      </c>
+      <c r="V1" s="3">
+        <v>45747</v>
+      </c>
+      <c r="Z1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:109" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:112" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
@@ -860,65 +946,72 @@
         <v>39</v>
       </c>
       <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="U2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="W2" s="1">
+      <c r="Z2" s="1">
         <v>2018</v>
       </c>
-      <c r="X2" s="1">
+      <c r="AA2" s="1">
         <v>2019</v>
       </c>
-      <c r="Y2">
+      <c r="AB2">
         <v>2020</v>
       </c>
-      <c r="Z2">
-        <f>+Y2+1</f>
+      <c r="AC2">
+        <f>+AB2+1</f>
         <v>2021</v>
       </c>
-      <c r="AA2">
-        <f t="shared" ref="AA2:AC2" si="0">+Z2+1</f>
+      <c r="AD2">
+        <f t="shared" ref="AD2:AF2" si="0">+AC2+1</f>
         <v>2022</v>
       </c>
-      <c r="AB2">
+      <c r="AE2">
         <f t="shared" si="0"/>
         <v>2023</v>
       </c>
-      <c r="AC2">
+      <c r="AF2">
         <f t="shared" si="0"/>
         <v>2024</v>
       </c>
-      <c r="AD2">
+      <c r="AG2">
         <v>2025</v>
       </c>
-      <c r="AE2">
+      <c r="AH2">
         <v>2026</v>
       </c>
-      <c r="AF2">
+      <c r="AI2">
         <v>2027</v>
       </c>
-      <c r="AG2">
+      <c r="AJ2">
         <v>2028</v>
       </c>
-      <c r="AH2">
+      <c r="AK2">
         <v>2029</v>
       </c>
-      <c r="AI2">
+      <c r="AL2">
         <v>2030</v>
       </c>
     </row>
-    <row r="3" spans="1:109" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -955,8 +1048,17 @@
       <c r="R3" s="23">
         <v>18.225999999999999</v>
       </c>
-    </row>
-    <row r="4" spans="1:109" x14ac:dyDescent="0.25">
+      <c r="S3" s="23">
+        <v>20.116</v>
+      </c>
+      <c r="T3" s="23">
+        <v>22.65</v>
+      </c>
+      <c r="U3" s="23">
+        <v>26.047999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
         <v>44</v>
       </c>
@@ -995,16 +1097,25 @@
       <c r="R4" s="32">
         <v>38.378999999999998</v>
       </c>
-      <c r="U4">
+      <c r="S4" s="32">
+        <v>44.872</v>
+      </c>
+      <c r="T4" s="32">
+        <v>59.908999999999999</v>
+      </c>
+      <c r="U4" s="32">
+        <v>64.262</v>
+      </c>
+      <c r="X4">
         <f>1.15*Q4</f>
         <v>37.831549999999993</v>
       </c>
-      <c r="V4" s="23">
+      <c r="Y4" s="23">
         <f>Q4+23.4</f>
         <v>56.296999999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:109" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -1041,8 +1152,17 @@
       <c r="R5" s="23">
         <v>13.468</v>
       </c>
-    </row>
-    <row r="6" spans="1:109" x14ac:dyDescent="0.25">
+      <c r="S5" s="23">
+        <v>13.162000000000001</v>
+      </c>
+      <c r="T5" s="23">
+        <v>14.195</v>
+      </c>
+      <c r="U5" s="23">
+        <v>14.695</v>
+      </c>
+    </row>
+    <row r="6" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>46</v>
       </c>
@@ -1073,10 +1193,19 @@
       <c r="R6" s="23">
         <v>35.423999999999999</v>
       </c>
-    </row>
-    <row r="7" spans="1:109" x14ac:dyDescent="0.25">
+      <c r="S6" s="23">
+        <v>0</v>
+      </c>
+      <c r="T6" s="23">
+        <v>0</v>
+      </c>
+      <c r="U6" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B7" s="29"/>
       <c r="C7" s="29"/>
@@ -1110,10 +1239,22 @@
         <f>(R4-N4)/N4</f>
         <v>0.3723940640085821</v>
       </c>
-    </row>
-    <row r="8" spans="1:109" x14ac:dyDescent="0.25">
+      <c r="S7" s="33">
+        <f>(S4-O4)/O4</f>
+        <v>0.47741340708547347</v>
+      </c>
+      <c r="T7" s="33">
+        <f>(T4-P4)/P4</f>
+        <v>0.91018078627682297</v>
+      </c>
+      <c r="U7" s="33">
+        <f>(U4-Q4)/Q4</f>
+        <v>0.95343040398820567</v>
+      </c>
+    </row>
+    <row r="8" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J8" s="27"/>
       <c r="K8" s="27">
@@ -1121,7 +1262,7 @@
         <v>8.7620389945971267E-2</v>
       </c>
       <c r="L8" s="27">
-        <f t="shared" ref="L8:R8" si="1">(L4-K4)/K4</f>
+        <f t="shared" ref="L8:U8" si="1">(L4-K4)/K4</f>
         <v>8.7257019438445063E-2</v>
       </c>
       <c r="M8" s="27">
@@ -1148,21 +1289,30 @@
         <f t="shared" si="1"/>
         <v>0.16664133507614676</v>
       </c>
-      <c r="Z8" s="25">
-        <f>(Z13-Y13)/Y13</f>
+      <c r="S8" s="27">
+        <f t="shared" si="1"/>
+        <v>0.16918106256025436</v>
+      </c>
+      <c r="T8" s="27">
+        <f t="shared" si="1"/>
+        <v>0.33510875378855409</v>
+      </c>
+      <c r="U8" s="27">
+        <f>(U4-T4)/T4</f>
+        <v>7.2660201305313088E-2</v>
+      </c>
+      <c r="AC8" s="25">
+        <f>(AC13-AB13)/AB13</f>
         <v>0.32317364093065015</v>
       </c>
-      <c r="AA8" s="25">
-        <f>(AA13-Z13)/Z13</f>
+      <c r="AD8" s="25">
+        <f>(AD13-AC13)/AC13</f>
         <v>0.25777725929382483</v>
       </c>
-      <c r="AB8" s="25">
-        <f>(AB13-AA13)/AA13</f>
+      <c r="AE8" s="25">
+        <f>(AE13-AD13)/AD13</f>
         <v>0.1687151309040319</v>
       </c>
-      <c r="AC8" s="25"/>
-      <c r="AD8" s="25"/>
-      <c r="AE8" s="25"/>
       <c r="AF8" s="25"/>
       <c r="AG8" s="25"/>
       <c r="AH8" s="25"/>
@@ -1183,14 +1333,17 @@
       <c r="AW8" s="25"/>
       <c r="AX8" s="25"/>
       <c r="AY8" s="25"/>
-    </row>
-    <row r="9" spans="1:109" x14ac:dyDescent="0.25">
+      <c r="AZ8" s="25"/>
+      <c r="BA8" s="25"/>
+      <c r="BB8" s="25"/>
+    </row>
+    <row r="9" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J9" s="27"/>
       <c r="K9" s="27">
-        <f t="shared" ref="K9:R9" si="2">K15/K13</f>
+        <f t="shared" ref="K9:U9" si="2">K15/K13</f>
         <v>0.24821078114533499</v>
       </c>
       <c r="L9" s="27">
@@ -1221,9 +1374,18 @@
         <f t="shared" si="2"/>
         <v>0.27074703546072393</v>
       </c>
-      <c r="Z9" s="25"/>
-      <c r="AA9" s="25"/>
-      <c r="AB9" s="25"/>
+      <c r="S9" s="27">
+        <f t="shared" si="2"/>
+        <v>0.40982725527831099</v>
+      </c>
+      <c r="T9" s="27">
+        <f t="shared" si="2"/>
+        <v>0.44474647043016308</v>
+      </c>
+      <c r="U9" s="27">
+        <f t="shared" si="2"/>
+        <v>0.42861768487214896</v>
+      </c>
       <c r="AC9" s="25"/>
       <c r="AD9" s="25"/>
       <c r="AE9" s="25"/>
@@ -1247,14 +1409,17 @@
       <c r="AW9" s="25"/>
       <c r="AX9" s="25"/>
       <c r="AY9" s="25"/>
-    </row>
-    <row r="10" spans="1:109" x14ac:dyDescent="0.25">
+      <c r="AZ9" s="25"/>
+      <c r="BA9" s="25"/>
+      <c r="BB9" s="25"/>
+    </row>
+    <row r="10" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J10" s="22"/>
       <c r="K10" s="27">
-        <f t="shared" ref="K10:R10" si="3">K8+K9</f>
+        <f t="shared" ref="K10:U10" si="3">K8+K9</f>
         <v>0.33583117109130622</v>
       </c>
       <c r="L10" s="27">
@@ -1285,9 +1450,18 @@
         <f t="shared" si="3"/>
         <v>0.43738837053687069</v>
       </c>
-      <c r="Z10" s="25"/>
-      <c r="AA10" s="25"/>
-      <c r="AB10" s="25"/>
+      <c r="S10" s="27">
+        <f t="shared" si="3"/>
+        <v>0.57900831783856532</v>
+      </c>
+      <c r="T10" s="27">
+        <f t="shared" si="3"/>
+        <v>0.77985522421871711</v>
+      </c>
+      <c r="U10" s="27">
+        <f t="shared" si="3"/>
+        <v>0.50127788617746205</v>
+      </c>
       <c r="AC10" s="25"/>
       <c r="AD10" s="25"/>
       <c r="AE10" s="25"/>
@@ -1311,8 +1485,11 @@
       <c r="AW10" s="25"/>
       <c r="AX10" s="25"/>
       <c r="AY10" s="25"/>
-    </row>
-    <row r="11" spans="1:109" x14ac:dyDescent="0.25">
+      <c r="AZ10" s="25"/>
+      <c r="BA10" s="25"/>
+      <c r="BB10" s="25"/>
+    </row>
+    <row r="11" spans="1:112" x14ac:dyDescent="0.25">
       <c r="J11" s="22"/>
       <c r="K11" s="27"/>
       <c r="L11" s="27"/>
@@ -1321,18 +1498,15 @@
       <c r="O11" s="27"/>
       <c r="P11" s="27"/>
       <c r="Q11" s="27"/>
-      <c r="X11" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y11" s="34"/>
-      <c r="Z11" s="34"/>
-      <c r="AA11" s="34"/>
-      <c r="AB11" s="34">
+      <c r="AA11" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB11" s="34"/>
+      <c r="AC11" s="34"/>
+      <c r="AD11" s="34"/>
+      <c r="AE11" s="34">
         <v>136.9</v>
       </c>
-      <c r="AC11" s="25"/>
-      <c r="AD11" s="25"/>
-      <c r="AE11" s="25"/>
       <c r="AF11" s="25"/>
       <c r="AG11" s="25"/>
       <c r="AH11" s="25"/>
@@ -1353,381 +1527,396 @@
       <c r="AW11" s="25"/>
       <c r="AX11" s="25"/>
       <c r="AY11" s="25"/>
-    </row>
-    <row r="12" spans="1:109" x14ac:dyDescent="0.25">
+      <c r="AZ11" s="25"/>
+      <c r="BA11" s="25"/>
+      <c r="BB11" s="25"/>
+    </row>
+    <row r="12" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A12" s="35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J12" s="36">
-        <f>SUM(J3:J5)</f>
+        <f t="shared" ref="J12:U12" si="4">SUM(J3:J5)</f>
         <v>58.846000000000004</v>
       </c>
       <c r="K12" s="36">
-        <f>SUM(K3:K5)</f>
+        <f t="shared" si="4"/>
         <v>64.170999999999992</v>
       </c>
       <c r="L12" s="36">
-        <f>SUM(L3:L5)</f>
+        <f t="shared" si="4"/>
         <v>68.353000000000009</v>
       </c>
       <c r="M12" s="36">
-        <f>SUM(M3:M5)</f>
+        <f t="shared" si="4"/>
         <v>70.977000000000004</v>
       </c>
       <c r="N12" s="36">
-        <f>SUM(N3:N5)</f>
+        <f t="shared" si="4"/>
         <v>68.584000000000003</v>
       </c>
       <c r="O12" s="36">
-        <f>SUM(O3:O5)</f>
+        <f t="shared" si="4"/>
         <v>69.528999999999996</v>
       </c>
       <c r="P12" s="36">
-        <f>SUM(P3:P5)</f>
+        <f t="shared" si="4"/>
         <v>68.700999999999993</v>
       </c>
       <c r="Q12" s="36">
-        <f>SUM(Q3:Q5)</f>
+        <f t="shared" si="4"/>
         <v>69.899999999999991</v>
       </c>
       <c r="R12" s="36">
-        <f>SUM(R3:R5)</f>
+        <f t="shared" si="4"/>
         <v>70.072999999999993</v>
       </c>
-      <c r="AA12" s="38">
+      <c r="S12" s="36">
+        <f t="shared" si="4"/>
+        <v>78.150000000000006</v>
+      </c>
+      <c r="T12" s="36">
+        <f t="shared" si="4"/>
+        <v>96.753999999999991</v>
+      </c>
+      <c r="U12" s="36">
+        <f t="shared" si="4"/>
+        <v>105.005</v>
+      </c>
+      <c r="AD12" s="38">
         <f>SUM(J12:M12)</f>
         <v>262.34699999999998</v>
       </c>
-      <c r="AB12" s="38">
+      <c r="AE12" s="38">
         <f>SUM(N12:Q12)</f>
         <v>276.714</v>
       </c>
-      <c r="AC12" s="4">
-        <f>AB12*(1+$AA$32)</f>
+      <c r="AF12" s="4">
+        <f>AE12*(1+$AD$32)</f>
         <v>304.3854</v>
       </c>
-      <c r="AD12" s="4">
-        <f t="shared" ref="AD12:AI12" si="4">AC12*(1+$AA$32)</f>
+      <c r="AG12" s="4">
+        <f t="shared" ref="AG12:AL12" si="5">AF12*(1+$AD$32)</f>
         <v>334.82394000000005</v>
       </c>
-      <c r="AE12" s="4">
-        <f t="shared" si="4"/>
+      <c r="AH12" s="4">
+        <f t="shared" si="5"/>
         <v>368.30633400000011</v>
       </c>
-      <c r="AF12" s="4">
-        <f t="shared" si="4"/>
+      <c r="AI12" s="4">
+        <f t="shared" si="5"/>
         <v>405.13696740000017</v>
       </c>
-      <c r="AG12" s="4">
-        <f t="shared" si="4"/>
+      <c r="AJ12" s="4">
+        <f t="shared" si="5"/>
         <v>445.65066414000023</v>
       </c>
-      <c r="AH12" s="4">
-        <f t="shared" si="4"/>
+      <c r="AK12" s="4">
+        <f t="shared" si="5"/>
         <v>490.21573055400029</v>
-      </c>
-      <c r="AI12" s="4">
-        <f t="shared" si="4"/>
-        <v>539.23730360940033</v>
-      </c>
-      <c r="AJ12" s="4">
-        <f>AI12*(1+$AA$33)</f>
-        <v>544.62967664549433</v>
-      </c>
-      <c r="AK12" s="4">
-        <f t="shared" ref="AK12:CV12" si="5">AJ12*(1+$AA$33)</f>
-        <v>550.07597341194924</v>
       </c>
       <c r="AL12" s="4">
         <f t="shared" si="5"/>
+        <v>539.23730360940033</v>
+      </c>
+      <c r="AM12" s="4">
+        <f>AL12*(1+$AD$33)</f>
+        <v>544.62967664549433</v>
+      </c>
+      <c r="AN12" s="4">
+        <f t="shared" ref="AN12:CY12" si="6">AM12*(1+$AD$33)</f>
+        <v>550.07597341194924</v>
+      </c>
+      <c r="AO12" s="4">
+        <f t="shared" si="6"/>
         <v>555.5767331460687</v>
       </c>
-      <c r="AM12" s="4">
-        <f t="shared" si="5"/>
+      <c r="AP12" s="4">
+        <f t="shared" si="6"/>
         <v>561.13250047752945</v>
       </c>
-      <c r="AN12" s="4">
-        <f t="shared" si="5"/>
+      <c r="AQ12" s="4">
+        <f t="shared" si="6"/>
         <v>566.74382548230471</v>
       </c>
-      <c r="AO12" s="4">
-        <f t="shared" si="5"/>
+      <c r="AR12" s="4">
+        <f t="shared" si="6"/>
         <v>572.4112637371278</v>
       </c>
-      <c r="AP12" s="4">
-        <f t="shared" si="5"/>
+      <c r="AS12" s="4">
+        <f t="shared" si="6"/>
         <v>578.13537637449906</v>
       </c>
-      <c r="AQ12" s="4">
-        <f t="shared" si="5"/>
+      <c r="AT12" s="4">
+        <f t="shared" si="6"/>
         <v>583.91673013824402</v>
       </c>
-      <c r="AR12" s="4">
-        <f t="shared" si="5"/>
+      <c r="AU12" s="4">
+        <f t="shared" si="6"/>
         <v>589.75589743962644</v>
       </c>
-      <c r="AS12" s="4">
-        <f t="shared" si="5"/>
+      <c r="AV12" s="4">
+        <f t="shared" si="6"/>
         <v>595.65345641402268</v>
       </c>
-      <c r="AT12" s="4">
-        <f t="shared" si="5"/>
+      <c r="AW12" s="4">
+        <f t="shared" si="6"/>
         <v>601.60999097816295</v>
       </c>
-      <c r="AU12" s="4">
-        <f t="shared" si="5"/>
+      <c r="AX12" s="4">
+        <f t="shared" si="6"/>
         <v>607.62609088794454</v>
       </c>
-      <c r="AV12" s="4">
-        <f t="shared" si="5"/>
+      <c r="AY12" s="4">
+        <f t="shared" si="6"/>
         <v>613.70235179682402</v>
       </c>
-      <c r="AW12" s="4">
-        <f t="shared" si="5"/>
+      <c r="AZ12" s="4">
+        <f t="shared" si="6"/>
         <v>619.83937531479228</v>
       </c>
-      <c r="AX12" s="4">
-        <f t="shared" si="5"/>
+      <c r="BA12" s="4">
+        <f t="shared" si="6"/>
         <v>626.03776906794019</v>
       </c>
-      <c r="AY12" s="4">
-        <f t="shared" si="5"/>
+      <c r="BB12" s="4">
+        <f t="shared" si="6"/>
         <v>632.29814675861962</v>
       </c>
-      <c r="AZ12" s="4">
-        <f t="shared" si="5"/>
+      <c r="BC12" s="4">
+        <f t="shared" si="6"/>
         <v>638.62112822620577</v>
       </c>
-      <c r="BA12" s="4">
-        <f t="shared" si="5"/>
+      <c r="BD12" s="4">
+        <f t="shared" si="6"/>
         <v>645.00733950846779</v>
       </c>
-      <c r="BB12" s="4">
-        <f t="shared" si="5"/>
+      <c r="BE12" s="4">
+        <f t="shared" si="6"/>
         <v>651.45741290355249</v>
       </c>
-      <c r="BC12" s="4">
-        <f t="shared" si="5"/>
+      <c r="BF12" s="4">
+        <f t="shared" si="6"/>
         <v>657.971987032588</v>
       </c>
-      <c r="BD12" s="4">
-        <f t="shared" si="5"/>
+      <c r="BG12" s="4">
+        <f t="shared" si="6"/>
         <v>664.55170690291391</v>
       </c>
-      <c r="BE12" s="4">
-        <f t="shared" si="5"/>
+      <c r="BH12" s="4">
+        <f t="shared" si="6"/>
         <v>671.197223971943</v>
       </c>
-      <c r="BF12" s="4">
-        <f t="shared" si="5"/>
+      <c r="BI12" s="4">
+        <f t="shared" si="6"/>
         <v>677.90919621166245</v>
       </c>
-      <c r="BG12" s="4">
-        <f t="shared" si="5"/>
+      <c r="BJ12" s="4">
+        <f t="shared" si="6"/>
         <v>684.68828817377903</v>
       </c>
-      <c r="BH12" s="4">
-        <f t="shared" si="5"/>
+      <c r="BK12" s="4">
+        <f t="shared" si="6"/>
         <v>691.5351710555168</v>
       </c>
-      <c r="BI12" s="4">
-        <f t="shared" si="5"/>
+      <c r="BL12" s="4">
+        <f t="shared" si="6"/>
         <v>698.45052276607203</v>
       </c>
-      <c r="BJ12" s="4">
-        <f t="shared" si="5"/>
+      <c r="BM12" s="4">
+        <f t="shared" si="6"/>
         <v>705.43502799373277</v>
       </c>
-      <c r="BK12" s="4">
-        <f t="shared" si="5"/>
+      <c r="BN12" s="4">
+        <f t="shared" si="6"/>
         <v>712.48937827367013</v>
       </c>
-      <c r="BL12" s="4">
-        <f t="shared" si="5"/>
+      <c r="BO12" s="4">
+        <f t="shared" si="6"/>
         <v>719.61427205640689</v>
       </c>
-      <c r="BM12" s="4">
-        <f t="shared" si="5"/>
+      <c r="BP12" s="4">
+        <f t="shared" si="6"/>
         <v>726.81041477697102</v>
       </c>
-      <c r="BN12" s="4">
-        <f t="shared" si="5"/>
+      <c r="BQ12" s="4">
+        <f t="shared" si="6"/>
         <v>734.07851892474071</v>
       </c>
-      <c r="BO12" s="4">
-        <f t="shared" si="5"/>
+      <c r="BR12" s="4">
+        <f t="shared" si="6"/>
         <v>741.41930411398812</v>
       </c>
-      <c r="BP12" s="4">
-        <f t="shared" si="5"/>
+      <c r="BS12" s="4">
+        <f t="shared" si="6"/>
         <v>748.83349715512804</v>
       </c>
-      <c r="BQ12" s="4">
-        <f t="shared" si="5"/>
+      <c r="BT12" s="4">
+        <f t="shared" si="6"/>
         <v>756.32183212667928</v>
       </c>
-      <c r="BR12" s="4">
-        <f t="shared" si="5"/>
+      <c r="BU12" s="4">
+        <f t="shared" si="6"/>
         <v>763.88505044794613</v>
       </c>
-      <c r="BS12" s="4">
-        <f t="shared" si="5"/>
+      <c r="BV12" s="4">
+        <f t="shared" si="6"/>
         <v>771.52390095242561</v>
       </c>
-      <c r="BT12" s="4">
-        <f t="shared" si="5"/>
+      <c r="BW12" s="4">
+        <f t="shared" si="6"/>
         <v>779.23913996194983</v>
       </c>
-      <c r="BU12" s="4">
-        <f t="shared" si="5"/>
+      <c r="BX12" s="4">
+        <f t="shared" si="6"/>
         <v>787.03153136156936</v>
       </c>
-      <c r="BV12" s="4">
-        <f t="shared" si="5"/>
+      <c r="BY12" s="4">
+        <f t="shared" si="6"/>
         <v>794.90184667518508</v>
       </c>
-      <c r="BW12" s="4">
-        <f t="shared" si="5"/>
+      <c r="BZ12" s="4">
+        <f t="shared" si="6"/>
         <v>802.85086514193699</v>
       </c>
-      <c r="BX12" s="4">
-        <f t="shared" si="5"/>
+      <c r="CA12" s="4">
+        <f t="shared" si="6"/>
         <v>810.87937379335642</v>
       </c>
-      <c r="BY12" s="4">
-        <f t="shared" si="5"/>
+      <c r="CB12" s="4">
+        <f t="shared" si="6"/>
         <v>818.98816753128995</v>
       </c>
-      <c r="BZ12" s="4">
-        <f t="shared" si="5"/>
+      <c r="CC12" s="4">
+        <f t="shared" si="6"/>
         <v>827.17804920660285</v>
       </c>
-      <c r="CA12" s="4">
-        <f t="shared" si="5"/>
+      <c r="CD12" s="4">
+        <f t="shared" si="6"/>
         <v>835.44982969866885</v>
       </c>
-      <c r="CB12" s="4">
-        <f t="shared" si="5"/>
+      <c r="CE12" s="4">
+        <f t="shared" si="6"/>
         <v>843.80432799565551</v>
       </c>
-      <c r="CC12" s="4">
-        <f t="shared" si="5"/>
+      <c r="CF12" s="4">
+        <f t="shared" si="6"/>
         <v>852.24237127561207</v>
       </c>
-      <c r="CD12" s="4">
-        <f t="shared" si="5"/>
+      <c r="CG12" s="4">
+        <f t="shared" si="6"/>
         <v>860.76479498836818</v>
       </c>
-      <c r="CE12" s="4">
-        <f t="shared" si="5"/>
+      <c r="CH12" s="4">
+        <f t="shared" si="6"/>
         <v>869.37244293825188</v>
       </c>
-      <c r="CF12" s="4">
-        <f t="shared" si="5"/>
+      <c r="CI12" s="4">
+        <f t="shared" si="6"/>
         <v>878.06616736763442</v>
       </c>
-      <c r="CG12" s="4">
-        <f t="shared" si="5"/>
+      <c r="CJ12" s="4">
+        <f t="shared" si="6"/>
         <v>886.8468290413108</v>
       </c>
-      <c r="CH12" s="4">
-        <f t="shared" si="5"/>
+      <c r="CK12" s="4">
+        <f t="shared" si="6"/>
         <v>895.71529733172395</v>
       </c>
-      <c r="CI12" s="4">
-        <f t="shared" si="5"/>
+      <c r="CL12" s="4">
+        <f t="shared" si="6"/>
         <v>904.67245030504114</v>
       </c>
-      <c r="CJ12" s="4">
-        <f t="shared" si="5"/>
+      <c r="CM12" s="4">
+        <f t="shared" si="6"/>
         <v>913.71917480809157</v>
       </c>
-      <c r="CK12" s="4">
-        <f t="shared" si="5"/>
+      <c r="CN12" s="4">
+        <f t="shared" si="6"/>
         <v>922.85636655617247</v>
       </c>
-      <c r="CL12" s="4">
-        <f t="shared" si="5"/>
+      <c r="CO12" s="4">
+        <f t="shared" si="6"/>
         <v>932.08493022173423</v>
       </c>
-      <c r="CM12" s="4">
-        <f t="shared" si="5"/>
+      <c r="CP12" s="4">
+        <f t="shared" si="6"/>
         <v>941.40577952395154</v>
       </c>
-      <c r="CN12" s="4">
-        <f t="shared" si="5"/>
+      <c r="CQ12" s="4">
+        <f t="shared" si="6"/>
         <v>950.81983731919104</v>
       </c>
-      <c r="CO12" s="4">
-        <f t="shared" si="5"/>
+      <c r="CR12" s="4">
+        <f t="shared" si="6"/>
         <v>960.32803569238297</v>
       </c>
-      <c r="CP12" s="4">
-        <f t="shared" si="5"/>
+      <c r="CS12" s="4">
+        <f t="shared" si="6"/>
         <v>969.93131604930682</v>
       </c>
-      <c r="CQ12" s="4">
-        <f t="shared" si="5"/>
+      <c r="CT12" s="4">
+        <f t="shared" si="6"/>
         <v>979.63062920979985</v>
       </c>
-      <c r="CR12" s="4">
-        <f t="shared" si="5"/>
+      <c r="CU12" s="4">
+        <f t="shared" si="6"/>
         <v>989.4269355018979</v>
       </c>
-      <c r="CS12" s="4">
-        <f t="shared" si="5"/>
+      <c r="CV12" s="4">
+        <f t="shared" si="6"/>
         <v>999.32120485691689</v>
       </c>
-      <c r="CT12" s="4">
-        <f t="shared" si="5"/>
+      <c r="CW12" s="4">
+        <f t="shared" si="6"/>
         <v>1009.314416905486</v>
       </c>
-      <c r="CU12" s="4">
-        <f t="shared" si="5"/>
+      <c r="CX12" s="4">
+        <f t="shared" si="6"/>
         <v>1019.4075610745409</v>
       </c>
-      <c r="CV12" s="4">
-        <f t="shared" si="5"/>
+      <c r="CY12" s="4">
+        <f t="shared" si="6"/>
         <v>1029.6016366852864</v>
       </c>
-      <c r="CW12" s="4">
-        <f t="shared" ref="CW12:DE12" si="6">CV12*(1+$AA$33)</f>
+      <c r="CZ12" s="4">
+        <f t="shared" ref="CZ12:DH12" si="7">CY12*(1+$AD$33)</f>
         <v>1039.8976530521393</v>
       </c>
-      <c r="CX12" s="4">
-        <f t="shared" si="6"/>
+      <c r="DA12" s="4">
+        <f t="shared" si="7"/>
         <v>1050.2966295826607</v>
       </c>
-      <c r="CY12" s="4">
-        <f t="shared" si="6"/>
+      <c r="DB12" s="4">
+        <f t="shared" si="7"/>
         <v>1060.7995958784873</v>
       </c>
-      <c r="CZ12" s="4">
-        <f t="shared" si="6"/>
+      <c r="DC12" s="4">
+        <f t="shared" si="7"/>
         <v>1071.4075918372721</v>
       </c>
-      <c r="DA12" s="4">
-        <f t="shared" si="6"/>
+      <c r="DD12" s="4">
+        <f t="shared" si="7"/>
         <v>1082.1216677556449</v>
       </c>
-      <c r="DB12" s="4">
-        <f t="shared" si="6"/>
+      <c r="DE12" s="4">
+        <f t="shared" si="7"/>
         <v>1092.9428844332015</v>
       </c>
-      <c r="DC12" s="4">
-        <f t="shared" si="6"/>
+      <c r="DF12" s="4">
+        <f t="shared" si="7"/>
         <v>1103.8723132775335</v>
       </c>
-      <c r="DD12" s="4">
-        <f t="shared" si="6"/>
+      <c r="DG12" s="4">
+        <f t="shared" si="7"/>
         <v>1114.911036410309</v>
       </c>
-      <c r="DE12" s="4">
-        <f t="shared" si="6"/>
+      <c r="DH12" s="4">
+        <f t="shared" si="7"/>
         <v>1126.060146774412</v>
       </c>
     </row>
-    <row r="13" spans="1:109" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:112" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>15</v>
       </c>
@@ -1740,381 +1929,393 @@
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="24">
-        <f t="shared" ref="J13:R13" si="7">SUM(J3:J6)</f>
+        <f t="shared" ref="J13:U13" si="8">SUM(J3:J6)</f>
         <v>80.284999999999997</v>
       </c>
       <c r="K13" s="24">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>85.092999999999989</v>
       </c>
       <c r="L13" s="24">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>92.76700000000001</v>
       </c>
       <c r="M13" s="24">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97.65</v>
       </c>
       <c r="N13" s="24">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>100.43700000000001</v>
       </c>
       <c r="O13" s="24">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>100.544</v>
       </c>
       <c r="P13" s="24">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>107.13399999999999</v>
       </c>
       <c r="Q13" s="24">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>107.708</v>
       </c>
       <c r="R13" s="24">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>105.49699999999999</v>
       </c>
-      <c r="Y13" s="4">
+      <c r="S13" s="24">
+        <f t="shared" si="8"/>
+        <v>78.150000000000006</v>
+      </c>
+      <c r="T13" s="24">
+        <f t="shared" si="8"/>
+        <v>96.753999999999991</v>
+      </c>
+      <c r="U13" s="24">
+        <f t="shared" si="8"/>
+        <v>105.005</v>
+      </c>
+      <c r="AB13" s="4">
         <v>213.786</v>
       </c>
-      <c r="Z13" s="4">
+      <c r="AC13" s="4">
         <v>282.87599999999998</v>
       </c>
-      <c r="AA13" s="4">
+      <c r="AD13" s="4">
         <f>SUM(J13:M13)</f>
         <v>355.79499999999996</v>
       </c>
-      <c r="AB13" s="4">
+      <c r="AE13" s="4">
         <f>SUM(N13:Q13)</f>
         <v>415.82299999999998</v>
       </c>
-      <c r="AC13" s="4">
-        <f t="shared" ref="AC12:AI13" si="8">AB13*(1+$X$32)</f>
-        <v>478.19644999999991</v>
-      </c>
-      <c r="AD13" s="4">
-        <f t="shared" si="8"/>
-        <v>549.92591749999985</v>
-      </c>
-      <c r="AE13" s="4">
-        <f t="shared" si="8"/>
-        <v>632.41480512499982</v>
-      </c>
       <c r="AF13" s="4">
-        <f t="shared" si="8"/>
-        <v>727.27702589374974</v>
+        <f>SUM(R13:U13)</f>
+        <v>385.40599999999995</v>
       </c>
       <c r="AG13" s="4">
-        <f t="shared" si="8"/>
-        <v>836.3685797778121</v>
+        <f t="shared" ref="AF13:AL15" si="9">AF13*(1+$AA$32)</f>
+        <v>462.48719999999992</v>
       </c>
       <c r="AH13" s="4">
-        <f t="shared" si="8"/>
-        <v>961.82386674448389</v>
+        <f t="shared" si="9"/>
+        <v>554.9846399999999</v>
       </c>
       <c r="AI13" s="4">
-        <f t="shared" si="8"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="9"/>
+        <v>665.98156799999981</v>
       </c>
       <c r="AJ13" s="4">
-        <f>AI13*(1+$X$33)</f>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="9"/>
+        <v>799.17788159999975</v>
       </c>
       <c r="AK13" s="4">
-        <f t="shared" ref="AK13:CV13" si="9">AJ13*(1+$X$33)</f>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="9"/>
+        <v>959.01345791999961</v>
       </c>
       <c r="AL13" s="4">
         <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <v>1150.8161495039994</v>
       </c>
       <c r="AM13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f>AL13*(1+$AA$33)</f>
+        <v>1139.3079880089595</v>
       </c>
       <c r="AN13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" ref="AN13:CY13" si="10">AM13*(1+$AA$33)</f>
+        <v>1127.9149081288699</v>
       </c>
       <c r="AO13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>1116.6357590475811</v>
       </c>
       <c r="AP13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>1105.4694014571053</v>
       </c>
       <c r="AQ13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>1094.4147074425341</v>
       </c>
       <c r="AR13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>1083.4705603681089</v>
       </c>
       <c r="AS13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>1072.6358547644277</v>
       </c>
       <c r="AT13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>1061.9094962167833</v>
       </c>
       <c r="AU13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>1051.2904012546155</v>
       </c>
       <c r="AV13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>1040.7774972420693</v>
       </c>
       <c r="AW13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>1030.3697222696487</v>
       </c>
       <c r="AX13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>1020.0660250469522</v>
       </c>
       <c r="AY13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>1009.8653647964826</v>
       </c>
       <c r="AZ13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>999.76671114851774</v>
       </c>
       <c r="BA13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>989.76904403703259</v>
       </c>
       <c r="BB13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>979.87135359666229</v>
       </c>
       <c r="BC13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>970.07264006069568</v>
       </c>
       <c r="BD13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>960.37191366008869</v>
       </c>
       <c r="BE13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>950.76819452348775</v>
       </c>
       <c r="BF13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>941.26051257825281</v>
       </c>
       <c r="BG13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>931.84790745247028</v>
       </c>
       <c r="BH13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>922.52942837794558</v>
       </c>
       <c r="BI13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>913.3041340941661</v>
       </c>
       <c r="BJ13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>904.17109275322446</v>
       </c>
       <c r="BK13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>895.12938182569223</v>
       </c>
       <c r="BL13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>886.17808800743535</v>
       </c>
       <c r="BM13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>877.31630712736103</v>
       </c>
       <c r="BN13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>868.54314405608739</v>
       </c>
       <c r="BO13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>859.85771261552645</v>
       </c>
       <c r="BP13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>851.25913548937115</v>
       </c>
       <c r="BQ13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>842.7465441344774</v>
       </c>
       <c r="BR13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>834.31907869313261</v>
       </c>
       <c r="BS13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>825.97588790620125</v>
       </c>
       <c r="BT13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>817.71612902713923</v>
       </c>
       <c r="BU13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>809.53896773686779</v>
       </c>
       <c r="BV13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>801.44357805949915</v>
       </c>
       <c r="BW13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>793.42914227890412</v>
       </c>
       <c r="BX13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>785.49485085611502</v>
       </c>
       <c r="BY13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>777.63990234755386</v>
       </c>
       <c r="BZ13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>769.86350332407835</v>
       </c>
       <c r="CA13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>762.1648682908376</v>
       </c>
       <c r="CB13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>754.54321960792925</v>
       </c>
       <c r="CC13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>746.99778741184991</v>
       </c>
       <c r="CD13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>739.5278095377314</v>
       </c>
       <c r="CE13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>732.13253144235409</v>
       </c>
       <c r="CF13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>724.81120612793052</v>
       </c>
       <c r="CG13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>717.56309406665116</v>
       </c>
       <c r="CH13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>710.3874631259846</v>
       </c>
       <c r="CI13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>703.28358849472477</v>
       </c>
       <c r="CJ13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>696.25075260977746</v>
       </c>
       <c r="CK13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>689.28824508367973</v>
       </c>
       <c r="CL13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>682.39536263284288</v>
       </c>
       <c r="CM13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>675.57140900651439</v>
       </c>
       <c r="CN13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>668.81569491644927</v>
       </c>
       <c r="CO13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>662.12753796728475</v>
       </c>
       <c r="CP13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>655.5062625876119</v>
       </c>
       <c r="CQ13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>648.95119996173582</v>
       </c>
       <c r="CR13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>642.4616879621185</v>
       </c>
       <c r="CS13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>636.03707108249728</v>
       </c>
       <c r="CT13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>629.67670037167227</v>
       </c>
       <c r="CU13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>623.37993336795557</v>
       </c>
       <c r="CV13" s="4">
-        <f t="shared" si="9"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>617.14613403427597</v>
       </c>
       <c r="CW13" s="4">
-        <f t="shared" ref="CW13:DE13" si="10">CV13*(1+$X$33)</f>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="10"/>
+        <v>610.97467269393326</v>
       </c>
       <c r="CX13" s="4">
         <f t="shared" si="10"/>
-        <v>1106.0974467561564</v>
+        <v>604.86492596699395</v>
       </c>
       <c r="CY13" s="4">
         <f t="shared" si="10"/>
-        <v>1106.0974467561564</v>
+        <v>598.81627670732405</v>
       </c>
       <c r="CZ13" s="4">
-        <f t="shared" si="10"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" ref="CZ13:DH13" si="11">CY13*(1+$AA$33)</f>
+        <v>592.82811394025077</v>
       </c>
       <c r="DA13" s="4">
-        <f t="shared" si="10"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="11"/>
+        <v>586.89983280084823</v>
       </c>
       <c r="DB13" s="4">
-        <f t="shared" si="10"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="11"/>
+        <v>581.03083447283973</v>
       </c>
       <c r="DC13" s="4">
-        <f t="shared" si="10"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="11"/>
+        <v>575.22052612811137</v>
       </c>
       <c r="DD13" s="4">
-        <f t="shared" si="10"/>
-        <v>1106.0974467561564</v>
+        <f t="shared" si="11"/>
+        <v>569.46832086683025</v>
       </c>
       <c r="DE13" s="4">
-        <f t="shared" si="10"/>
-        <v>1106.0974467561564</v>
-      </c>
-    </row>
-    <row r="14" spans="1:109" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="11"/>
+        <v>563.77363765816199</v>
+      </c>
+      <c r="DF13" s="4">
+        <f t="shared" si="11"/>
+        <v>558.13590128158035</v>
+      </c>
+      <c r="DG13" s="4">
+        <f t="shared" si="11"/>
+        <v>552.55454226876452</v>
+      </c>
+      <c r="DH13" s="4">
+        <f t="shared" si="11"/>
+        <v>547.02899684607689</v>
+      </c>
+    </row>
+    <row r="14" spans="1:112" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>16</v>
       </c>
@@ -2160,28 +2361,39 @@
       <c r="R14" s="6">
         <v>76.933999999999997</v>
       </c>
-      <c r="Y14" s="25">
-        <f>(Z13-Y13)/Y13</f>
+      <c r="S14" s="6">
+        <v>46.122</v>
+      </c>
+      <c r="T14" s="6">
+        <f>53.723</f>
+        <v>53.722999999999999</v>
+      </c>
+      <c r="U14" s="6">
+        <f>59.998</f>
+        <v>59.997999999999998</v>
+      </c>
+      <c r="AC14" s="25">
+        <f>(AC13-AB13)/AB13</f>
         <v>0.32317364093065015</v>
       </c>
-      <c r="Z14" s="25">
-        <f>(AA13-Z13)/Z13</f>
+      <c r="AD14" s="25">
+        <f>(AD13-AC13)/AC13</f>
         <v>0.25777725929382483</v>
       </c>
-      <c r="AA14" s="25">
-        <f>(AB13-AA13)/AA13</f>
+      <c r="AE14" s="25">
+        <f>(AE13-AD13)/AD13</f>
         <v>0.1687151309040319</v>
       </c>
-      <c r="AB14" s="25">
-        <f>(AC13-AB13)/AB13</f>
-        <v>0.14999999999999986</v>
-      </c>
-      <c r="AC14" s="25">
-        <f>(AD13-AC13)/AC13</f>
-        <v>0.14999999999999991</v>
-      </c>
-    </row>
-    <row r="15" spans="1:109" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AF14" s="25">
+        <f>(AF13-AE13)/AE13</f>
+        <v>-7.3148911916849316E-2</v>
+      </c>
+      <c r="AG14" s="25">
+        <f>(AG13-AF13)/AF13</f>
+        <v>0.19999999999999993</v>
+      </c>
+    </row>
+    <row r="15" spans="1:112" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -2194,43 +2406,396 @@
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
       <c r="J15" s="23">
-        <f t="shared" ref="J15:R15" si="11">J13-J14</f>
+        <f t="shared" ref="J15:U15" si="12">J13-J14</f>
         <v>20.613</v>
       </c>
       <c r="K15" s="23">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>21.120999999999988</v>
       </c>
       <c r="L15" s="23">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>21.408000000000015</v>
       </c>
       <c r="M15" s="23">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>26.15100000000001</v>
       </c>
       <c r="N15" s="23">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>23.193000000000012</v>
       </c>
       <c r="O15" s="23">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>20.53</v>
       </c>
       <c r="P15" s="23">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>28.185999999999993</v>
       </c>
       <c r="Q15" s="23">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>26.400999999999996</v>
       </c>
       <c r="R15" s="23">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>28.562999999999988</v>
       </c>
-    </row>
-    <row r="16" spans="1:109" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S15" s="23">
+        <f t="shared" si="12"/>
+        <v>32.028000000000006</v>
+      </c>
+      <c r="T15" s="23">
+        <f t="shared" si="12"/>
+        <v>43.030999999999992</v>
+      </c>
+      <c r="U15" s="23">
+        <f t="shared" si="12"/>
+        <v>45.006999999999998</v>
+      </c>
+      <c r="AA15" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB15" s="4">
+        <v>213.786</v>
+      </c>
+      <c r="AC15" s="4">
+        <v>282.87599999999998</v>
+      </c>
+      <c r="AD15" s="4">
+        <f>SUM(J12:M12)</f>
+        <v>262.34699999999998</v>
+      </c>
+      <c r="AE15" s="4">
+        <f>SUM(N12:Q12)</f>
+        <v>276.714</v>
+      </c>
+      <c r="AF15" s="4">
+        <f>SUM(R12:U12)</f>
+        <v>349.98199999999997</v>
+      </c>
+      <c r="AG15" s="4">
+        <f t="shared" si="9"/>
+        <v>419.97839999999997</v>
+      </c>
+      <c r="AH15" s="4">
+        <f t="shared" ref="AH15" si="13">AG15*(1+$AA$32)</f>
+        <v>503.97407999999996</v>
+      </c>
+      <c r="AI15" s="4">
+        <f t="shared" ref="AI15" si="14">AH15*(1+$AA$32)</f>
+        <v>604.76889599999993</v>
+      </c>
+      <c r="AJ15" s="4">
+        <f t="shared" ref="AJ15" si="15">AI15*(1+$AA$32)</f>
+        <v>725.72267519999991</v>
+      </c>
+      <c r="AK15" s="4">
+        <f t="shared" ref="AK15" si="16">AJ15*(1+$AA$32)</f>
+        <v>870.86721023999985</v>
+      </c>
+      <c r="AL15" s="4">
+        <f t="shared" ref="AL15" si="17">AK15*(1+$AA$32)</f>
+        <v>1045.0406522879998</v>
+      </c>
+      <c r="AM15" s="4">
+        <f>AL15*(1+$AA$33)</f>
+        <v>1034.5902457651198</v>
+      </c>
+      <c r="AN15" s="4">
+        <f t="shared" ref="AN15:CY15" si="18">AM15*(1+$AA$33)</f>
+        <v>1024.2443433074686</v>
+      </c>
+      <c r="AO15" s="4">
+        <f t="shared" si="18"/>
+        <v>1014.001899874394</v>
+      </c>
+      <c r="AP15" s="4">
+        <f t="shared" si="18"/>
+        <v>1003.8618808756501</v>
+      </c>
+      <c r="AQ15" s="4">
+        <f t="shared" si="18"/>
+        <v>993.82326206689356</v>
+      </c>
+      <c r="AR15" s="4">
+        <f t="shared" si="18"/>
+        <v>983.88502944622462</v>
+      </c>
+      <c r="AS15" s="4">
+        <f t="shared" si="18"/>
+        <v>974.04617915176232</v>
+      </c>
+      <c r="AT15" s="4">
+        <f t="shared" si="18"/>
+        <v>964.30571736024467</v>
+      </c>
+      <c r="AU15" s="4">
+        <f t="shared" si="18"/>
+        <v>954.66266018664226</v>
+      </c>
+      <c r="AV15" s="4">
+        <f t="shared" si="18"/>
+        <v>945.11603358477578</v>
+      </c>
+      <c r="AW15" s="4">
+        <f t="shared" si="18"/>
+        <v>935.66487324892796</v>
+      </c>
+      <c r="AX15" s="4">
+        <f t="shared" si="18"/>
+        <v>926.30822451643871</v>
+      </c>
+      <c r="AY15" s="4">
+        <f t="shared" si="18"/>
+        <v>917.04514227127436</v>
+      </c>
+      <c r="AZ15" s="4">
+        <f t="shared" si="18"/>
+        <v>907.87469084856161</v>
+      </c>
+      <c r="BA15" s="4">
+        <f t="shared" si="18"/>
+        <v>898.79594394007597</v>
+      </c>
+      <c r="BB15" s="4">
+        <f t="shared" si="18"/>
+        <v>889.80798450067516</v>
+      </c>
+      <c r="BC15" s="4">
+        <f t="shared" si="18"/>
+        <v>880.90990465566836</v>
+      </c>
+      <c r="BD15" s="4">
+        <f t="shared" si="18"/>
+        <v>872.10080560911172</v>
+      </c>
+      <c r="BE15" s="4">
+        <f t="shared" si="18"/>
+        <v>863.37979755302058</v>
+      </c>
+      <c r="BF15" s="4">
+        <f t="shared" si="18"/>
+        <v>854.74599957749035</v>
+      </c>
+      <c r="BG15" s="4">
+        <f t="shared" si="18"/>
+        <v>846.19853958171541</v>
+      </c>
+      <c r="BH15" s="4">
+        <f t="shared" si="18"/>
+        <v>837.73655418589829</v>
+      </c>
+      <c r="BI15" s="4">
+        <f t="shared" si="18"/>
+        <v>829.35918864403925</v>
+      </c>
+      <c r="BJ15" s="4">
+        <f t="shared" si="18"/>
+        <v>821.06559675759888</v>
+      </c>
+      <c r="BK15" s="4">
+        <f t="shared" si="18"/>
+        <v>812.85494079002285</v>
+      </c>
+      <c r="BL15" s="4">
+        <f t="shared" si="18"/>
+        <v>804.72639138212264</v>
+      </c>
+      <c r="BM15" s="4">
+        <f t="shared" si="18"/>
+        <v>796.67912746830143</v>
+      </c>
+      <c r="BN15" s="4">
+        <f t="shared" si="18"/>
+        <v>788.7123361936184</v>
+      </c>
+      <c r="BO15" s="4">
+        <f t="shared" si="18"/>
+        <v>780.82521283168217</v>
+      </c>
+      <c r="BP15" s="4">
+        <f t="shared" si="18"/>
+        <v>773.01696070336538</v>
+      </c>
+      <c r="BQ15" s="4">
+        <f t="shared" si="18"/>
+        <v>765.28679109633174</v>
+      </c>
+      <c r="BR15" s="4">
+        <f t="shared" si="18"/>
+        <v>757.63392318536842</v>
+      </c>
+      <c r="BS15" s="4">
+        <f t="shared" si="18"/>
+        <v>750.05758395351472</v>
+      </c>
+      <c r="BT15" s="4">
+        <f t="shared" si="18"/>
+        <v>742.55700811397958</v>
+      </c>
+      <c r="BU15" s="4">
+        <f t="shared" si="18"/>
+        <v>735.13143803283981</v>
+      </c>
+      <c r="BV15" s="4">
+        <f t="shared" si="18"/>
+        <v>727.78012365251141</v>
+      </c>
+      <c r="BW15" s="4">
+        <f t="shared" si="18"/>
+        <v>720.50232241598633</v>
+      </c>
+      <c r="BX15" s="4">
+        <f t="shared" si="18"/>
+        <v>713.29729919182648</v>
+      </c>
+      <c r="BY15" s="4">
+        <f t="shared" si="18"/>
+        <v>706.16432619990826</v>
+      </c>
+      <c r="BZ15" s="4">
+        <f t="shared" si="18"/>
+        <v>699.10268293790921</v>
+      </c>
+      <c r="CA15" s="4">
+        <f t="shared" si="18"/>
+        <v>692.11165610853016</v>
+      </c>
+      <c r="CB15" s="4">
+        <f t="shared" si="18"/>
+        <v>685.19053954744481</v>
+      </c>
+      <c r="CC15" s="4">
+        <f t="shared" si="18"/>
+        <v>678.33863415197038</v>
+      </c>
+      <c r="CD15" s="4">
+        <f t="shared" si="18"/>
+        <v>671.55524781045062</v>
+      </c>
+      <c r="CE15" s="4">
+        <f t="shared" si="18"/>
+        <v>664.83969533234608</v>
+      </c>
+      <c r="CF15" s="4">
+        <f t="shared" si="18"/>
+        <v>658.19129837902267</v>
+      </c>
+      <c r="CG15" s="4">
+        <f t="shared" si="18"/>
+        <v>651.60938539523238</v>
+      </c>
+      <c r="CH15" s="4">
+        <f t="shared" si="18"/>
+        <v>645.09329154128</v>
+      </c>
+      <c r="CI15" s="4">
+        <f t="shared" si="18"/>
+        <v>638.64235862586725</v>
+      </c>
+      <c r="CJ15" s="4">
+        <f t="shared" si="18"/>
+        <v>632.25593503960852</v>
+      </c>
+      <c r="CK15" s="4">
+        <f t="shared" si="18"/>
+        <v>625.93337568921243</v>
+      </c>
+      <c r="CL15" s="4">
+        <f t="shared" si="18"/>
+        <v>619.67404193232028</v>
+      </c>
+      <c r="CM15" s="4">
+        <f t="shared" si="18"/>
+        <v>613.47730151299709</v>
+      </c>
+      <c r="CN15" s="4">
+        <f t="shared" si="18"/>
+        <v>607.34252849786708</v>
+      </c>
+      <c r="CO15" s="4">
+        <f t="shared" si="18"/>
+        <v>601.26910321288835</v>
+      </c>
+      <c r="CP15" s="4">
+        <f t="shared" si="18"/>
+        <v>595.25641218075941</v>
+      </c>
+      <c r="CQ15" s="4">
+        <f t="shared" si="18"/>
+        <v>589.30384805895176</v>
+      </c>
+      <c r="CR15" s="4">
+        <f t="shared" si="18"/>
+        <v>583.4108095783622</v>
+      </c>
+      <c r="CS15" s="4">
+        <f t="shared" si="18"/>
+        <v>577.57670148257853</v>
+      </c>
+      <c r="CT15" s="4">
+        <f t="shared" si="18"/>
+        <v>571.80093446775277</v>
+      </c>
+      <c r="CU15" s="4">
+        <f t="shared" si="18"/>
+        <v>566.08292512307526</v>
+      </c>
+      <c r="CV15" s="4">
+        <f t="shared" si="18"/>
+        <v>560.42209587184448</v>
+      </c>
+      <c r="CW15" s="4">
+        <f t="shared" si="18"/>
+        <v>554.81787491312605</v>
+      </c>
+      <c r="CX15" s="4">
+        <f t="shared" si="18"/>
+        <v>549.26969616399481</v>
+      </c>
+      <c r="CY15" s="4">
+        <f t="shared" si="18"/>
+        <v>543.77699920235489</v>
+      </c>
+      <c r="CZ15" s="4">
+        <f t="shared" ref="CZ15:DH15" si="19">CY15*(1+$AA$33)</f>
+        <v>538.33922921033138</v>
+      </c>
+      <c r="DA15" s="4">
+        <f t="shared" si="19"/>
+        <v>532.9558369182281</v>
+      </c>
+      <c r="DB15" s="4">
+        <f t="shared" si="19"/>
+        <v>527.62627854904576</v>
+      </c>
+      <c r="DC15" s="4">
+        <f t="shared" si="19"/>
+        <v>522.35001576355535</v>
+      </c>
+      <c r="DD15" s="4">
+        <f t="shared" si="19"/>
+        <v>517.12651560591974</v>
+      </c>
+      <c r="DE15" s="4">
+        <f t="shared" si="19"/>
+        <v>511.95525044986056</v>
+      </c>
+      <c r="DF15" s="4">
+        <f t="shared" si="19"/>
+        <v>506.83569794536197</v>
+      </c>
+      <c r="DG15" s="4">
+        <f t="shared" si="19"/>
+        <v>501.76734096590837</v>
+      </c>
+      <c r="DH15" s="4">
+        <f t="shared" si="19"/>
+        <v>496.74966755624928</v>
+      </c>
+    </row>
+    <row r="16" spans="1:112" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>18</v>
       </c>
@@ -2275,8 +2840,27 @@
         <f>15.768</f>
         <v>15.768000000000001</v>
       </c>
-    </row>
-    <row r="17" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S16" s="6">
+        <f>16.237</f>
+        <v>16.236999999999998</v>
+      </c>
+      <c r="T16" s="6">
+        <v>17.821000000000002</v>
+      </c>
+      <c r="U16" s="6">
+        <v>17.431999999999999</v>
+      </c>
+      <c r="AE16" s="25">
+        <f>(AE15-AD15)/AD15</f>
+        <v>5.4763347779848905E-2</v>
+      </c>
+      <c r="AF16" s="25">
+        <f>(AF15-AE15)/AE15</f>
+        <v>0.26477879688053357</v>
+      </c>
+      <c r="AG16" s="25"/>
+    </row>
+    <row r="17" spans="1:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>47</v>
       </c>
@@ -2318,8 +2902,18 @@
         <f>10.926</f>
         <v>10.926</v>
       </c>
-    </row>
-    <row r="18" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S17" s="6">
+        <f>9.811</f>
+        <v>9.8109999999999999</v>
+      </c>
+      <c r="T17" s="6">
+        <v>10.5</v>
+      </c>
+      <c r="U17" s="6">
+        <v>10.471</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>48</v>
       </c>
@@ -2364,10 +2958,20 @@
         <f>25.608</f>
         <v>25.608000000000001</v>
       </c>
-    </row>
-    <row r="19" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S18" s="6">
+        <f>25.369</f>
+        <v>25.369</v>
+      </c>
+      <c r="T18" s="6">
+        <v>27.352</v>
+      </c>
+      <c r="U18" s="6">
+        <v>31.001999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -2411,8 +3015,20 @@
         <f>0+0.932</f>
         <v>0.93200000000000005</v>
       </c>
-    </row>
-    <row r="20" spans="1:27" s="6" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S19" s="6">
+        <f>-0.6+1.946</f>
+        <v>1.3460000000000001</v>
+      </c>
+      <c r="T19" s="6">
+        <f>2.699+-0.147</f>
+        <v>2.552</v>
+      </c>
+      <c r="U19" s="6">
+        <f>2.875+-0.348</f>
+        <v>2.5270000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" s="6" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
@@ -2425,43 +3041,55 @@
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
       <c r="J20" s="23">
-        <f t="shared" ref="J20:R20" si="12">SUM(J16:J19)</f>
+        <f t="shared" ref="J20:U20" si="20">SUM(J16:J19)</f>
         <v>33.208999999999996</v>
       </c>
       <c r="K20" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>37.22</v>
       </c>
       <c r="L20" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>39.385999999999996</v>
       </c>
       <c r="M20" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>36.467000000000006</v>
       </c>
       <c r="N20" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>37.057000000000002</v>
       </c>
       <c r="O20" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>38.183</v>
       </c>
       <c r="P20" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>41.372999999999998</v>
       </c>
       <c r="Q20" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>41.405999999999999</v>
       </c>
       <c r="R20" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>53.234000000000009</v>
       </c>
-    </row>
-    <row r="21" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S20" s="23">
+        <f t="shared" si="20"/>
+        <v>52.763000000000005</v>
+      </c>
+      <c r="T20" s="23">
+        <f t="shared" si="20"/>
+        <v>58.225000000000001</v>
+      </c>
+      <c r="U20" s="23">
+        <f t="shared" si="20"/>
+        <v>61.432000000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
@@ -2474,43 +3102,55 @@
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
       <c r="J21" s="23">
-        <f t="shared" ref="J21:R21" si="13">J15-J20</f>
+        <f t="shared" ref="J21:U21" si="21">J15-J20</f>
         <v>-12.595999999999997</v>
       </c>
       <c r="K21" s="23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>-16.099000000000011</v>
       </c>
       <c r="L21" s="23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>-17.97799999999998</v>
       </c>
       <c r="M21" s="23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>-10.315999999999995</v>
       </c>
       <c r="N21" s="23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>-13.86399999999999</v>
       </c>
       <c r="O21" s="23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>-17.652999999999999</v>
       </c>
       <c r="P21" s="23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>-13.187000000000005</v>
       </c>
       <c r="Q21" s="23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>-15.005000000000003</v>
       </c>
       <c r="R21" s="23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>-24.671000000000021</v>
       </c>
-    </row>
-    <row r="22" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S21" s="23">
+        <f t="shared" si="21"/>
+        <v>-20.734999999999999</v>
+      </c>
+      <c r="T21" s="23">
+        <f t="shared" si="21"/>
+        <v>-15.19400000000001</v>
+      </c>
+      <c r="U21" s="23">
+        <f t="shared" si="21"/>
+        <v>-16.425000000000004</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>21</v>
       </c>
@@ -2558,8 +3198,20 @@
         <f>-1.708+0.306</f>
         <v>-1.4019999999999999</v>
       </c>
-    </row>
-    <row r="23" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S22" s="6">
+        <f>-1.63</f>
+        <v>-1.63</v>
+      </c>
+      <c r="T22" s="6">
+        <f>-3.417</f>
+        <v>-3.4169999999999998</v>
+      </c>
+      <c r="U22" s="6">
+        <f>-3.412+-6.56+2.856</f>
+        <v>-7.1159999999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>22</v>
       </c>
@@ -2572,43 +3224,55 @@
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
       <c r="J23" s="23">
-        <f t="shared" ref="J23:R23" si="14">J21+J22</f>
+        <f t="shared" ref="J23:U23" si="22">J21+J22</f>
         <v>-15.426999999999996</v>
       </c>
       <c r="K23" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>-18.807000000000009</v>
       </c>
       <c r="L23" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>-20.296999999999979</v>
       </c>
       <c r="M23" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>-12.482999999999995</v>
       </c>
       <c r="N23" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>-15.589999999999989</v>
       </c>
       <c r="O23" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>-19.387999999999998</v>
       </c>
       <c r="P23" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>-15.310000000000006</v>
       </c>
       <c r="Q23" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>-16.784000000000002</v>
       </c>
       <c r="R23" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>-26.073000000000022</v>
       </c>
-    </row>
-    <row r="24" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S23" s="23">
+        <f t="shared" si="22"/>
+        <v>-22.364999999999998</v>
+      </c>
+      <c r="T23" s="23">
+        <f t="shared" si="22"/>
+        <v>-18.611000000000011</v>
+      </c>
+      <c r="U23" s="23">
+        <f t="shared" si="22"/>
+        <v>-23.541000000000004</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>23</v>
       </c>
@@ -2655,8 +3319,20 @@
         <f>7.785</f>
         <v>7.7850000000000001</v>
       </c>
-    </row>
-    <row r="25" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S24" s="6">
+        <f>-0.612</f>
+        <v>-0.61199999999999999</v>
+      </c>
+      <c r="T24" s="6">
+        <f>-0.653</f>
+        <v>-0.65300000000000002</v>
+      </c>
+      <c r="U24" s="6">
+        <f>-1.752</f>
+        <v>-1.752</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>24</v>
       </c>
@@ -2669,43 +3345,55 @@
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
       <c r="J25" s="23">
-        <f t="shared" ref="J25:R25" si="15">J23+J24</f>
+        <f t="shared" ref="J25:U25" si="23">J23+J24</f>
         <v>-15.436999999999996</v>
       </c>
       <c r="K25" s="23">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>-18.84800000000001</v>
       </c>
       <c r="L25" s="23">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>-20.874999999999979</v>
       </c>
       <c r="M25" s="23">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>-13.105999999999995</v>
       </c>
       <c r="N25" s="23">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>-15.904999999999989</v>
       </c>
       <c r="O25" s="23">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>-19.796999999999997</v>
       </c>
       <c r="P25" s="23">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>-15.516000000000005</v>
       </c>
       <c r="Q25" s="23">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>-17.842000000000002</v>
       </c>
       <c r="R25" s="23">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>-18.288000000000022</v>
       </c>
-    </row>
-    <row r="26" spans="1:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S25" s="23">
+        <f t="shared" si="23"/>
+        <v>-22.976999999999997</v>
+      </c>
+      <c r="T25" s="23">
+        <f t="shared" si="23"/>
+        <v>-19.26400000000001</v>
+      </c>
+      <c r="U25" s="23">
+        <f t="shared" si="23"/>
+        <v>-25.293000000000003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>25</v>
       </c>
@@ -2718,43 +3406,55 @@
       <c r="H26" s="9"/>
       <c r="I26" s="9"/>
       <c r="J26" s="23">
-        <f t="shared" ref="J26:R26" si="16">J25/J27</f>
+        <f t="shared" ref="J26:U26" si="24">J25/J27</f>
         <v>-0.57237671486837216</v>
       </c>
       <c r="K26" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>-0.69853976725224265</v>
       </c>
       <c r="L26" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>-0.77001106602729541</v>
       </c>
       <c r="M26" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>-0.48329522826167104</v>
       </c>
       <c r="N26" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>-0.58166325336454028</v>
       </c>
       <c r="O26" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>-0.72365390941989249</v>
       </c>
       <c r="P26" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>-0.56479324403028552</v>
       </c>
       <c r="Q26" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>-0.63794336384439365</v>
       </c>
       <c r="R26" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>-0.61959615124000622</v>
       </c>
-    </row>
-    <row r="27" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S26" s="23">
+        <f t="shared" si="24"/>
+        <v>-0.67549610465970888</v>
+      </c>
+      <c r="T26" s="23">
+        <f t="shared" si="24"/>
+        <v>-0.53712533110274663</v>
+      </c>
+      <c r="U26" s="23">
+        <f t="shared" si="24"/>
+        <v>-0.67997419146705385</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
@@ -2793,33 +3493,56 @@
       <c r="R27" s="6">
         <v>29.515999999999998</v>
       </c>
-    </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="S27" s="6">
+        <f>34.015</f>
+        <v>34.015000000000001</v>
+      </c>
+      <c r="T27" s="6">
+        <f>35.865</f>
+        <v>35.865000000000002</v>
+      </c>
+      <c r="U27" s="6">
+        <v>37.197000000000003</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="37" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N29" s="11">
-        <f>+N12/J12-1</f>
+        <f t="shared" ref="N29:U30" si="25">+N12/J12-1</f>
         <v>0.16548278557591001</v>
       </c>
       <c r="O29" s="11">
-        <f>+O12/K12-1</f>
+        <f t="shared" si="25"/>
         <v>8.3495660033348518E-2</v>
       </c>
       <c r="P29" s="11">
-        <f>+P12/L12-1</f>
+        <f t="shared" si="25"/>
         <v>5.091217649554336E-3</v>
       </c>
       <c r="Q29" s="11">
-        <f>+Q12/M12-1</f>
+        <f t="shared" si="25"/>
         <v>-1.517392958282282E-2</v>
       </c>
       <c r="R29" s="11">
-        <f>+R12/N12-1</f>
+        <f t="shared" si="25"/>
         <v>2.1710603056106281E-2</v>
       </c>
-    </row>
-    <row r="30" spans="1:27" s="12" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="S29" s="11">
+        <f t="shared" si="25"/>
+        <v>0.12399142803722207</v>
+      </c>
+      <c r="T29" s="11">
+        <f t="shared" si="25"/>
+        <v>0.40833466761764758</v>
+      </c>
+      <c r="U29" s="11">
+        <f t="shared" si="25"/>
+        <v>0.50221745350500724</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" s="12" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>27</v>
       </c>
@@ -2836,56 +3559,68 @@
       <c r="L30" s="11"/>
       <c r="M30" s="11"/>
       <c r="N30" s="11">
-        <f>+N13/J13-1</f>
+        <f t="shared" si="25"/>
         <v>0.25100579186647587</v>
       </c>
       <c r="O30" s="11">
-        <f>+O13/K13-1</f>
+        <f t="shared" si="25"/>
         <v>0.18157780310953919</v>
       </c>
       <c r="P30" s="11">
-        <f>+P13/L13-1</f>
+        <f t="shared" si="25"/>
         <v>0.15487188332057711</v>
       </c>
       <c r="Q30" s="11">
-        <f>+Q13/M13-1</f>
+        <f t="shared" si="25"/>
         <v>0.10300051203276994</v>
       </c>
       <c r="R30" s="11">
-        <f>+R13/N13-1</f>
+        <f t="shared" si="25"/>
         <v>5.0379840098768058E-2</v>
       </c>
-    </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="S30" s="11">
+        <f t="shared" si="25"/>
+        <v>-0.22272835773392741</v>
+      </c>
+      <c r="T30" s="11">
+        <f t="shared" si="25"/>
+        <v>-9.6888009408777731E-2</v>
+      </c>
+      <c r="U30" s="11">
+        <f t="shared" si="25"/>
+        <v>-2.5095628922642721E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D31" s="13" t="e">
-        <f t="shared" ref="D31:J31" si="17">+D15/D13</f>
+        <f t="shared" ref="D31:J31" si="26">+D15/D13</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E31" s="13" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F31" s="13" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G31" s="13" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H31" s="13" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I31" s="13" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J31" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="26"/>
         <v>0.2567478358348384</v>
       </c>
       <c r="K31" s="13">
@@ -2893,49 +3628,61 @@
         <v>0.24821078114533499</v>
       </c>
       <c r="L31" s="13">
-        <f t="shared" ref="L31:R31" si="18">+L15/L13</f>
+        <f t="shared" ref="L31:U31" si="27">+L15/L13</f>
         <v>0.23077171839123842</v>
       </c>
       <c r="M31" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="27"/>
         <v>0.26780337941628274</v>
       </c>
       <c r="N31" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="27"/>
         <v>0.23092087577287265</v>
       </c>
       <c r="O31" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="27"/>
         <v>0.20418921069382562</v>
       </c>
       <c r="P31" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="27"/>
         <v>0.2630910821961282</v>
       </c>
       <c r="Q31" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="27"/>
         <v>0.2451164258922271</v>
       </c>
       <c r="R31" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="27"/>
         <v>0.27074703546072393</v>
       </c>
-    </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="W32" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="X32" s="15">
-        <v>0.15</v>
-      </c>
+      <c r="S31" s="13">
+        <f t="shared" si="27"/>
+        <v>0.40982725527831099</v>
+      </c>
+      <c r="T31" s="13">
+        <f t="shared" si="27"/>
+        <v>0.44474647043016308</v>
+      </c>
+      <c r="U31" s="13">
+        <f t="shared" si="27"/>
+        <v>0.42861768487214896</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="Z32" s="14" t="s">
         <v>29</v>
       </c>
       <c r="AA32" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="AC32" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD32" s="15">
         <v>0.1</v>
       </c>
     </row>
-    <row r="33" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -2948,20 +3695,20 @@
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
-      <c r="W33" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="X33" s="17">
-        <v>0</v>
-      </c>
       <c r="Z33" s="16" t="s">
         <v>31</v>
       </c>
       <c r="AA33" s="17">
+        <v>-0.01</v>
+      </c>
+      <c r="AC33" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD33" s="17">
         <v>0.01</v>
       </c>
     </row>
-    <row r="34" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
@@ -2974,20 +3721,20 @@
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
       <c r="M34" s="7"/>
-      <c r="W34" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="X34" s="17">
-        <v>0.15</v>
-      </c>
       <c r="Z34" s="16" t="s">
         <v>32</v>
       </c>
       <c r="AA34" s="17">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC34" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD34" s="17">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
@@ -3000,22 +3747,22 @@
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
       <c r="M35" s="7"/>
-      <c r="W35" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="X35" s="26">
-        <f>NPV(X34,Y13:DE13)</f>
-        <v>4120.6585220078041</v>
-      </c>
       <c r="Z35" s="16" t="s">
         <v>33</v>
       </c>
       <c r="AA35" s="26">
-        <f>NPV(AA34,AA12:DH12)</f>
+        <f>NPV(AA34,AB15:DH15)</f>
+        <v>3509.2663645457556</v>
+      </c>
+      <c r="AC35" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD35" s="26">
+        <f>NPV(AD34,AD12:DK12)</f>
         <v>2774.0440873876159</v>
       </c>
     </row>
-    <row r="36" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
@@ -3029,20 +3776,13 @@
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
       <c r="Q36" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R36" s="6">
         <v>23</v>
       </c>
       <c r="S36" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="W36" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="X36" s="19">
-        <f>$R$27</f>
-        <v>29.515999999999998</v>
+        <v>57</v>
       </c>
       <c r="Z36" s="16" t="s">
         <v>26</v>
@@ -3051,8 +3791,15 @@
         <f>$R$27</f>
         <v>29.515999999999998</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC36" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD36" s="19">
+        <f>$R$27</f>
+        <v>29.515999999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
@@ -3065,22 +3812,22 @@
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
-      <c r="W37" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="X37" s="20">
-        <f>X35/X36</f>
-        <v>139.60762034177409</v>
-      </c>
       <c r="Z37" s="16" t="s">
         <v>34</v>
       </c>
       <c r="AA37" s="20">
         <f>AA35/AA36</f>
+        <v>118.89369713192018</v>
+      </c>
+      <c r="AC37" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD37" s="20">
+        <f>AD35/AD36</f>
         <v>93.984418193102599</v>
       </c>
     </row>
-    <row r="38" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
@@ -3093,22 +3840,22 @@
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
-      <c r="W38" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="X38" s="15">
-        <f>(X37-Main!L5)/Main!L5</f>
-        <v>2.0029602138475817</v>
-      </c>
       <c r="Z38" s="16" t="s">
         <v>35</v>
       </c>
       <c r="AA38" s="15">
         <f>(AA37-Main!L5)/Main!L5</f>
-        <v>1.0216050374941406</v>
-      </c>
-    </row>
-    <row r="39" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>0.72309705988290107</v>
+      </c>
+      <c r="AC38" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD38" s="15">
+        <f>(AD37-Main!L5)/Main!L5</f>
+        <v>0.36209301729134202</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
@@ -3121,22 +3868,22 @@
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
       <c r="M39" s="7"/>
-      <c r="W39" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="X39" s="18">
-        <f>X36*X37</f>
-        <v>4120.6585220078041</v>
-      </c>
       <c r="Z39" s="16" t="s">
         <v>36</v>
       </c>
       <c r="AA39" s="18">
         <f>AA36*AA37</f>
+        <v>3509.2663645457556</v>
+      </c>
+      <c r="AC39" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD39" s="18">
+        <f>AD36*AD37</f>
         <v>2774.0440873876159</v>
       </c>
     </row>
-    <row r="40" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
@@ -3150,7 +3897,7 @@
       <c r="L40" s="7"/>
       <c r="M40" s="7"/>
     </row>
-    <row r="41" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
@@ -3164,7 +3911,7 @@
       <c r="L41" s="7"/>
       <c r="M41" s="7"/>
     </row>
-    <row r="43" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
@@ -3178,7 +3925,7 @@
       <c r="L43" s="7"/>
       <c r="M43" s="7"/>
     </row>
-    <row r="44" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
@@ -3192,7 +3939,7 @@
       <c r="L44" s="7"/>
       <c r="M44" s="7"/>
     </row>
-    <row r="45" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
@@ -3206,7 +3953,7 @@
       <c r="L45" s="7"/>
       <c r="M45" s="7"/>
     </row>
-    <row r="46" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
@@ -3220,7 +3967,7 @@
       <c r="L46" s="7"/>
       <c r="M46" s="7"/>
     </row>
-    <row r="47" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
@@ -3234,7 +3981,7 @@
       <c r="L47" s="7"/>
       <c r="M47" s="7"/>
     </row>
-    <row r="48" spans="2:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
@@ -3446,5 +4193,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/$PAR.xlsx
+++ b/$PAR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffe\Documents\GitHub\martinshkreli-models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD4D5C4-6009-4351-B61A-789FCA30AAB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB09D54-B0E9-4740-A6C8-8CD27E627FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="90" windowWidth="27270" windowHeight="20805" activeTab="1" xr2:uid="{8F193AD5-4822-438A-B757-2B234AE27955}"/>
+    <workbookView xWindow="-15" yWindow="90" windowWidth="19245" windowHeight="20805" activeTab="1" xr2:uid="{8F193AD5-4822-438A-B757-2B234AE27955}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="2" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="83">
   <si>
     <t>FY</t>
   </si>
@@ -272,18 +272,67 @@
   </si>
   <si>
     <t>Rest Rev</t>
+  </si>
+  <si>
+    <t>Discount Rate (r)=Rf​+β×(Rm​−Rf​)+Size Premium+Specific Risk Premium</t>
+  </si>
+  <si>
+    <t>Rf</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Rm - Rf</t>
+  </si>
+  <si>
+    <t>Size Premium</t>
+  </si>
+  <si>
+    <t>1-3%</t>
+  </si>
+  <si>
+    <t>5-6.5%</t>
+  </si>
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Estimated Value</t>
+  </si>
+  <si>
+    <t>Typical Range</t>
+  </si>
+  <si>
+    <t>Specific Risk Prem</t>
+  </si>
+  <si>
+    <t>1-2%</t>
+  </si>
+  <si>
+    <t>Discount rate</t>
+  </si>
+  <si>
+    <t>Growth rate of 2-3% matches or slightly exceeds long-term US GDP growth</t>
+  </si>
+  <si>
+    <t>Bull case 3.5%-4% if will continue to grow and take share in fragmented market</t>
+  </si>
+  <si>
+    <t>Conversative case 1.5%-2%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="171" formatCode="0.0000%"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -329,7 +378,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -339,6 +388,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -373,7 +428,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -443,6 +498,19 @@
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -450,7 +518,35 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -461,6 +557,18 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BB51B890-2FC8-4114-8D37-1B569A044EC6}" name="Table1" displayName="Table1" ref="Z22:AB28" totalsRowShown="0">
+  <autoFilter ref="Z22:AB28" xr:uid="{BB51B890-2FC8-4114-8D37-1B569A044EC6}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{74DABAA3-C917-41B3-A57B-92DBCAE597C3}" name="Component" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{094D8EA8-133C-4AAB-81FA-8255CE427369}" name="Estimated Value" dataDxfId="1" dataCellStyle="Percent"/>
+    <tableColumn id="3" xr3:uid="{E7A06C0F-9517-487E-84D4-B98F995A88FC}" name="Typical Range" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -768,7 +876,7 @@
         <v>41</v>
       </c>
       <c r="L5" s="8">
-        <v>69</v>
+        <v>65.95</v>
       </c>
     </row>
     <row r="6" spans="11:12" x14ac:dyDescent="0.25">
@@ -785,7 +893,7 @@
       </c>
       <c r="L7" s="6">
         <f>+L5*L6</f>
-        <v>2553</v>
+        <v>2440.15</v>
       </c>
     </row>
     <row r="8" spans="11:12" x14ac:dyDescent="0.25">
@@ -810,7 +918,7 @@
       </c>
       <c r="L10" s="6">
         <f>+L7-L8+L9</f>
-        <v>2773.627</v>
+        <v>2660.777</v>
       </c>
     </row>
   </sheetData>
@@ -839,11 +947,13 @@
     <col min="20" max="20" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17.42578125" customWidth="1"/>
+    <col min="27" max="27" width="18.140625" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" customWidth="1"/>
     <col min="29" max="29" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="9.140625" style="39"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:112" x14ac:dyDescent="0.25">
@@ -992,7 +1102,7 @@
         <f t="shared" si="0"/>
         <v>2024</v>
       </c>
-      <c r="AG2">
+      <c r="AG2" s="39">
         <v>2025</v>
       </c>
       <c r="AH2">
@@ -1056,6 +1166,9 @@
       </c>
       <c r="U3" s="23">
         <v>26.047999999999998</v>
+      </c>
+      <c r="V3" s="23">
+        <v>21.843</v>
       </c>
     </row>
     <row r="4" spans="1:112" x14ac:dyDescent="0.25">
@@ -1106,6 +1219,9 @@
       <c r="U4" s="32">
         <v>64.262</v>
       </c>
+      <c r="V4" s="32">
+        <v>68.41</v>
+      </c>
       <c r="X4">
         <f>1.15*Q4</f>
         <v>37.831549999999993</v>
@@ -1161,6 +1277,9 @@
       <c r="U5" s="23">
         <v>14.695</v>
       </c>
+      <c r="V5" s="23">
+        <v>13.606</v>
+      </c>
     </row>
     <row r="6" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -1200,6 +1319,9 @@
         <v>0</v>
       </c>
       <c r="U6" s="23">
+        <v>0</v>
+      </c>
+      <c r="V6" s="23">
         <v>0</v>
       </c>
     </row>
@@ -1220,36 +1342,40 @@
       <c r="L7" s="31"/>
       <c r="M7" s="31"/>
       <c r="N7" s="33">
-        <f>(N4-J4)/J4</f>
+        <f t="shared" ref="N7:V7" si="1">(N4-J4)/J4</f>
         <v>0.31383603476626731</v>
       </c>
       <c r="O7" s="33">
-        <f>(O4-K4)/K4</f>
+        <f t="shared" si="1"/>
         <v>0.31196544276457888</v>
       </c>
       <c r="P7" s="33">
-        <f>(P4-L4)/L4</f>
+        <f t="shared" si="1"/>
         <v>0.24604688120778695</v>
       </c>
       <c r="Q7" s="33">
-        <f>(Q4-M4)/M4</f>
+        <f t="shared" si="1"/>
         <v>0.17876594524867412</v>
       </c>
       <c r="R7" s="33">
-        <f>(R4-N4)/N4</f>
+        <f t="shared" si="1"/>
         <v>0.3723940640085821</v>
       </c>
       <c r="S7" s="33">
-        <f>(S4-O4)/O4</f>
+        <f t="shared" si="1"/>
         <v>0.47741340708547347</v>
       </c>
       <c r="T7" s="33">
-        <f>(T4-P4)/P4</f>
+        <f t="shared" si="1"/>
         <v>0.91018078627682297</v>
       </c>
       <c r="U7" s="33">
-        <f>(U4-Q4)/Q4</f>
+        <f t="shared" si="1"/>
         <v>0.95343040398820567</v>
+      </c>
+      <c r="V7" s="33">
+        <f t="shared" si="1"/>
+        <v>0.7824852132676724</v>
       </c>
     </row>
     <row r="8" spans="1:112" x14ac:dyDescent="0.25">
@@ -1262,45 +1388,49 @@
         <v>8.7620389945971267E-2</v>
       </c>
       <c r="L8" s="27">
-        <f t="shared" ref="L8:U8" si="1">(L4-K4)/K4</f>
+        <f t="shared" ref="L8:T8" si="2">(L4-K4)/K4</f>
         <v>8.7257019438445063E-2</v>
       </c>
       <c r="M8" s="27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.10878029400079457</v>
       </c>
       <c r="N8" s="27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.0424251110792106E-3</v>
       </c>
       <c r="O8" s="27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.6071875558734134E-2</v>
       </c>
       <c r="P8" s="27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.2628736994600276E-2</v>
       </c>
       <c r="Q8" s="27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.8911137327423998E-2</v>
       </c>
       <c r="R8" s="27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.16664133507614676</v>
       </c>
       <c r="S8" s="27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.16918106256025436</v>
       </c>
       <c r="T8" s="27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.33510875378855409</v>
       </c>
       <c r="U8" s="27">
         <f>(U4-T4)/T4</f>
         <v>7.2660201305313088E-2</v>
       </c>
+      <c r="V8" s="27">
+        <f>(V4-U4)/U4</f>
+        <v>6.4548255578724539E-2</v>
+      </c>
       <c r="AC8" s="25">
         <f>(AC13-AB13)/AB13</f>
         <v>0.32317364093065015</v>
@@ -1314,7 +1444,7 @@
         <v>0.1687151309040319</v>
       </c>
       <c r="AF8" s="25"/>
-      <c r="AG8" s="25"/>
+      <c r="AG8" s="40"/>
       <c r="AH8" s="25"/>
       <c r="AI8" s="25"/>
       <c r="AJ8" s="25"/>
@@ -1343,54 +1473,58 @@
       </c>
       <c r="J9" s="27"/>
       <c r="K9" s="27">
-        <f t="shared" ref="K9:U9" si="2">K15/K13</f>
+        <f t="shared" ref="K9:V9" si="3">K15/K13</f>
         <v>0.24821078114533499</v>
       </c>
       <c r="L9" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.23077171839123842</v>
       </c>
       <c r="M9" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.26780337941628274</v>
       </c>
       <c r="N9" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.23092087577287265</v>
       </c>
       <c r="O9" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.20418921069382562</v>
       </c>
       <c r="P9" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.2630910821961282</v>
       </c>
       <c r="Q9" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.2451164258922271</v>
       </c>
       <c r="R9" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.27074703546072393</v>
       </c>
       <c r="S9" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.40982725527831099</v>
       </c>
       <c r="T9" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.44474647043016308</v>
       </c>
       <c r="U9" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.42861768487214896</v>
+      </c>
+      <c r="V9" s="27">
+        <f t="shared" si="3"/>
+        <v>0.46545797667992178</v>
       </c>
       <c r="AC9" s="25"/>
       <c r="AD9" s="25"/>
       <c r="AE9" s="25"/>
       <c r="AF9" s="25"/>
-      <c r="AG9" s="25"/>
+      <c r="AG9" s="40"/>
       <c r="AH9" s="25"/>
       <c r="AI9" s="25"/>
       <c r="AJ9" s="25"/>
@@ -1419,54 +1553,58 @@
       </c>
       <c r="J10" s="22"/>
       <c r="K10" s="27">
-        <f t="shared" ref="K10:U10" si="3">K8+K9</f>
+        <f t="shared" ref="K10:V10" si="4">K8+K9</f>
         <v>0.33583117109130622</v>
       </c>
       <c r="L10" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.31802873782968349</v>
       </c>
       <c r="M10" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.37658367341707732</v>
       </c>
       <c r="N10" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.23296330088395187</v>
       </c>
       <c r="O10" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.29026108625255975</v>
       </c>
       <c r="P10" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.29571981919072848</v>
       </c>
       <c r="Q10" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.29402756321965107</v>
       </c>
       <c r="R10" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.43738837053687069</v>
       </c>
       <c r="S10" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.57900831783856532</v>
       </c>
       <c r="T10" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.77985522421871711</v>
       </c>
       <c r="U10" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.50127788617746205</v>
+      </c>
+      <c r="V10" s="27">
+        <f t="shared" si="4"/>
+        <v>0.53000623225864629</v>
       </c>
       <c r="AC10" s="25"/>
       <c r="AD10" s="25"/>
       <c r="AE10" s="25"/>
       <c r="AF10" s="25"/>
-      <c r="AG10" s="25"/>
+      <c r="AG10" s="40"/>
       <c r="AH10" s="25"/>
       <c r="AI10" s="25"/>
       <c r="AJ10" s="25"/>
@@ -1508,7 +1646,7 @@
         <v>136.9</v>
       </c>
       <c r="AF11" s="25"/>
-      <c r="AG11" s="25"/>
+      <c r="AG11" s="40"/>
       <c r="AH11" s="25"/>
       <c r="AI11" s="25"/>
       <c r="AJ11" s="25"/>
@@ -1536,52 +1674,56 @@
         <v>61</v>
       </c>
       <c r="J12" s="36">
-        <f t="shared" ref="J12:U12" si="4">SUM(J3:J5)</f>
+        <f t="shared" ref="J12:U12" si="5">SUM(J3:J5)</f>
         <v>58.846000000000004</v>
       </c>
       <c r="K12" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>64.170999999999992</v>
       </c>
       <c r="L12" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>68.353000000000009</v>
       </c>
       <c r="M12" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>70.977000000000004</v>
       </c>
       <c r="N12" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>68.584000000000003</v>
       </c>
       <c r="O12" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>69.528999999999996</v>
       </c>
       <c r="P12" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>68.700999999999993</v>
       </c>
       <c r="Q12" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>69.899999999999991</v>
       </c>
       <c r="R12" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>70.072999999999993</v>
       </c>
       <c r="S12" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>78.150000000000006</v>
       </c>
       <c r="T12" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>96.753999999999991</v>
       </c>
       <c r="U12" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>105.005</v>
+      </c>
+      <c r="V12" s="24">
+        <f t="shared" ref="J12:V13" si="6">SUM(V2:V5)</f>
+        <v>103.85899999999999</v>
       </c>
       <c r="AD12" s="38">
         <f>SUM(J12:M12)</f>
@@ -1593,327 +1735,327 @@
       </c>
       <c r="AF12" s="4">
         <f>AE12*(1+$AD$32)</f>
-        <v>304.3854</v>
-      </c>
-      <c r="AG12" s="4">
-        <f t="shared" ref="AG12:AL12" si="5">AF12*(1+$AD$32)</f>
-        <v>334.82394000000005</v>
+        <v>332.05680000000001</v>
+      </c>
+      <c r="AG12" s="41">
+        <f t="shared" ref="AG12:AL12" si="7">AF12*(1+$AD$32)</f>
+        <v>398.46816000000001</v>
       </c>
       <c r="AH12" s="4">
-        <f t="shared" si="5"/>
-        <v>368.30633400000011</v>
+        <f t="shared" si="7"/>
+        <v>478.16179199999999</v>
       </c>
       <c r="AI12" s="4">
-        <f t="shared" si="5"/>
-        <v>405.13696740000017</v>
+        <f t="shared" si="7"/>
+        <v>573.79415039999992</v>
       </c>
       <c r="AJ12" s="4">
-        <f t="shared" si="5"/>
-        <v>445.65066414000023</v>
+        <f t="shared" si="7"/>
+        <v>688.55298047999986</v>
       </c>
       <c r="AK12" s="4">
-        <f t="shared" si="5"/>
-        <v>490.21573055400029</v>
+        <f t="shared" si="7"/>
+        <v>826.26357657599976</v>
       </c>
       <c r="AL12" s="4">
-        <f t="shared" si="5"/>
-        <v>539.23730360940033</v>
+        <f t="shared" si="7"/>
+        <v>991.51629189119967</v>
       </c>
       <c r="AM12" s="4">
         <f>AL12*(1+$AD$33)</f>
-        <v>544.62967664549433</v>
+        <v>1001.4314548101116</v>
       </c>
       <c r="AN12" s="4">
-        <f t="shared" ref="AN12:CY12" si="6">AM12*(1+$AD$33)</f>
-        <v>550.07597341194924</v>
+        <f t="shared" ref="AN12:CY12" si="8">AM12*(1+$AD$33)</f>
+        <v>1011.4457693582127</v>
       </c>
       <c r="AO12" s="4">
-        <f t="shared" si="6"/>
-        <v>555.5767331460687</v>
+        <f t="shared" si="8"/>
+        <v>1021.5602270517949</v>
       </c>
       <c r="AP12" s="4">
-        <f t="shared" si="6"/>
-        <v>561.13250047752945</v>
+        <f t="shared" si="8"/>
+        <v>1031.7758293223128</v>
       </c>
       <c r="AQ12" s="4">
-        <f t="shared" si="6"/>
-        <v>566.74382548230471</v>
+        <f t="shared" si="8"/>
+        <v>1042.0935876155359</v>
       </c>
       <c r="AR12" s="4">
-        <f t="shared" si="6"/>
-        <v>572.4112637371278</v>
+        <f t="shared" si="8"/>
+        <v>1052.5145234916913</v>
       </c>
       <c r="AS12" s="4">
-        <f t="shared" si="6"/>
-        <v>578.13537637449906</v>
+        <f t="shared" si="8"/>
+        <v>1063.0396687266082</v>
       </c>
       <c r="AT12" s="4">
-        <f t="shared" si="6"/>
-        <v>583.91673013824402</v>
+        <f t="shared" si="8"/>
+        <v>1073.6700654138742</v>
       </c>
       <c r="AU12" s="4">
-        <f t="shared" si="6"/>
-        <v>589.75589743962644</v>
+        <f t="shared" si="8"/>
+        <v>1084.406766068013</v>
       </c>
       <c r="AV12" s="4">
-        <f t="shared" si="6"/>
-        <v>595.65345641402268</v>
+        <f t="shared" si="8"/>
+        <v>1095.2508337286931</v>
       </c>
       <c r="AW12" s="4">
-        <f t="shared" si="6"/>
-        <v>601.60999097816295</v>
+        <f t="shared" si="8"/>
+        <v>1106.20334206598</v>
       </c>
       <c r="AX12" s="4">
-        <f t="shared" si="6"/>
-        <v>607.62609088794454</v>
+        <f t="shared" si="8"/>
+        <v>1117.2653754866399</v>
       </c>
       <c r="AY12" s="4">
-        <f t="shared" si="6"/>
-        <v>613.70235179682402</v>
+        <f t="shared" si="8"/>
+        <v>1128.4380292415062</v>
       </c>
       <c r="AZ12" s="4">
-        <f t="shared" si="6"/>
-        <v>619.83937531479228</v>
+        <f t="shared" si="8"/>
+        <v>1139.7224095339213</v>
       </c>
       <c r="BA12" s="4">
-        <f t="shared" si="6"/>
-        <v>626.03776906794019</v>
+        <f t="shared" si="8"/>
+        <v>1151.1196336292605</v>
       </c>
       <c r="BB12" s="4">
-        <f t="shared" si="6"/>
-        <v>632.29814675861962</v>
+        <f t="shared" si="8"/>
+        <v>1162.6308299655532</v>
       </c>
       <c r="BC12" s="4">
-        <f t="shared" si="6"/>
-        <v>638.62112822620577</v>
+        <f t="shared" si="8"/>
+        <v>1174.2571382652088</v>
       </c>
       <c r="BD12" s="4">
-        <f t="shared" si="6"/>
-        <v>645.00733950846779</v>
+        <f t="shared" si="8"/>
+        <v>1185.999709647861</v>
       </c>
       <c r="BE12" s="4">
-        <f t="shared" si="6"/>
-        <v>651.45741290355249</v>
+        <f t="shared" si="8"/>
+        <v>1197.8597067443395</v>
       </c>
       <c r="BF12" s="4">
-        <f t="shared" si="6"/>
-        <v>657.971987032588</v>
+        <f t="shared" si="8"/>
+        <v>1209.8383038117829</v>
       </c>
       <c r="BG12" s="4">
-        <f t="shared" si="6"/>
-        <v>664.55170690291391</v>
+        <f t="shared" si="8"/>
+        <v>1221.9366868499008</v>
       </c>
       <c r="BH12" s="4">
-        <f t="shared" si="6"/>
-        <v>671.197223971943</v>
+        <f t="shared" si="8"/>
+        <v>1234.1560537183998</v>
       </c>
       <c r="BI12" s="4">
-        <f t="shared" si="6"/>
-        <v>677.90919621166245</v>
+        <f t="shared" si="8"/>
+        <v>1246.4976142555838</v>
       </c>
       <c r="BJ12" s="4">
-        <f t="shared" si="6"/>
-        <v>684.68828817377903</v>
+        <f t="shared" si="8"/>
+        <v>1258.9625903981396</v>
       </c>
       <c r="BK12" s="4">
-        <f t="shared" si="6"/>
-        <v>691.5351710555168</v>
+        <f t="shared" si="8"/>
+        <v>1271.552216302121</v>
       </c>
       <c r="BL12" s="4">
-        <f t="shared" si="6"/>
-        <v>698.45052276607203</v>
+        <f t="shared" si="8"/>
+        <v>1284.2677384651422</v>
       </c>
       <c r="BM12" s="4">
-        <f t="shared" si="6"/>
-        <v>705.43502799373277</v>
+        <f t="shared" si="8"/>
+        <v>1297.1104158497935</v>
       </c>
       <c r="BN12" s="4">
-        <f t="shared" si="6"/>
-        <v>712.48937827367013</v>
+        <f t="shared" si="8"/>
+        <v>1310.0815200082914</v>
       </c>
       <c r="BO12" s="4">
-        <f t="shared" si="6"/>
-        <v>719.61427205640689</v>
+        <f t="shared" si="8"/>
+        <v>1323.1823352083743</v>
       </c>
       <c r="BP12" s="4">
-        <f t="shared" si="6"/>
-        <v>726.81041477697102</v>
+        <f t="shared" si="8"/>
+        <v>1336.414158560458</v>
       </c>
       <c r="BQ12" s="4">
-        <f t="shared" si="6"/>
-        <v>734.07851892474071</v>
+        <f t="shared" si="8"/>
+        <v>1349.7783001460625</v>
       </c>
       <c r="BR12" s="4">
-        <f t="shared" si="6"/>
-        <v>741.41930411398812</v>
+        <f t="shared" si="8"/>
+        <v>1363.2760831475232</v>
       </c>
       <c r="BS12" s="4">
-        <f t="shared" si="6"/>
-        <v>748.83349715512804</v>
+        <f t="shared" si="8"/>
+        <v>1376.9088439789984</v>
       </c>
       <c r="BT12" s="4">
-        <f t="shared" si="6"/>
-        <v>756.32183212667928</v>
+        <f t="shared" si="8"/>
+        <v>1390.6779324187885</v>
       </c>
       <c r="BU12" s="4">
-        <f t="shared" si="6"/>
-        <v>763.88505044794613</v>
+        <f t="shared" si="8"/>
+        <v>1404.5847117429764</v>
       </c>
       <c r="BV12" s="4">
-        <f t="shared" si="6"/>
-        <v>771.52390095242561</v>
+        <f t="shared" si="8"/>
+        <v>1418.6305588604062</v>
       </c>
       <c r="BW12" s="4">
-        <f t="shared" si="6"/>
-        <v>779.23913996194983</v>
+        <f t="shared" si="8"/>
+        <v>1432.8168644490102</v>
       </c>
       <c r="BX12" s="4">
-        <f t="shared" si="6"/>
-        <v>787.03153136156936</v>
+        <f t="shared" si="8"/>
+        <v>1447.1450330935002</v>
       </c>
       <c r="BY12" s="4">
-        <f t="shared" si="6"/>
-        <v>794.90184667518508</v>
+        <f t="shared" si="8"/>
+        <v>1461.6164834244353</v>
       </c>
       <c r="BZ12" s="4">
-        <f t="shared" si="6"/>
-        <v>802.85086514193699</v>
+        <f t="shared" si="8"/>
+        <v>1476.2326482586795</v>
       </c>
       <c r="CA12" s="4">
-        <f t="shared" si="6"/>
-        <v>810.87937379335642</v>
+        <f t="shared" si="8"/>
+        <v>1490.9949747412663</v>
       </c>
       <c r="CB12" s="4">
-        <f t="shared" si="6"/>
-        <v>818.98816753128995</v>
+        <f t="shared" si="8"/>
+        <v>1505.9049244886789</v>
       </c>
       <c r="CC12" s="4">
-        <f t="shared" si="6"/>
-        <v>827.17804920660285</v>
+        <f t="shared" si="8"/>
+        <v>1520.9639737335658</v>
       </c>
       <c r="CD12" s="4">
-        <f t="shared" si="6"/>
-        <v>835.44982969866885</v>
+        <f t="shared" si="8"/>
+        <v>1536.1736134709015</v>
       </c>
       <c r="CE12" s="4">
-        <f t="shared" si="6"/>
-        <v>843.80432799565551</v>
+        <f t="shared" si="8"/>
+        <v>1551.5353496056105</v>
       </c>
       <c r="CF12" s="4">
-        <f t="shared" si="6"/>
-        <v>852.24237127561207</v>
+        <f t="shared" si="8"/>
+        <v>1567.0507031016666</v>
       </c>
       <c r="CG12" s="4">
-        <f t="shared" si="6"/>
-        <v>860.76479498836818</v>
+        <f t="shared" si="8"/>
+        <v>1582.7212101326834</v>
       </c>
       <c r="CH12" s="4">
-        <f t="shared" si="6"/>
-        <v>869.37244293825188</v>
+        <f t="shared" si="8"/>
+        <v>1598.5484222340103</v>
       </c>
       <c r="CI12" s="4">
-        <f t="shared" si="6"/>
-        <v>878.06616736763442</v>
+        <f t="shared" si="8"/>
+        <v>1614.5339064563505</v>
       </c>
       <c r="CJ12" s="4">
-        <f t="shared" si="6"/>
-        <v>886.8468290413108</v>
+        <f t="shared" si="8"/>
+        <v>1630.679245520914</v>
       </c>
       <c r="CK12" s="4">
-        <f t="shared" si="6"/>
-        <v>895.71529733172395</v>
+        <f t="shared" si="8"/>
+        <v>1646.9860379761233</v>
       </c>
       <c r="CL12" s="4">
-        <f t="shared" si="6"/>
-        <v>904.67245030504114</v>
+        <f t="shared" si="8"/>
+        <v>1663.4558983558845</v>
       </c>
       <c r="CM12" s="4">
-        <f t="shared" si="6"/>
-        <v>913.71917480809157</v>
+        <f t="shared" si="8"/>
+        <v>1680.0904573394434</v>
       </c>
       <c r="CN12" s="4">
-        <f t="shared" si="6"/>
-        <v>922.85636655617247</v>
+        <f t="shared" si="8"/>
+        <v>1696.891361912838</v>
       </c>
       <c r="CO12" s="4">
-        <f t="shared" si="6"/>
-        <v>932.08493022173423</v>
+        <f t="shared" si="8"/>
+        <v>1713.8602755319664</v>
       </c>
       <c r="CP12" s="4">
-        <f t="shared" si="6"/>
-        <v>941.40577952395154</v>
+        <f t="shared" si="8"/>
+        <v>1730.9988782872861</v>
       </c>
       <c r="CQ12" s="4">
-        <f t="shared" si="6"/>
-        <v>950.81983731919104</v>
+        <f t="shared" si="8"/>
+        <v>1748.3088670701588</v>
       </c>
       <c r="CR12" s="4">
-        <f t="shared" si="6"/>
-        <v>960.32803569238297</v>
+        <f t="shared" si="8"/>
+        <v>1765.7919557408604</v>
       </c>
       <c r="CS12" s="4">
-        <f t="shared" si="6"/>
-        <v>969.93131604930682</v>
+        <f t="shared" si="8"/>
+        <v>1783.449875298269</v>
       </c>
       <c r="CT12" s="4">
-        <f t="shared" si="6"/>
-        <v>979.63062920979985</v>
+        <f t="shared" si="8"/>
+        <v>1801.2843740512517</v>
       </c>
       <c r="CU12" s="4">
-        <f t="shared" si="6"/>
-        <v>989.4269355018979</v>
+        <f t="shared" si="8"/>
+        <v>1819.2972177917643</v>
       </c>
       <c r="CV12" s="4">
-        <f t="shared" si="6"/>
-        <v>999.32120485691689</v>
+        <f t="shared" si="8"/>
+        <v>1837.490189969682</v>
       </c>
       <c r="CW12" s="4">
-        <f t="shared" si="6"/>
-        <v>1009.314416905486</v>
+        <f t="shared" si="8"/>
+        <v>1855.8650918693788</v>
       </c>
       <c r="CX12" s="4">
-        <f t="shared" si="6"/>
-        <v>1019.4075610745409</v>
+        <f t="shared" si="8"/>
+        <v>1874.4237427880726</v>
       </c>
       <c r="CY12" s="4">
-        <f t="shared" si="6"/>
-        <v>1029.6016366852864</v>
+        <f t="shared" si="8"/>
+        <v>1893.1679802159533</v>
       </c>
       <c r="CZ12" s="4">
-        <f t="shared" ref="CZ12:DH12" si="7">CY12*(1+$AD$33)</f>
-        <v>1039.8976530521393</v>
+        <f t="shared" ref="CZ12:DH12" si="9">CY12*(1+$AD$33)</f>
+        <v>1912.0996600181129</v>
       </c>
       <c r="DA12" s="4">
-        <f t="shared" si="7"/>
-        <v>1050.2966295826607</v>
+        <f t="shared" si="9"/>
+        <v>1931.220656618294</v>
       </c>
       <c r="DB12" s="4">
-        <f t="shared" si="7"/>
-        <v>1060.7995958784873</v>
+        <f t="shared" si="9"/>
+        <v>1950.532863184477</v>
       </c>
       <c r="DC12" s="4">
-        <f t="shared" si="7"/>
-        <v>1071.4075918372721</v>
+        <f t="shared" si="9"/>
+        <v>1970.0381918163218</v>
       </c>
       <c r="DD12" s="4">
-        <f t="shared" si="7"/>
-        <v>1082.1216677556449</v>
+        <f t="shared" si="9"/>
+        <v>1989.738573734485</v>
       </c>
       <c r="DE12" s="4">
-        <f t="shared" si="7"/>
-        <v>1092.9428844332015</v>
+        <f t="shared" si="9"/>
+        <v>2009.6359594718299</v>
       </c>
       <c r="DF12" s="4">
-        <f t="shared" si="7"/>
-        <v>1103.8723132775335</v>
+        <f t="shared" si="9"/>
+        <v>2029.7323190665481</v>
       </c>
       <c r="DG12" s="4">
-        <f t="shared" si="7"/>
-        <v>1114.911036410309</v>
+        <f t="shared" si="9"/>
+        <v>2050.0296422572137</v>
       </c>
       <c r="DH12" s="4">
-        <f t="shared" si="7"/>
-        <v>1126.060146774412</v>
+        <f t="shared" si="9"/>
+        <v>2070.529938679786</v>
       </c>
     </row>
     <row r="13" spans="1:112" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -1929,52 +2071,56 @@
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="24">
-        <f t="shared" ref="J13:U13" si="8">SUM(J3:J6)</f>
+        <f t="shared" si="6"/>
         <v>80.284999999999997</v>
       </c>
       <c r="K13" s="24">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>85.092999999999989</v>
       </c>
       <c r="L13" s="24">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>92.76700000000001</v>
       </c>
       <c r="M13" s="24">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>97.65</v>
       </c>
       <c r="N13" s="24">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>100.43700000000001</v>
       </c>
       <c r="O13" s="24">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>100.544</v>
       </c>
       <c r="P13" s="24">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>107.13399999999999</v>
       </c>
       <c r="Q13" s="24">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>107.708</v>
       </c>
       <c r="R13" s="24">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>105.49699999999999</v>
       </c>
       <c r="S13" s="24">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>78.150000000000006</v>
       </c>
       <c r="T13" s="24">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>96.753999999999991</v>
       </c>
       <c r="U13" s="24">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>105.005</v>
+      </c>
+      <c r="V13" s="24">
+        <f t="shared" si="6"/>
+        <v>103.85899999999999</v>
       </c>
       <c r="AB13" s="4">
         <v>213.786</v>
@@ -1994,325 +2140,325 @@
         <f>SUM(R13:U13)</f>
         <v>385.40599999999995</v>
       </c>
-      <c r="AG13" s="4">
-        <f t="shared" ref="AF13:AL15" si="9">AF13*(1+$AA$32)</f>
-        <v>462.48719999999992</v>
+      <c r="AG13" s="41">
+        <f t="shared" ref="AG13:AL15" si="10">AF13*(1+$AA$32)</f>
+        <v>501.02779999999996</v>
       </c>
       <c r="AH13" s="4">
-        <f t="shared" si="9"/>
-        <v>554.9846399999999</v>
+        <f t="shared" si="10"/>
+        <v>651.33614</v>
       </c>
       <c r="AI13" s="4">
-        <f t="shared" si="9"/>
-        <v>665.98156799999981</v>
+        <f t="shared" si="10"/>
+        <v>846.73698200000001</v>
       </c>
       <c r="AJ13" s="4">
-        <f t="shared" si="9"/>
-        <v>799.17788159999975</v>
+        <f t="shared" si="10"/>
+        <v>1100.7580766000001</v>
       </c>
       <c r="AK13" s="4">
-        <f t="shared" si="9"/>
-        <v>959.01345791999961</v>
+        <f t="shared" si="10"/>
+        <v>1430.9854995800001</v>
       </c>
       <c r="AL13" s="4">
-        <f t="shared" si="9"/>
-        <v>1150.8161495039994</v>
+        <f t="shared" si="10"/>
+        <v>1860.2811494540001</v>
       </c>
       <c r="AM13" s="4">
         <f>AL13*(1+$AA$33)</f>
-        <v>1139.3079880089595</v>
+        <v>1897.4867724430801</v>
       </c>
       <c r="AN13" s="4">
-        <f t="shared" ref="AN13:CY13" si="10">AM13*(1+$AA$33)</f>
-        <v>1127.9149081288699</v>
+        <f t="shared" ref="AN13:CY13" si="11">AM13*(1+$AA$33)</f>
+        <v>1935.4365078919418</v>
       </c>
       <c r="AO13" s="4">
-        <f t="shared" si="10"/>
-        <v>1116.6357590475811</v>
+        <f t="shared" si="11"/>
+        <v>1974.1452380497806</v>
       </c>
       <c r="AP13" s="4">
-        <f t="shared" si="10"/>
-        <v>1105.4694014571053</v>
+        <f t="shared" si="11"/>
+        <v>2013.6281428107761</v>
       </c>
       <c r="AQ13" s="4">
-        <f t="shared" si="10"/>
-        <v>1094.4147074425341</v>
+        <f t="shared" si="11"/>
+        <v>2053.9007056669916</v>
       </c>
       <c r="AR13" s="4">
-        <f t="shared" si="10"/>
-        <v>1083.4705603681089</v>
+        <f t="shared" si="11"/>
+        <v>2094.9787197803316</v>
       </c>
       <c r="AS13" s="4">
-        <f t="shared" si="10"/>
-        <v>1072.6358547644277</v>
+        <f t="shared" si="11"/>
+        <v>2136.8782941759382</v>
       </c>
       <c r="AT13" s="4">
-        <f t="shared" si="10"/>
-        <v>1061.9094962167833</v>
+        <f t="shared" si="11"/>
+        <v>2179.6158600594572</v>
       </c>
       <c r="AU13" s="4">
-        <f t="shared" si="10"/>
-        <v>1051.2904012546155</v>
+        <f t="shared" si="11"/>
+        <v>2223.2081772606462</v>
       </c>
       <c r="AV13" s="4">
-        <f t="shared" si="10"/>
-        <v>1040.7774972420693</v>
+        <f t="shared" si="11"/>
+        <v>2267.6723408058592</v>
       </c>
       <c r="AW13" s="4">
-        <f t="shared" si="10"/>
-        <v>1030.3697222696487</v>
+        <f t="shared" si="11"/>
+        <v>2313.0257876219766</v>
       </c>
       <c r="AX13" s="4">
-        <f t="shared" si="10"/>
-        <v>1020.0660250469522</v>
+        <f t="shared" si="11"/>
+        <v>2359.2863033744161</v>
       </c>
       <c r="AY13" s="4">
-        <f t="shared" si="10"/>
-        <v>1009.8653647964826</v>
+        <f t="shared" si="11"/>
+        <v>2406.4720294419044</v>
       </c>
       <c r="AZ13" s="4">
-        <f t="shared" si="10"/>
-        <v>999.76671114851774</v>
+        <f t="shared" si="11"/>
+        <v>2454.6014700307423</v>
       </c>
       <c r="BA13" s="4">
-        <f t="shared" si="10"/>
-        <v>989.76904403703259</v>
+        <f t="shared" si="11"/>
+        <v>2503.6934994313574</v>
       </c>
       <c r="BB13" s="4">
-        <f t="shared" si="10"/>
-        <v>979.87135359666229</v>
+        <f t="shared" si="11"/>
+        <v>2553.7673694199848</v>
       </c>
       <c r="BC13" s="4">
-        <f t="shared" si="10"/>
-        <v>970.07264006069568</v>
+        <f t="shared" si="11"/>
+        <v>2604.8427168083845</v>
       </c>
       <c r="BD13" s="4">
-        <f t="shared" si="10"/>
-        <v>960.37191366008869</v>
+        <f t="shared" si="11"/>
+        <v>2656.9395711445522</v>
       </c>
       <c r="BE13" s="4">
-        <f t="shared" si="10"/>
-        <v>950.76819452348775</v>
+        <f t="shared" si="11"/>
+        <v>2710.0783625674435</v>
       </c>
       <c r="BF13" s="4">
-        <f t="shared" si="10"/>
-        <v>941.26051257825281</v>
+        <f t="shared" si="11"/>
+        <v>2764.2799298187924</v>
       </c>
       <c r="BG13" s="4">
-        <f t="shared" si="10"/>
-        <v>931.84790745247028</v>
+        <f t="shared" si="11"/>
+        <v>2819.5655284151685</v>
       </c>
       <c r="BH13" s="4">
-        <f t="shared" si="10"/>
-        <v>922.52942837794558</v>
+        <f t="shared" si="11"/>
+        <v>2875.9568389834717</v>
       </c>
       <c r="BI13" s="4">
-        <f t="shared" si="10"/>
-        <v>913.3041340941661</v>
+        <f t="shared" si="11"/>
+        <v>2933.4759757631414</v>
       </c>
       <c r="BJ13" s="4">
-        <f t="shared" si="10"/>
-        <v>904.17109275322446</v>
+        <f t="shared" si="11"/>
+        <v>2992.1454952784043</v>
       </c>
       <c r="BK13" s="4">
-        <f t="shared" si="10"/>
-        <v>895.12938182569223</v>
+        <f t="shared" si="11"/>
+        <v>3051.9884051839722</v>
       </c>
       <c r="BL13" s="4">
-        <f t="shared" si="10"/>
-        <v>886.17808800743535</v>
+        <f t="shared" si="11"/>
+        <v>3113.0281732876515</v>
       </c>
       <c r="BM13" s="4">
-        <f t="shared" si="10"/>
-        <v>877.31630712736103</v>
+        <f t="shared" si="11"/>
+        <v>3175.2887367534045</v>
       </c>
       <c r="BN13" s="4">
-        <f t="shared" si="10"/>
-        <v>868.54314405608739</v>
+        <f t="shared" si="11"/>
+        <v>3238.7945114884728</v>
       </c>
       <c r="BO13" s="4">
-        <f t="shared" si="10"/>
-        <v>859.85771261552645</v>
+        <f t="shared" si="11"/>
+        <v>3303.5704017182425</v>
       </c>
       <c r="BP13" s="4">
-        <f t="shared" si="10"/>
-        <v>851.25913548937115</v>
+        <f t="shared" si="11"/>
+        <v>3369.6418097526075</v>
       </c>
       <c r="BQ13" s="4">
-        <f t="shared" si="10"/>
-        <v>842.7465441344774</v>
+        <f t="shared" si="11"/>
+        <v>3437.0346459476596</v>
       </c>
       <c r="BR13" s="4">
-        <f t="shared" si="10"/>
-        <v>834.31907869313261</v>
+        <f t="shared" si="11"/>
+        <v>3505.7753388666129</v>
       </c>
       <c r="BS13" s="4">
-        <f t="shared" si="10"/>
-        <v>825.97588790620125</v>
+        <f t="shared" si="11"/>
+        <v>3575.8908456439453</v>
       </c>
       <c r="BT13" s="4">
-        <f t="shared" si="10"/>
-        <v>817.71612902713923</v>
+        <f t="shared" si="11"/>
+        <v>3647.4086625568243</v>
       </c>
       <c r="BU13" s="4">
-        <f t="shared" si="10"/>
-        <v>809.53896773686779</v>
+        <f t="shared" si="11"/>
+        <v>3720.356835807961</v>
       </c>
       <c r="BV13" s="4">
-        <f t="shared" si="10"/>
-        <v>801.44357805949915</v>
+        <f t="shared" si="11"/>
+        <v>3794.7639725241202</v>
       </c>
       <c r="BW13" s="4">
-        <f t="shared" si="10"/>
-        <v>793.42914227890412</v>
+        <f t="shared" si="11"/>
+        <v>3870.6592519746027</v>
       </c>
       <c r="BX13" s="4">
-        <f t="shared" si="10"/>
-        <v>785.49485085611502</v>
+        <f t="shared" si="11"/>
+        <v>3948.0724370140947</v>
       </c>
       <c r="BY13" s="4">
-        <f t="shared" si="10"/>
-        <v>777.63990234755386</v>
+        <f t="shared" si="11"/>
+        <v>4027.0338857543766</v>
       </c>
       <c r="BZ13" s="4">
-        <f t="shared" si="10"/>
-        <v>769.86350332407835</v>
+        <f t="shared" si="11"/>
+        <v>4107.574563469464</v>
       </c>
       <c r="CA13" s="4">
-        <f t="shared" si="10"/>
-        <v>762.1648682908376</v>
+        <f t="shared" si="11"/>
+        <v>4189.7260547388532</v>
       </c>
       <c r="CB13" s="4">
-        <f t="shared" si="10"/>
-        <v>754.54321960792925</v>
+        <f t="shared" si="11"/>
+        <v>4273.5205758336306</v>
       </c>
       <c r="CC13" s="4">
-        <f t="shared" si="10"/>
-        <v>746.99778741184991</v>
+        <f t="shared" si="11"/>
+        <v>4358.9909873503029</v>
       </c>
       <c r="CD13" s="4">
-        <f t="shared" si="10"/>
-        <v>739.5278095377314</v>
+        <f t="shared" si="11"/>
+        <v>4446.1708070973091</v>
       </c>
       <c r="CE13" s="4">
-        <f t="shared" si="10"/>
-        <v>732.13253144235409</v>
+        <f t="shared" si="11"/>
+        <v>4535.0942232392554</v>
       </c>
       <c r="CF13" s="4">
-        <f t="shared" si="10"/>
-        <v>724.81120612793052</v>
+        <f t="shared" si="11"/>
+        <v>4625.7961077040409</v>
       </c>
       <c r="CG13" s="4">
-        <f t="shared" si="10"/>
-        <v>717.56309406665116</v>
+        <f t="shared" si="11"/>
+        <v>4718.3120298581216</v>
       </c>
       <c r="CH13" s="4">
-        <f t="shared" si="10"/>
-        <v>710.3874631259846</v>
+        <f t="shared" si="11"/>
+        <v>4812.6782704552843</v>
       </c>
       <c r="CI13" s="4">
-        <f t="shared" si="10"/>
-        <v>703.28358849472477</v>
+        <f t="shared" si="11"/>
+        <v>4908.9318358643905</v>
       </c>
       <c r="CJ13" s="4">
-        <f t="shared" si="10"/>
-        <v>696.25075260977746</v>
+        <f t="shared" si="11"/>
+        <v>5007.1104725816786</v>
       </c>
       <c r="CK13" s="4">
-        <f t="shared" si="10"/>
-        <v>689.28824508367973</v>
+        <f t="shared" si="11"/>
+        <v>5107.2526820333123</v>
       </c>
       <c r="CL13" s="4">
-        <f t="shared" si="10"/>
-        <v>682.39536263284288</v>
+        <f t="shared" si="11"/>
+        <v>5209.3977356739788</v>
       </c>
       <c r="CM13" s="4">
-        <f t="shared" si="10"/>
-        <v>675.57140900651439</v>
+        <f t="shared" si="11"/>
+        <v>5313.5856903874583</v>
       </c>
       <c r="CN13" s="4">
-        <f t="shared" si="10"/>
-        <v>668.81569491644927</v>
+        <f t="shared" si="11"/>
+        <v>5419.8574041952079</v>
       </c>
       <c r="CO13" s="4">
-        <f t="shared" si="10"/>
-        <v>662.12753796728475</v>
+        <f t="shared" si="11"/>
+        <v>5528.2545522791124</v>
       </c>
       <c r="CP13" s="4">
-        <f t="shared" si="10"/>
-        <v>655.5062625876119</v>
+        <f t="shared" si="11"/>
+        <v>5638.8196433246949</v>
       </c>
       <c r="CQ13" s="4">
-        <f t="shared" si="10"/>
-        <v>648.95119996173582</v>
+        <f t="shared" si="11"/>
+        <v>5751.5960361911884</v>
       </c>
       <c r="CR13" s="4">
-        <f t="shared" si="10"/>
-        <v>642.4616879621185</v>
+        <f t="shared" si="11"/>
+        <v>5866.627956915012</v>
       </c>
       <c r="CS13" s="4">
-        <f t="shared" si="10"/>
-        <v>636.03707108249728</v>
+        <f t="shared" si="11"/>
+        <v>5983.9605160533119</v>
       </c>
       <c r="CT13" s="4">
-        <f t="shared" si="10"/>
-        <v>629.67670037167227</v>
+        <f t="shared" si="11"/>
+        <v>6103.6397263743784</v>
       </c>
       <c r="CU13" s="4">
-        <f t="shared" si="10"/>
-        <v>623.37993336795557</v>
+        <f t="shared" si="11"/>
+        <v>6225.7125209018659</v>
       </c>
       <c r="CV13" s="4">
-        <f t="shared" si="10"/>
-        <v>617.14613403427597</v>
+        <f t="shared" si="11"/>
+        <v>6350.2267713199035</v>
       </c>
       <c r="CW13" s="4">
-        <f t="shared" si="10"/>
-        <v>610.97467269393326</v>
+        <f t="shared" si="11"/>
+        <v>6477.2313067463019</v>
       </c>
       <c r="CX13" s="4">
-        <f t="shared" si="10"/>
-        <v>604.86492596699395</v>
+        <f t="shared" si="11"/>
+        <v>6606.7759328812281</v>
       </c>
       <c r="CY13" s="4">
-        <f t="shared" si="10"/>
-        <v>598.81627670732405</v>
+        <f t="shared" si="11"/>
+        <v>6738.9114515388528</v>
       </c>
       <c r="CZ13" s="4">
-        <f t="shared" ref="CZ13:DH13" si="11">CY13*(1+$AA$33)</f>
-        <v>592.82811394025077</v>
+        <f t="shared" ref="CZ13:DH13" si="12">CY13*(1+$AA$33)</f>
+        <v>6873.6896805696297</v>
       </c>
       <c r="DA13" s="4">
-        <f t="shared" si="11"/>
-        <v>586.89983280084823</v>
+        <f t="shared" si="12"/>
+        <v>7011.1634741810221</v>
       </c>
       <c r="DB13" s="4">
-        <f t="shared" si="11"/>
-        <v>581.03083447283973</v>
+        <f t="shared" si="12"/>
+        <v>7151.3867436646424</v>
       </c>
       <c r="DC13" s="4">
-        <f t="shared" si="11"/>
-        <v>575.22052612811137</v>
+        <f t="shared" si="12"/>
+        <v>7294.4144785379358</v>
       </c>
       <c r="DD13" s="4">
-        <f t="shared" si="11"/>
-        <v>569.46832086683025</v>
+        <f t="shared" si="12"/>
+        <v>7440.3027681086951</v>
       </c>
       <c r="DE13" s="4">
-        <f t="shared" si="11"/>
-        <v>563.77363765816199</v>
+        <f t="shared" si="12"/>
+        <v>7589.1088234708695</v>
       </c>
       <c r="DF13" s="4">
-        <f t="shared" si="11"/>
-        <v>558.13590128158035</v>
+        <f t="shared" si="12"/>
+        <v>7740.8909999402867</v>
       </c>
       <c r="DG13" s="4">
-        <f t="shared" si="11"/>
-        <v>552.55454226876452</v>
+        <f t="shared" si="12"/>
+        <v>7895.7088199390928</v>
       </c>
       <c r="DH13" s="4">
-        <f t="shared" si="11"/>
-        <v>547.02899684607689</v>
+        <f t="shared" si="12"/>
+        <v>8053.6229963378746</v>
       </c>
     </row>
     <row r="14" spans="1:112" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2372,6 +2518,9 @@
         <f>59.998</f>
         <v>59.997999999999998</v>
       </c>
+      <c r="V14" s="6">
+        <v>55.517000000000003</v>
+      </c>
       <c r="AC14" s="25">
         <f>(AC13-AB13)/AB13</f>
         <v>0.32317364093065015</v>
@@ -2388,9 +2537,9 @@
         <f>(AF13-AE13)/AE13</f>
         <v>-7.3148911916849316E-2</v>
       </c>
-      <c r="AG14" s="25">
+      <c r="AG14" s="40">
         <f>(AG13-AF13)/AF13</f>
-        <v>0.19999999999999993</v>
+        <v>0.30000000000000004</v>
       </c>
     </row>
     <row r="15" spans="1:112" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2406,52 +2555,56 @@
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
       <c r="J15" s="23">
-        <f t="shared" ref="J15:U15" si="12">J13-J14</f>
+        <f t="shared" ref="J15:V15" si="13">J13-J14</f>
         <v>20.613</v>
       </c>
       <c r="K15" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>21.120999999999988</v>
       </c>
       <c r="L15" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>21.408000000000015</v>
       </c>
       <c r="M15" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>26.15100000000001</v>
       </c>
       <c r="N15" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>23.193000000000012</v>
       </c>
       <c r="O15" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>20.53</v>
       </c>
       <c r="P15" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>28.185999999999993</v>
       </c>
       <c r="Q15" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>26.400999999999996</v>
       </c>
       <c r="R15" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>28.562999999999988</v>
       </c>
       <c r="S15" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>32.028000000000006</v>
       </c>
       <c r="T15" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>43.030999999999992</v>
       </c>
       <c r="U15" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>45.006999999999998</v>
+      </c>
+      <c r="V15" s="23">
+        <f t="shared" si="13"/>
+        <v>48.341999999999992</v>
       </c>
       <c r="AA15" s="6" t="s">
         <v>66</v>
@@ -2474,325 +2627,325 @@
         <f>SUM(R12:U12)</f>
         <v>349.98199999999997</v>
       </c>
-      <c r="AG15" s="4">
-        <f t="shared" si="9"/>
-        <v>419.97839999999997</v>
+      <c r="AG15" s="41">
+        <f t="shared" si="10"/>
+        <v>454.97659999999996</v>
       </c>
       <c r="AH15" s="4">
-        <f t="shared" ref="AH15" si="13">AG15*(1+$AA$32)</f>
-        <v>503.97407999999996</v>
+        <f t="shared" ref="AH15" si="14">AG15*(1+$AA$32)</f>
+        <v>591.46957999999995</v>
       </c>
       <c r="AI15" s="4">
-        <f t="shared" ref="AI15" si="14">AH15*(1+$AA$32)</f>
-        <v>604.76889599999993</v>
+        <f t="shared" ref="AI15" si="15">AH15*(1+$AA$32)</f>
+        <v>768.91045399999996</v>
       </c>
       <c r="AJ15" s="4">
-        <f t="shared" ref="AJ15" si="15">AI15*(1+$AA$32)</f>
-        <v>725.72267519999991</v>
+        <f t="shared" ref="AJ15" si="16">AI15*(1+$AA$32)</f>
+        <v>999.5835902</v>
       </c>
       <c r="AK15" s="4">
-        <f t="shared" ref="AK15" si="16">AJ15*(1+$AA$32)</f>
-        <v>870.86721023999985</v>
+        <f t="shared" ref="AK15" si="17">AJ15*(1+$AA$32)</f>
+        <v>1299.4586672600001</v>
       </c>
       <c r="AL15" s="4">
-        <f t="shared" ref="AL15" si="17">AK15*(1+$AA$32)</f>
-        <v>1045.0406522879998</v>
+        <f t="shared" ref="AL15" si="18">AK15*(1+$AA$32)</f>
+        <v>1689.2962674380001</v>
       </c>
       <c r="AM15" s="4">
         <f>AL15*(1+$AA$33)</f>
-        <v>1034.5902457651198</v>
+        <v>1723.0821927867601</v>
       </c>
       <c r="AN15" s="4">
-        <f t="shared" ref="AN15:CY15" si="18">AM15*(1+$AA$33)</f>
-        <v>1024.2443433074686</v>
+        <f t="shared" ref="AN15:CY15" si="19">AM15*(1+$AA$33)</f>
+        <v>1757.5438366424953</v>
       </c>
       <c r="AO15" s="4">
-        <f t="shared" si="18"/>
-        <v>1014.001899874394</v>
+        <f t="shared" si="19"/>
+        <v>1792.6947133753451</v>
       </c>
       <c r="AP15" s="4">
-        <f t="shared" si="18"/>
-        <v>1003.8618808756501</v>
+        <f t="shared" si="19"/>
+        <v>1828.5486076428522</v>
       </c>
       <c r="AQ15" s="4">
-        <f t="shared" si="18"/>
-        <v>993.82326206689356</v>
+        <f t="shared" si="19"/>
+        <v>1865.1195797957093</v>
       </c>
       <c r="AR15" s="4">
-        <f t="shared" si="18"/>
-        <v>983.88502944622462</v>
+        <f t="shared" si="19"/>
+        <v>1902.4219713916236</v>
       </c>
       <c r="AS15" s="4">
-        <f t="shared" si="18"/>
-        <v>974.04617915176232</v>
+        <f t="shared" si="19"/>
+        <v>1940.4704108194562</v>
       </c>
       <c r="AT15" s="4">
-        <f t="shared" si="18"/>
-        <v>964.30571736024467</v>
+        <f t="shared" si="19"/>
+        <v>1979.2798190358453</v>
       </c>
       <c r="AU15" s="4">
-        <f t="shared" si="18"/>
-        <v>954.66266018664226</v>
+        <f t="shared" si="19"/>
+        <v>2018.8654154165622</v>
       </c>
       <c r="AV15" s="4">
-        <f t="shared" si="18"/>
-        <v>945.11603358477578</v>
+        <f t="shared" si="19"/>
+        <v>2059.2427237248935</v>
       </c>
       <c r="AW15" s="4">
-        <f t="shared" si="18"/>
-        <v>935.66487324892796</v>
+        <f t="shared" si="19"/>
+        <v>2100.4275781993915</v>
       </c>
       <c r="AX15" s="4">
-        <f t="shared" si="18"/>
-        <v>926.30822451643871</v>
+        <f t="shared" si="19"/>
+        <v>2142.4361297633795</v>
       </c>
       <c r="AY15" s="4">
-        <f t="shared" si="18"/>
-        <v>917.04514227127436</v>
+        <f t="shared" si="19"/>
+        <v>2185.2848523586472</v>
       </c>
       <c r="AZ15" s="4">
-        <f t="shared" si="18"/>
-        <v>907.87469084856161</v>
+        <f t="shared" si="19"/>
+        <v>2228.9905494058203</v>
       </c>
       <c r="BA15" s="4">
-        <f t="shared" si="18"/>
-        <v>898.79594394007597</v>
+        <f t="shared" si="19"/>
+        <v>2273.5703603939369</v>
       </c>
       <c r="BB15" s="4">
-        <f t="shared" si="18"/>
-        <v>889.80798450067516</v>
+        <f t="shared" si="19"/>
+        <v>2319.0417676018155</v>
       </c>
       <c r="BC15" s="4">
-        <f t="shared" si="18"/>
-        <v>880.90990465566836</v>
+        <f t="shared" si="19"/>
+        <v>2365.4226029538518</v>
       </c>
       <c r="BD15" s="4">
-        <f t="shared" si="18"/>
-        <v>872.10080560911172</v>
+        <f t="shared" si="19"/>
+        <v>2412.7310550129287</v>
       </c>
       <c r="BE15" s="4">
-        <f t="shared" si="18"/>
-        <v>863.37979755302058</v>
+        <f t="shared" si="19"/>
+        <v>2460.9856761131873</v>
       </c>
       <c r="BF15" s="4">
-        <f t="shared" si="18"/>
-        <v>854.74599957749035</v>
+        <f t="shared" si="19"/>
+        <v>2510.205389635451</v>
       </c>
       <c r="BG15" s="4">
-        <f t="shared" si="18"/>
-        <v>846.19853958171541</v>
+        <f t="shared" si="19"/>
+        <v>2560.4094974281602</v>
       </c>
       <c r="BH15" s="4">
-        <f t="shared" si="18"/>
-        <v>837.73655418589829</v>
+        <f t="shared" si="19"/>
+        <v>2611.6176873767236</v>
       </c>
       <c r="BI15" s="4">
-        <f t="shared" si="18"/>
-        <v>829.35918864403925</v>
+        <f t="shared" si="19"/>
+        <v>2663.850041124258</v>
       </c>
       <c r="BJ15" s="4">
-        <f t="shared" si="18"/>
-        <v>821.06559675759888</v>
+        <f t="shared" si="19"/>
+        <v>2717.1270419467432</v>
       </c>
       <c r="BK15" s="4">
-        <f t="shared" si="18"/>
-        <v>812.85494079002285</v>
+        <f t="shared" si="19"/>
+        <v>2771.4695827856781</v>
       </c>
       <c r="BL15" s="4">
-        <f t="shared" si="18"/>
-        <v>804.72639138212264</v>
+        <f t="shared" si="19"/>
+        <v>2826.8989744413916</v>
       </c>
       <c r="BM15" s="4">
-        <f t="shared" si="18"/>
-        <v>796.67912746830143</v>
+        <f t="shared" si="19"/>
+        <v>2883.4369539302193</v>
       </c>
       <c r="BN15" s="4">
-        <f t="shared" si="18"/>
-        <v>788.7123361936184</v>
+        <f t="shared" si="19"/>
+        <v>2941.1056930088239</v>
       </c>
       <c r="BO15" s="4">
-        <f t="shared" si="18"/>
-        <v>780.82521283168217</v>
+        <f t="shared" si="19"/>
+        <v>2999.9278068690005</v>
       </c>
       <c r="BP15" s="4">
-        <f t="shared" si="18"/>
-        <v>773.01696070336538</v>
+        <f t="shared" si="19"/>
+        <v>3059.9263630063806</v>
       </c>
       <c r="BQ15" s="4">
-        <f t="shared" si="18"/>
-        <v>765.28679109633174</v>
+        <f t="shared" si="19"/>
+        <v>3121.1248902665084</v>
       </c>
       <c r="BR15" s="4">
-        <f t="shared" si="18"/>
-        <v>757.63392318536842</v>
+        <f t="shared" si="19"/>
+        <v>3183.5473880718387</v>
       </c>
       <c r="BS15" s="4">
-        <f t="shared" si="18"/>
-        <v>750.05758395351472</v>
+        <f t="shared" si="19"/>
+        <v>3247.2183358332754</v>
       </c>
       <c r="BT15" s="4">
-        <f t="shared" si="18"/>
-        <v>742.55700811397958</v>
+        <f t="shared" si="19"/>
+        <v>3312.1627025499411</v>
       </c>
       <c r="BU15" s="4">
-        <f t="shared" si="18"/>
-        <v>735.13143803283981</v>
+        <f t="shared" si="19"/>
+        <v>3378.40595660094</v>
       </c>
       <c r="BV15" s="4">
-        <f t="shared" si="18"/>
-        <v>727.78012365251141</v>
+        <f t="shared" si="19"/>
+        <v>3445.9740757329587</v>
       </c>
       <c r="BW15" s="4">
-        <f t="shared" si="18"/>
-        <v>720.50232241598633</v>
+        <f t="shared" si="19"/>
+        <v>3514.893557247618</v>
       </c>
       <c r="BX15" s="4">
-        <f t="shared" si="18"/>
-        <v>713.29729919182648</v>
+        <f t="shared" si="19"/>
+        <v>3585.1914283925703</v>
       </c>
       <c r="BY15" s="4">
-        <f t="shared" si="18"/>
-        <v>706.16432619990826</v>
+        <f t="shared" si="19"/>
+        <v>3656.8952569604216</v>
       </c>
       <c r="BZ15" s="4">
-        <f t="shared" si="18"/>
-        <v>699.10268293790921</v>
+        <f t="shared" si="19"/>
+        <v>3730.0331620996303</v>
       </c>
       <c r="CA15" s="4">
-        <f t="shared" si="18"/>
-        <v>692.11165610853016</v>
+        <f t="shared" si="19"/>
+        <v>3804.6338253416229</v>
       </c>
       <c r="CB15" s="4">
-        <f t="shared" si="18"/>
-        <v>685.19053954744481</v>
+        <f t="shared" si="19"/>
+        <v>3880.7265018484554</v>
       </c>
       <c r="CC15" s="4">
-        <f t="shared" si="18"/>
-        <v>678.33863415197038</v>
+        <f t="shared" si="19"/>
+        <v>3958.3410318854244</v>
       </c>
       <c r="CD15" s="4">
-        <f t="shared" si="18"/>
-        <v>671.55524781045062</v>
+        <f t="shared" si="19"/>
+        <v>4037.5078525231329</v>
       </c>
       <c r="CE15" s="4">
-        <f t="shared" si="18"/>
-        <v>664.83969533234608</v>
+        <f t="shared" si="19"/>
+        <v>4118.2580095735957</v>
       </c>
       <c r="CF15" s="4">
-        <f t="shared" si="18"/>
-        <v>658.19129837902267</v>
+        <f t="shared" si="19"/>
+        <v>4200.6231697650674</v>
       </c>
       <c r="CG15" s="4">
-        <f t="shared" si="18"/>
-        <v>651.60938539523238</v>
+        <f t="shared" si="19"/>
+        <v>4284.6356331603683</v>
       </c>
       <c r="CH15" s="4">
-        <f t="shared" si="18"/>
-        <v>645.09329154128</v>
+        <f t="shared" si="19"/>
+        <v>4370.3283458235755</v>
       </c>
       <c r="CI15" s="4">
-        <f t="shared" si="18"/>
-        <v>638.64235862586725</v>
+        <f t="shared" si="19"/>
+        <v>4457.7349127400475</v>
       </c>
       <c r="CJ15" s="4">
-        <f t="shared" si="18"/>
-        <v>632.25593503960852</v>
+        <f t="shared" si="19"/>
+        <v>4546.8896109948482</v>
       </c>
       <c r="CK15" s="4">
-        <f t="shared" si="18"/>
-        <v>625.93337568921243</v>
+        <f t="shared" si="19"/>
+        <v>4637.8274032147456</v>
       </c>
       <c r="CL15" s="4">
-        <f t="shared" si="18"/>
-        <v>619.67404193232028</v>
+        <f t="shared" si="19"/>
+        <v>4730.5839512790408</v>
       </c>
       <c r="CM15" s="4">
-        <f t="shared" si="18"/>
-        <v>613.47730151299709</v>
+        <f t="shared" si="19"/>
+        <v>4825.1956303046218</v>
       </c>
       <c r="CN15" s="4">
-        <f t="shared" si="18"/>
-        <v>607.34252849786708</v>
+        <f t="shared" si="19"/>
+        <v>4921.6995429107146</v>
       </c>
       <c r="CO15" s="4">
-        <f t="shared" si="18"/>
-        <v>601.26910321288835</v>
+        <f t="shared" si="19"/>
+        <v>5020.1335337689288</v>
       </c>
       <c r="CP15" s="4">
-        <f t="shared" si="18"/>
-        <v>595.25641218075941</v>
+        <f t="shared" si="19"/>
+        <v>5120.5362044443073</v>
       </c>
       <c r="CQ15" s="4">
-        <f t="shared" si="18"/>
-        <v>589.30384805895176</v>
+        <f t="shared" si="19"/>
+        <v>5222.9469285331934</v>
       </c>
       <c r="CR15" s="4">
-        <f t="shared" si="18"/>
-        <v>583.4108095783622</v>
+        <f t="shared" si="19"/>
+        <v>5327.4058671038574</v>
       </c>
       <c r="CS15" s="4">
-        <f t="shared" si="18"/>
-        <v>577.57670148257853</v>
+        <f t="shared" si="19"/>
+        <v>5433.953984445935</v>
       </c>
       <c r="CT15" s="4">
-        <f t="shared" si="18"/>
-        <v>571.80093446775277</v>
+        <f t="shared" si="19"/>
+        <v>5542.6330641348541</v>
       </c>
       <c r="CU15" s="4">
-        <f t="shared" si="18"/>
-        <v>566.08292512307526</v>
+        <f t="shared" si="19"/>
+        <v>5653.4857254175513</v>
       </c>
       <c r="CV15" s="4">
-        <f t="shared" si="18"/>
-        <v>560.42209587184448</v>
+        <f t="shared" si="19"/>
+        <v>5766.5554399259026</v>
       </c>
       <c r="CW15" s="4">
-        <f t="shared" si="18"/>
-        <v>554.81787491312605</v>
+        <f t="shared" si="19"/>
+        <v>5881.8865487244211</v>
       </c>
       <c r="CX15" s="4">
-        <f t="shared" si="18"/>
-        <v>549.26969616399481</v>
+        <f t="shared" si="19"/>
+        <v>5999.5242796989096</v>
       </c>
       <c r="CY15" s="4">
-        <f t="shared" si="18"/>
-        <v>543.77699920235489</v>
+        <f t="shared" si="19"/>
+        <v>6119.5147652928881</v>
       </c>
       <c r="CZ15" s="4">
-        <f t="shared" ref="CZ15:DH15" si="19">CY15*(1+$AA$33)</f>
-        <v>538.33922921033138</v>
+        <f t="shared" ref="CZ15:DH15" si="20">CY15*(1+$AA$33)</f>
+        <v>6241.9050605987459</v>
       </c>
       <c r="DA15" s="4">
-        <f t="shared" si="19"/>
-        <v>532.9558369182281</v>
+        <f t="shared" si="20"/>
+        <v>6366.7431618107212</v>
       </c>
       <c r="DB15" s="4">
-        <f t="shared" si="19"/>
-        <v>527.62627854904576</v>
+        <f t="shared" si="20"/>
+        <v>6494.0780250469361</v>
       </c>
       <c r="DC15" s="4">
-        <f t="shared" si="19"/>
-        <v>522.35001576355535</v>
+        <f t="shared" si="20"/>
+        <v>6623.9595855478747</v>
       </c>
       <c r="DD15" s="4">
-        <f t="shared" si="19"/>
-        <v>517.12651560591974</v>
+        <f t="shared" si="20"/>
+        <v>6756.4387772588325</v>
       </c>
       <c r="DE15" s="4">
-        <f t="shared" si="19"/>
-        <v>511.95525044986056</v>
+        <f t="shared" si="20"/>
+        <v>6891.5675528040092</v>
       </c>
       <c r="DF15" s="4">
-        <f t="shared" si="19"/>
-        <v>506.83569794536197</v>
+        <f t="shared" si="20"/>
+        <v>7029.3989038600894</v>
       </c>
       <c r="DG15" s="4">
-        <f t="shared" si="19"/>
-        <v>501.76734096590837</v>
+        <f t="shared" si="20"/>
+        <v>7169.9868819372914</v>
       </c>
       <c r="DH15" s="4">
-        <f t="shared" si="19"/>
-        <v>496.74966755624928</v>
+        <f t="shared" si="20"/>
+        <v>7313.3866195760374</v>
       </c>
     </row>
     <row r="16" spans="1:112" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2850,6 +3003,9 @@
       <c r="U16" s="6">
         <v>17.431999999999999</v>
       </c>
+      <c r="V16" s="6">
+        <v>19.766999999999999</v>
+      </c>
       <c r="AE16" s="25">
         <f>(AE15-AD15)/AD15</f>
         <v>5.4763347779848905E-2</v>
@@ -2858,9 +3014,9 @@
         <f>(AF15-AE15)/AE15</f>
         <v>0.26477879688053357</v>
       </c>
-      <c r="AG16" s="25"/>
-    </row>
-    <row r="17" spans="1:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AG16" s="40"/>
+    </row>
+    <row r="17" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>47</v>
       </c>
@@ -2912,8 +3068,12 @@
       <c r="U17" s="6">
         <v>10.471</v>
       </c>
-    </row>
-    <row r="18" spans="1:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="V17" s="6">
+        <v>11.782</v>
+      </c>
+      <c r="AG17" s="42"/>
+    </row>
+    <row r="18" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>48</v>
       </c>
@@ -2968,8 +3128,12 @@
       <c r="U18" s="6">
         <v>31.001999999999999</v>
       </c>
-    </row>
-    <row r="19" spans="1:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="V18" s="6">
+        <v>29.283999999999999</v>
+      </c>
+      <c r="AG18" s="42"/>
+    </row>
+    <row r="19" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>65</v>
       </c>
@@ -3027,8 +3191,13 @@
         <f>2.875+-0.348</f>
         <v>2.5270000000000001</v>
       </c>
-    </row>
-    <row r="20" spans="1:30" s="6" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V19" s="6">
+        <f>3.259</f>
+        <v>3.2589999999999999</v>
+      </c>
+      <c r="AG19" s="42"/>
+    </row>
+    <row r="20" spans="1:33" s="6" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
@@ -3041,55 +3210,60 @@
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
       <c r="J20" s="23">
-        <f t="shared" ref="J20:U20" si="20">SUM(J16:J19)</f>
+        <f t="shared" ref="J20:V20" si="21">SUM(J16:J19)</f>
         <v>33.208999999999996</v>
       </c>
       <c r="K20" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>37.22</v>
       </c>
       <c r="L20" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>39.385999999999996</v>
       </c>
       <c r="M20" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>36.467000000000006</v>
       </c>
       <c r="N20" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>37.057000000000002</v>
       </c>
       <c r="O20" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>38.183</v>
       </c>
       <c r="P20" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>41.372999999999998</v>
       </c>
       <c r="Q20" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>41.405999999999999</v>
       </c>
       <c r="R20" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>53.234000000000009</v>
       </c>
       <c r="S20" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>52.763000000000005</v>
       </c>
       <c r="T20" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>58.225000000000001</v>
       </c>
       <c r="U20" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>61.432000000000002</v>
       </c>
-    </row>
-    <row r="21" spans="1:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="V20" s="23">
+        <f t="shared" si="21"/>
+        <v>64.091999999999999</v>
+      </c>
+      <c r="AG20" s="42"/>
+    </row>
+    <row r="21" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
@@ -3102,55 +3276,63 @@
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
       <c r="J21" s="23">
-        <f t="shared" ref="J21:U21" si="21">J15-J20</f>
+        <f t="shared" ref="J21:V21" si="22">J15-J20</f>
         <v>-12.595999999999997</v>
       </c>
       <c r="K21" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-16.099000000000011</v>
       </c>
       <c r="L21" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-17.97799999999998</v>
       </c>
       <c r="M21" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-10.315999999999995</v>
       </c>
       <c r="N21" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-13.86399999999999</v>
       </c>
       <c r="O21" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-17.652999999999999</v>
       </c>
       <c r="P21" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-13.187000000000005</v>
       </c>
       <c r="Q21" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-15.005000000000003</v>
       </c>
       <c r="R21" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-24.671000000000021</v>
       </c>
       <c r="S21" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-20.734999999999999</v>
       </c>
       <c r="T21" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-15.19400000000001</v>
       </c>
       <c r="U21" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-16.425000000000004</v>
       </c>
-    </row>
-    <row r="22" spans="1:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="V21" s="23">
+        <f t="shared" si="22"/>
+        <v>-15.750000000000007</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG21" s="42"/>
+    </row>
+    <row r="22" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>21</v>
       </c>
@@ -3210,8 +3392,22 @@
         <f>-3.412+-6.56+2.856</f>
         <v>-7.1159999999999997</v>
       </c>
-    </row>
-    <row r="23" spans="1:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="V22" s="6">
+        <f>-0.91-1.635-5.791</f>
+        <v>-8.3360000000000003</v>
+      </c>
+      <c r="Z22" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA22" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB22" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG22" s="42"/>
+    </row>
+    <row r="23" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>22</v>
       </c>
@@ -3224,55 +3420,67 @@
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
       <c r="J23" s="23">
-        <f t="shared" ref="J23:U23" si="22">J21+J22</f>
+        <f t="shared" ref="J23:V23" si="23">J21+J22</f>
         <v>-15.426999999999996</v>
       </c>
       <c r="K23" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-18.807000000000009</v>
       </c>
       <c r="L23" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-20.296999999999979</v>
       </c>
       <c r="M23" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-12.482999999999995</v>
       </c>
       <c r="N23" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-15.589999999999989</v>
       </c>
       <c r="O23" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-19.387999999999998</v>
       </c>
       <c r="P23" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-15.310000000000006</v>
       </c>
       <c r="Q23" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-16.784000000000002</v>
       </c>
       <c r="R23" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-26.073000000000022</v>
       </c>
       <c r="S23" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-22.364999999999998</v>
       </c>
       <c r="T23" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-18.611000000000011</v>
       </c>
       <c r="U23" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-23.541000000000004</v>
       </c>
-    </row>
-    <row r="24" spans="1:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="V23" s="23">
+        <f t="shared" si="23"/>
+        <v>-24.086000000000006</v>
+      </c>
+      <c r="Z23" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA23" s="45">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="AB23" s="7"/>
+      <c r="AG23" s="42"/>
+    </row>
+    <row r="24" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>23</v>
       </c>
@@ -3331,8 +3539,19 @@
         <f>-1.752</f>
         <v>-1.752</v>
       </c>
-    </row>
-    <row r="25" spans="1:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="V24" s="6">
+        <v>-1.2809999999999999</v>
+      </c>
+      <c r="Z24" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA24" s="1">
+        <v>1.76</v>
+      </c>
+      <c r="AB24" s="7"/>
+      <c r="AG24" s="42"/>
+    </row>
+    <row r="25" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>24</v>
       </c>
@@ -3345,55 +3564,69 @@
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
       <c r="J25" s="23">
-        <f t="shared" ref="J25:U25" si="23">J23+J24</f>
+        <f t="shared" ref="J25:V25" si="24">J23+J24</f>
         <v>-15.436999999999996</v>
       </c>
       <c r="K25" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-18.84800000000001</v>
       </c>
       <c r="L25" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-20.874999999999979</v>
       </c>
       <c r="M25" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-13.105999999999995</v>
       </c>
       <c r="N25" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-15.904999999999989</v>
       </c>
       <c r="O25" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-19.796999999999997</v>
       </c>
       <c r="P25" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-15.516000000000005</v>
       </c>
       <c r="Q25" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-17.842000000000002</v>
       </c>
       <c r="R25" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-18.288000000000022</v>
       </c>
       <c r="S25" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-22.976999999999997</v>
       </c>
       <c r="T25" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-19.26400000000001</v>
       </c>
       <c r="U25" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-25.293000000000003</v>
       </c>
-    </row>
-    <row r="26" spans="1:30" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="V25" s="23">
+        <f t="shared" si="24"/>
+        <v>-25.367000000000004</v>
+      </c>
+      <c r="Z25" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA25" s="45">
+        <v>5.5E-2</v>
+      </c>
+      <c r="AB25" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG25" s="42"/>
+    </row>
+    <row r="26" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>25</v>
       </c>
@@ -3406,55 +3639,69 @@
       <c r="H26" s="9"/>
       <c r="I26" s="9"/>
       <c r="J26" s="23">
-        <f t="shared" ref="J26:U26" si="24">J25/J27</f>
+        <f t="shared" ref="J26:V26" si="25">J25/J27</f>
         <v>-0.57237671486837216</v>
       </c>
       <c r="K26" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-0.69853976725224265</v>
       </c>
       <c r="L26" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-0.77001106602729541</v>
       </c>
       <c r="M26" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-0.48329522826167104</v>
       </c>
       <c r="N26" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-0.58166325336454028</v>
       </c>
       <c r="O26" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-0.72365390941989249</v>
       </c>
       <c r="P26" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-0.56479324403028552</v>
       </c>
       <c r="Q26" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-0.63794336384439365</v>
       </c>
       <c r="R26" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-0.61959615124000622</v>
       </c>
       <c r="S26" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-0.67549610465970888</v>
       </c>
       <c r="T26" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-0.53712533110274663</v>
       </c>
       <c r="U26" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-0.67997419146705385</v>
       </c>
-    </row>
-    <row r="27" spans="1:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="V26" s="23">
+        <f t="shared" si="25"/>
+        <v>-0.63142828695176001</v>
+      </c>
+      <c r="Z26" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA26" s="45">
+        <v>0.02</v>
+      </c>
+      <c r="AB26" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG26" s="43"/>
+    </row>
+    <row r="27" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
@@ -3504,45 +3751,74 @@
       <c r="U27" s="6">
         <v>37.197000000000003</v>
       </c>
-    </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="V27" s="6">
+        <v>40.173999999999999</v>
+      </c>
+      <c r="Z27" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA27" s="45">
+        <v>0.02</v>
+      </c>
+      <c r="AB27" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG27" s="42"/>
+    </row>
+    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="Z28" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA28" s="46">
+        <f>AA23+AA24*AA25+AA26+AA27</f>
+        <v>0.17879999999999999</v>
+      </c>
+      <c r="AB28" s="1"/>
+    </row>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" s="37" t="s">
         <v>62</v>
       </c>
       <c r="N29" s="11">
-        <f t="shared" ref="N29:U30" si="25">+N12/J12-1</f>
+        <f t="shared" ref="N29:V30" si="26">+N12/J12-1</f>
         <v>0.16548278557591001</v>
       </c>
       <c r="O29" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>8.3495660033348518E-2</v>
       </c>
       <c r="P29" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>5.091217649554336E-3</v>
       </c>
       <c r="Q29" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-1.517392958282282E-2</v>
       </c>
       <c r="R29" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>2.1710603056106281E-2</v>
       </c>
       <c r="S29" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.12399142803722207</v>
       </c>
       <c r="T29" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.40833466761764758</v>
       </c>
       <c r="U29" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.50221745350500724</v>
       </c>
-    </row>
-    <row r="30" spans="1:30" s="12" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="V29" s="11">
+        <f t="shared" si="26"/>
+        <v>0.48215432477559128</v>
+      </c>
+      <c r="AA29" s="1"/>
+      <c r="AB29" s="1"/>
+    </row>
+    <row r="30" spans="1:33" s="12" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>27</v>
       </c>
@@ -3559,68 +3835,73 @@
       <c r="L30" s="11"/>
       <c r="M30" s="11"/>
       <c r="N30" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.25100579186647587</v>
       </c>
       <c r="O30" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.18157780310953919</v>
       </c>
       <c r="P30" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.15487188332057711</v>
       </c>
       <c r="Q30" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.10300051203276994</v>
       </c>
       <c r="R30" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>5.0379840098768058E-2</v>
       </c>
       <c r="S30" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-0.22272835773392741</v>
       </c>
       <c r="T30" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-9.6888009408777731E-2</v>
       </c>
       <c r="U30" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-2.5095628922642721E-2</v>
       </c>
-    </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="V30" s="11">
+        <f t="shared" si="26"/>
+        <v>-1.5526507862782757E-2</v>
+      </c>
+      <c r="AG30" s="44"/>
+    </row>
+    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D31" s="13" t="e">
-        <f t="shared" ref="D31:J31" si="26">+D15/D13</f>
+        <f t="shared" ref="D31:J31" si="27">+D15/D13</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E31" s="13" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F31" s="13" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G31" s="13" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H31" s="13" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I31" s="13" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J31" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.2567478358348384</v>
       </c>
       <c r="K31" s="13">
@@ -3628,61 +3909,65 @@
         <v>0.24821078114533499</v>
       </c>
       <c r="L31" s="13">
-        <f t="shared" ref="L31:U31" si="27">+L15/L13</f>
+        <f t="shared" ref="L31:V31" si="28">+L15/L13</f>
         <v>0.23077171839123842</v>
       </c>
       <c r="M31" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.26780337941628274</v>
       </c>
       <c r="N31" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.23092087577287265</v>
       </c>
       <c r="O31" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.20418921069382562</v>
       </c>
       <c r="P31" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.2630910821961282</v>
       </c>
       <c r="Q31" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.2451164258922271</v>
       </c>
       <c r="R31" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.27074703546072393</v>
       </c>
       <c r="S31" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.40982725527831099</v>
       </c>
       <c r="T31" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.44474647043016308</v>
       </c>
       <c r="U31" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.42861768487214896</v>
       </c>
-    </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="V31" s="13">
+        <f t="shared" si="28"/>
+        <v>0.46545797667992178</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="Z32" s="14" t="s">
         <v>29</v>
       </c>
       <c r="AA32" s="15">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AC32" s="14" t="s">
         <v>29</v>
       </c>
       <c r="AD32" s="15">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="33" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -3699,7 +3984,7 @@
         <v>31</v>
       </c>
       <c r="AA33" s="17">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="AC33" s="16" t="s">
         <v>31</v>
@@ -3707,8 +3992,9 @@
       <c r="AD33" s="17">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AG33" s="42"/>
+    </row>
+    <row r="34" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
@@ -3725,16 +4011,17 @@
         <v>32</v>
       </c>
       <c r="AA34" s="17">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="AC34" s="16" t="s">
         <v>32</v>
       </c>
       <c r="AD34" s="17">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="35" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>0.17</v>
+      </c>
+      <c r="AG34" s="42"/>
+    </row>
+    <row r="35" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
@@ -3752,17 +4039,18 @@
       </c>
       <c r="AA35" s="26">
         <f>NPV(AA34,AB15:DH15)</f>
-        <v>3509.2663645457556</v>
+        <v>4310.3538275688079</v>
       </c>
       <c r="AC35" s="16" t="s">
         <v>33</v>
       </c>
       <c r="AD35" s="26">
         <f>NPV(AD34,AD12:DK12)</f>
-        <v>2774.0440873876159</v>
-      </c>
-    </row>
-    <row r="36" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>3517.6117155492348</v>
+      </c>
+      <c r="AG35" s="42"/>
+    </row>
+    <row r="36" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
@@ -3788,18 +4076,19 @@
         <v>26</v>
       </c>
       <c r="AA36" s="19">
-        <f>$R$27</f>
-        <v>29.515999999999998</v>
+        <f>V27</f>
+        <v>40.173999999999999</v>
       </c>
       <c r="AC36" s="16" t="s">
         <v>26</v>
       </c>
       <c r="AD36" s="19">
-        <f>$R$27</f>
-        <v>29.515999999999998</v>
-      </c>
-    </row>
-    <row r="37" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <f>AA36</f>
+        <v>40.173999999999999</v>
+      </c>
+      <c r="AG36" s="42"/>
+    </row>
+    <row r="37" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
@@ -3817,17 +4106,18 @@
       </c>
       <c r="AA37" s="20">
         <f>AA35/AA36</f>
-        <v>118.89369713192018</v>
+        <v>107.29212494570638</v>
       </c>
       <c r="AC37" s="16" t="s">
         <v>34</v>
       </c>
       <c r="AD37" s="20">
         <f>AD35/AD36</f>
-        <v>93.984418193102599</v>
-      </c>
-    </row>
-    <row r="38" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>87.559409457590348</v>
+      </c>
+      <c r="AG37" s="42"/>
+    </row>
+    <row r="38" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
@@ -3845,17 +4135,18 @@
       </c>
       <c r="AA38" s="15">
         <f>(AA37-Main!L5)/Main!L5</f>
-        <v>0.72309705988290107</v>
+        <v>0.62687073458235587</v>
       </c>
       <c r="AC38" s="16" t="s">
         <v>35</v>
       </c>
       <c r="AD38" s="15">
         <f>(AD37-Main!L5)/Main!L5</f>
-        <v>0.36209301729134202</v>
-      </c>
-    </row>
-    <row r="39" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>0.32766352475497112</v>
+      </c>
+      <c r="AG38" s="42"/>
+    </row>
+    <row r="39" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
@@ -3873,17 +4164,18 @@
       </c>
       <c r="AA39" s="18">
         <f>AA36*AA37</f>
-        <v>3509.2663645457556</v>
+        <v>4310.3538275688079</v>
       </c>
       <c r="AC39" s="16" t="s">
         <v>36</v>
       </c>
       <c r="AD39" s="18">
         <f>AD36*AD37</f>
-        <v>2774.0440873876159</v>
-      </c>
-    </row>
-    <row r="40" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>3517.6117155492348</v>
+      </c>
+      <c r="AG39" s="42"/>
+    </row>
+    <row r="40" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
@@ -3896,8 +4188,9 @@
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
       <c r="M40" s="7"/>
-    </row>
-    <row r="41" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AG40" s="42"/>
+    </row>
+    <row r="41" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
@@ -3910,8 +4203,14 @@
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
       <c r="M41" s="7"/>
-    </row>
-    <row r="43" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AG41" s="42"/>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="Z42" s="47" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
@@ -3924,8 +4223,12 @@
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
       <c r="M43" s="7"/>
-    </row>
-    <row r="44" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z43" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="AG43" s="42"/>
+    </row>
+    <row r="44" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
@@ -3938,8 +4241,12 @@
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
       <c r="M44" s="7"/>
-    </row>
-    <row r="45" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z44" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="AG44" s="42"/>
+    </row>
+    <row r="45" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
@@ -3952,8 +4259,9 @@
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
       <c r="M45" s="7"/>
-    </row>
-    <row r="46" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AG45" s="42"/>
+    </row>
+    <row r="46" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
@@ -3966,8 +4274,9 @@
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
       <c r="M46" s="7"/>
-    </row>
-    <row r="47" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AG46" s="42"/>
+    </row>
+    <row r="47" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
@@ -3980,8 +4289,9 @@
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
       <c r="M47" s="7"/>
-    </row>
-    <row r="48" spans="2:30" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AG47" s="42"/>
+    </row>
+    <row r="48" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
@@ -3994,8 +4304,9 @@
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
       <c r="M48" s="7"/>
-    </row>
-    <row r="49" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AG48" s="42"/>
+    </row>
+    <row r="49" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
@@ -4008,8 +4319,9 @@
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
       <c r="M49" s="7"/>
-    </row>
-    <row r="50" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AG49" s="42"/>
+    </row>
+    <row r="50" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
@@ -4022,8 +4334,9 @@
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
       <c r="M50" s="7"/>
-    </row>
-    <row r="52" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AG50" s="42"/>
+    </row>
+    <row r="52" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
@@ -4036,8 +4349,9 @@
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
       <c r="M52" s="7"/>
-    </row>
-    <row r="53" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AG52" s="42"/>
+    </row>
+    <row r="53" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
@@ -4050,8 +4364,9 @@
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
       <c r="M53" s="7"/>
-    </row>
-    <row r="54" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AG53" s="42"/>
+    </row>
+    <row r="54" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
@@ -4064,8 +4379,9 @@
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
       <c r="M54" s="7"/>
-    </row>
-    <row r="55" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AG54" s="42"/>
+    </row>
+    <row r="55" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
@@ -4078,8 +4394,9 @@
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
       <c r="M55" s="7"/>
-    </row>
-    <row r="56" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AG55" s="42"/>
+    </row>
+    <row r="56" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
@@ -4092,8 +4409,9 @@
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
-    </row>
-    <row r="57" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AG56" s="42"/>
+    </row>
+    <row r="57" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
@@ -4106,8 +4424,9 @@
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
       <c r="M57" s="7"/>
-    </row>
-    <row r="58" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AG57" s="42"/>
+    </row>
+    <row r="58" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
@@ -4120,8 +4439,9 @@
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
       <c r="M58" s="7"/>
-    </row>
-    <row r="59" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AG58" s="42"/>
+    </row>
+    <row r="59" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
@@ -4134,8 +4454,9 @@
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
       <c r="M59" s="7"/>
-    </row>
-    <row r="60" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AG59" s="42"/>
+    </row>
+    <row r="60" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
@@ -4148,8 +4469,9 @@
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
       <c r="M60" s="7"/>
-    </row>
-    <row r="61" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AG60" s="42"/>
+    </row>
+    <row r="61" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
@@ -4162,8 +4484,9 @@
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
       <c r="M61" s="7"/>
-    </row>
-    <row r="62" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AG61" s="42"/>
+    </row>
+    <row r="62" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
@@ -4176,8 +4499,9 @@
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
       <c r="M62" s="7"/>
-    </row>
-    <row r="63" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AG62" s="42"/>
+    </row>
+    <row r="63" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B63" s="7"/>
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
@@ -4190,9 +4514,13 @@
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
       <c r="M63" s="7"/>
+      <c r="AG63" s="42"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/$PAR.xlsx
+++ b/$PAR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffe\Documents\GitHub\martinshkreli-models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB09D54-B0E9-4740-A6C8-8CD27E627FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349C3068-59DA-4548-B5AB-21FB1580C9AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="90" windowWidth="19245" windowHeight="20805" activeTab="1" xr2:uid="{8F193AD5-4822-438A-B757-2B234AE27955}"/>
+    <workbookView xWindow="31305" yWindow="90" windowWidth="20310" windowHeight="20805" activeTab="1" xr2:uid="{8F193AD5-4822-438A-B757-2B234AE27955}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="2" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="96">
   <si>
     <t>FY</t>
   </si>
@@ -320,19 +320,60 @@
   </si>
   <si>
     <t>Conversative case 1.5%-2%</t>
+  </si>
+  <si>
+    <t>Q225</t>
+  </si>
+  <si>
+    <t>Q325</t>
+  </si>
+  <si>
+    <t>Q425</t>
+  </si>
+  <si>
+    <t>Won't see ARR back in the 20% until Q4 at earliest</t>
+  </si>
+  <si>
+    <t>What is the industry multiple that PAR trades at?</t>
+  </si>
+  <si>
+    <t>POS Multiple</t>
+  </si>
+  <si>
+    <t>Lightspeed</t>
+  </si>
+  <si>
+    <t>Toast</t>
+  </si>
+  <si>
+    <t>NCR</t>
+  </si>
+  <si>
+    <t>Agilysys</t>
+  </si>
+  <si>
+    <t>EV/Rev (Multiple)</t>
+  </si>
+  <si>
+    <t>Avg</t>
+  </si>
+  <si>
+    <t>Chatgpt Industry ARR Multiple</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="8">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="0.0000%"/>
+    <numFmt numFmtId="166" formatCode="0.0000%"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -428,7 +469,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -507,10 +548,14 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -560,8 +605,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BB51B890-2FC8-4114-8D37-1B569A044EC6}" name="Table1" displayName="Table1" ref="Z22:AB28" totalsRowShown="0">
-  <autoFilter ref="Z22:AB28" xr:uid="{BB51B890-2FC8-4114-8D37-1B569A044EC6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BB51B890-2FC8-4114-8D37-1B569A044EC6}" name="Table1" displayName="Table1" ref="AB22:AD28" totalsRowShown="0">
+  <autoFilter ref="AB22:AD28" xr:uid="{BB51B890-2FC8-4114-8D37-1B569A044EC6}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{74DABAA3-C917-41B3-A57B-92DBCAE597C3}" name="Component" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{094D8EA8-133C-4AAB-81FA-8255CE427369}" name="Estimated Value" dataDxfId="1" dataCellStyle="Percent"/>
@@ -876,7 +921,7 @@
         <v>41</v>
       </c>
       <c r="L5" s="8">
-        <v>65.95</v>
+        <v>46.73</v>
       </c>
     </row>
     <row r="6" spans="11:12" x14ac:dyDescent="0.25">
@@ -884,7 +929,7 @@
         <v>26</v>
       </c>
       <c r="L6" s="6">
-        <v>37</v>
+        <v>40.520000000000003</v>
       </c>
     </row>
     <row r="7" spans="11:12" x14ac:dyDescent="0.25">
@@ -893,7 +938,7 @@
       </c>
       <c r="L7" s="6">
         <f>+L5*L6</f>
-        <v>2440.15</v>
+        <v>1893.4996000000001</v>
       </c>
     </row>
     <row r="8" spans="11:12" x14ac:dyDescent="0.25">
@@ -918,7 +963,7 @@
       </c>
       <c r="L10" s="6">
         <f>+L7-L8+L9</f>
-        <v>2660.777</v>
+        <v>2114.1266000000001</v>
       </c>
     </row>
   </sheetData>
@@ -928,7 +973,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE7FAD33-99C5-4121-980B-8556C8EA76DD}">
-  <dimension ref="A1:DH63"/>
+  <dimension ref="A1:DJ63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
@@ -944,19 +989,22 @@
     <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="17.42578125" customWidth="1"/>
-    <col min="27" max="27" width="18.140625" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="9.140625" style="39"/>
+    <col min="20" max="20" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.42578125" customWidth="1"/>
+    <col min="29" max="29" width="18.140625" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="17" style="39" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:114" x14ac:dyDescent="0.25">
       <c r="D1" s="2">
         <v>44104</v>
       </c>
@@ -1002,11 +1050,14 @@
       <c r="V1" s="3">
         <v>45747</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="W1" s="2">
+        <v>45838</v>
+      </c>
+      <c r="AB1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:114" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1070,58 +1121,66 @@
       <c r="V2" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="W2" s="1"/>
+      <c r="W2" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="X2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="Z2" s="1">
+      <c r="AB2" s="1">
         <v>2018</v>
       </c>
-      <c r="AA2" s="1">
+      <c r="AC2" s="1">
         <v>2019</v>
       </c>
-      <c r="AB2">
+      <c r="AD2">
         <v>2020</v>
       </c>
-      <c r="AC2">
-        <f>+AB2+1</f>
+      <c r="AE2">
+        <f>+AD2+1</f>
         <v>2021</v>
       </c>
-      <c r="AD2">
-        <f t="shared" ref="AD2:AF2" si="0">+AC2+1</f>
+      <c r="AF2">
+        <f t="shared" ref="AF2:AH2" si="0">+AE2+1</f>
         <v>2022</v>
       </c>
-      <c r="AE2">
+      <c r="AG2">
         <f t="shared" si="0"/>
         <v>2023</v>
       </c>
-      <c r="AF2">
+      <c r="AH2">
         <f t="shared" si="0"/>
         <v>2024</v>
       </c>
-      <c r="AG2" s="39">
+      <c r="AI2" s="39">
         <v>2025</v>
       </c>
-      <c r="AH2">
+      <c r="AJ2">
         <v>2026</v>
       </c>
-      <c r="AI2">
+      <c r="AK2">
         <v>2027</v>
       </c>
-      <c r="AJ2">
+      <c r="AL2">
         <v>2028</v>
       </c>
-      <c r="AK2">
+      <c r="AM2">
         <v>2029</v>
       </c>
-      <c r="AL2">
+      <c r="AN2">
         <v>2030</v>
       </c>
     </row>
-    <row r="3" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -1170,8 +1229,11 @@
       <c r="V3" s="23">
         <v>21.843</v>
       </c>
-    </row>
-    <row r="4" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="W3" s="23">
+        <v>26.864000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
         <v>44</v>
       </c>
@@ -1222,16 +1284,19 @@
       <c r="V4" s="32">
         <v>68.41</v>
       </c>
-      <c r="X4">
+      <c r="W4" s="32">
+        <v>71.903000000000006</v>
+      </c>
+      <c r="Z4">
         <f>1.15*Q4</f>
         <v>37.831549999999993</v>
       </c>
-      <c r="Y4" s="23">
+      <c r="AA4" s="23">
         <f>Q4+23.4</f>
         <v>56.296999999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -1280,8 +1345,11 @@
       <c r="V5" s="23">
         <v>13.606</v>
       </c>
-    </row>
-    <row r="6" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="W5" s="23">
+        <v>13.637</v>
+      </c>
+    </row>
+    <row r="6" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>46</v>
       </c>
@@ -1324,8 +1392,15 @@
       <c r="V6" s="23">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="W6" s="23">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="48">
+        <f>AI13-V12-W12</f>
+        <v>246.22819999999993</v>
+      </c>
+    </row>
+    <row r="7" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
         <v>50</v>
       </c>
@@ -1342,7 +1417,7 @@
       <c r="L7" s="31"/>
       <c r="M7" s="31"/>
       <c r="N7" s="33">
-        <f t="shared" ref="N7:V7" si="1">(N4-J4)/J4</f>
+        <f t="shared" ref="N7:W7" si="1">(N4-J4)/J4</f>
         <v>0.31383603476626731</v>
       </c>
       <c r="O7" s="33">
@@ -1377,8 +1452,12 @@
         <f t="shared" si="1"/>
         <v>0.7824852132676724</v>
       </c>
-    </row>
-    <row r="8" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="W7" s="33">
+        <f t="shared" si="1"/>
+        <v>0.60240238901765031</v>
+      </c>
+    </row>
+    <row r="8" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>49</v>
       </c>
@@ -1431,22 +1510,24 @@
         <f>(V4-U4)/U4</f>
         <v>6.4548255578724539E-2</v>
       </c>
-      <c r="AC8" s="25">
-        <f>(AC13-AB13)/AB13</f>
-        <v>0.32317364093065015</v>
-      </c>
-      <c r="AD8" s="25">
-        <f>(AD13-AC13)/AC13</f>
-        <v>0.25777725929382483</v>
+      <c r="W8" s="27">
+        <f>(W4-V4)/V4</f>
+        <v>5.1059786580909358E-2</v>
       </c>
       <c r="AE8" s="25">
         <f>(AE13-AD13)/AD13</f>
+        <v>0.32317364093065015</v>
+      </c>
+      <c r="AF8" s="25">
+        <f>(AF13-AE13)/AE13</f>
+        <v>0.25777725929382483</v>
+      </c>
+      <c r="AG8" s="25">
+        <f>(AG13-AF13)/AF13</f>
         <v>0.1687151309040319</v>
       </c>
-      <c r="AF8" s="25"/>
-      <c r="AG8" s="40"/>
       <c r="AH8" s="25"/>
-      <c r="AI8" s="25"/>
+      <c r="AI8" s="40"/>
       <c r="AJ8" s="25"/>
       <c r="AK8" s="25"/>
       <c r="AL8" s="25"/>
@@ -1466,14 +1547,16 @@
       <c r="AZ8" s="25"/>
       <c r="BA8" s="25"/>
       <c r="BB8" s="25"/>
-    </row>
-    <row r="9" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="BC8" s="25"/>
+      <c r="BD8" s="25"/>
+    </row>
+    <row r="9" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>59</v>
       </c>
       <c r="J9" s="27"/>
       <c r="K9" s="27">
-        <f t="shared" ref="K9:V9" si="3">K15/K13</f>
+        <f t="shared" ref="K9:W9" si="3">K15/K13</f>
         <v>0.24821078114533499</v>
       </c>
       <c r="L9" s="27">
@@ -1520,13 +1603,15 @@
         <f t="shared" si="3"/>
         <v>0.46545797667992178</v>
       </c>
-      <c r="AC9" s="25"/>
-      <c r="AD9" s="25"/>
+      <c r="W9" s="27">
+        <f t="shared" si="3"/>
+        <v>0.45362989323843422</v>
+      </c>
       <c r="AE9" s="25"/>
       <c r="AF9" s="25"/>
-      <c r="AG9" s="40"/>
+      <c r="AG9" s="25"/>
       <c r="AH9" s="25"/>
-      <c r="AI9" s="25"/>
+      <c r="AI9" s="40"/>
       <c r="AJ9" s="25"/>
       <c r="AK9" s="25"/>
       <c r="AL9" s="25"/>
@@ -1546,14 +1631,16 @@
       <c r="AZ9" s="25"/>
       <c r="BA9" s="25"/>
       <c r="BB9" s="25"/>
-    </row>
-    <row r="10" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="BC9" s="25"/>
+      <c r="BD9" s="25"/>
+    </row>
+    <row r="10" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>58</v>
       </c>
       <c r="J10" s="22"/>
       <c r="K10" s="27">
-        <f t="shared" ref="K10:V10" si="4">K8+K9</f>
+        <f t="shared" ref="K10:W10" si="4">K8+K9</f>
         <v>0.33583117109130622</v>
       </c>
       <c r="L10" s="27">
@@ -1600,13 +1687,15 @@
         <f t="shared" si="4"/>
         <v>0.53000623225864629</v>
       </c>
-      <c r="AC10" s="25"/>
-      <c r="AD10" s="25"/>
+      <c r="W10" s="27">
+        <f t="shared" si="4"/>
+        <v>0.50468967981934354</v>
+      </c>
       <c r="AE10" s="25"/>
       <c r="AF10" s="25"/>
-      <c r="AG10" s="40"/>
+      <c r="AG10" s="25"/>
       <c r="AH10" s="25"/>
-      <c r="AI10" s="25"/>
+      <c r="AI10" s="40"/>
       <c r="AJ10" s="25"/>
       <c r="AK10" s="25"/>
       <c r="AL10" s="25"/>
@@ -1626,8 +1715,10 @@
       <c r="AZ10" s="25"/>
       <c r="BA10" s="25"/>
       <c r="BB10" s="25"/>
-    </row>
-    <row r="11" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="BC10" s="25"/>
+      <c r="BD10" s="25"/>
+    </row>
+    <row r="11" spans="1:114" x14ac:dyDescent="0.25">
       <c r="J11" s="22"/>
       <c r="K11" s="27"/>
       <c r="L11" s="27"/>
@@ -1636,19 +1727,17 @@
       <c r="O11" s="27"/>
       <c r="P11" s="27"/>
       <c r="Q11" s="27"/>
-      <c r="AA11" t="s">
+      <c r="AC11" t="s">
         <v>60</v>
       </c>
-      <c r="AB11" s="34"/>
-      <c r="AC11" s="34"/>
       <c r="AD11" s="34"/>
-      <c r="AE11" s="34">
+      <c r="AE11" s="34"/>
+      <c r="AF11" s="34"/>
+      <c r="AG11" s="34">
         <v>136.9</v>
       </c>
-      <c r="AF11" s="25"/>
-      <c r="AG11" s="40"/>
       <c r="AH11" s="25"/>
-      <c r="AI11" s="25"/>
+      <c r="AI11" s="40"/>
       <c r="AJ11" s="25"/>
       <c r="AK11" s="25"/>
       <c r="AL11" s="25"/>
@@ -1668,8 +1757,10 @@
       <c r="AZ11" s="25"/>
       <c r="BA11" s="25"/>
       <c r="BB11" s="25"/>
-    </row>
-    <row r="12" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="BC11" s="25"/>
+      <c r="BD11" s="25"/>
+    </row>
+    <row r="12" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A12" s="35" t="s">
         <v>61</v>
       </c>
@@ -1725,340 +1816,343 @@
         <f t="shared" ref="J12:V13" si="6">SUM(V2:V5)</f>
         <v>103.85899999999999</v>
       </c>
-      <c r="AD12" s="38">
+      <c r="W12" s="47">
+        <v>112.4</v>
+      </c>
+      <c r="AF12" s="38">
         <f>SUM(J12:M12)</f>
         <v>262.34699999999998</v>
       </c>
-      <c r="AE12" s="38">
+      <c r="AG12" s="38">
         <f>SUM(N12:Q12)</f>
         <v>276.714</v>
       </c>
-      <c r="AF12" s="4">
-        <f>AE12*(1+$AD$32)</f>
+      <c r="AH12" s="4">
+        <f>AG12*(1+$AF$32)</f>
         <v>332.05680000000001</v>
       </c>
-      <c r="AG12" s="41">
-        <f t="shared" ref="AG12:AL12" si="7">AF12*(1+$AD$32)</f>
+      <c r="AI12" s="41">
+        <f t="shared" ref="AI12:AN12" si="7">AH12*(1+$AF$32)</f>
         <v>398.46816000000001</v>
       </c>
-      <c r="AH12" s="4">
+      <c r="AJ12" s="4">
         <f t="shared" si="7"/>
         <v>478.16179199999999</v>
       </c>
-      <c r="AI12" s="4">
+      <c r="AK12" s="4">
         <f t="shared" si="7"/>
         <v>573.79415039999992</v>
       </c>
-      <c r="AJ12" s="4">
+      <c r="AL12" s="4">
         <f t="shared" si="7"/>
         <v>688.55298047999986</v>
       </c>
-      <c r="AK12" s="4">
+      <c r="AM12" s="4">
         <f t="shared" si="7"/>
         <v>826.26357657599976</v>
       </c>
-      <c r="AL12" s="4">
+      <c r="AN12" s="4">
         <f t="shared" si="7"/>
         <v>991.51629189119967</v>
       </c>
-      <c r="AM12" s="4">
-        <f>AL12*(1+$AD$33)</f>
-        <v>1001.4314548101116</v>
-      </c>
-      <c r="AN12" s="4">
-        <f t="shared" ref="AN12:CY12" si="8">AM12*(1+$AD$33)</f>
-        <v>1011.4457693582127</v>
-      </c>
       <c r="AO12" s="4">
-        <f t="shared" si="8"/>
-        <v>1021.5602270517949</v>
+        <f>AN12*(1+$AF$33)</f>
+        <v>991.51629189119967</v>
       </c>
       <c r="AP12" s="4">
-        <f t="shared" si="8"/>
-        <v>1031.7758293223128</v>
+        <f t="shared" ref="AP12:DA12" si="8">AO12*(1+$AF$33)</f>
+        <v>991.51629189119967</v>
       </c>
       <c r="AQ12" s="4">
         <f t="shared" si="8"/>
-        <v>1042.0935876155359</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="AR12" s="4">
         <f t="shared" si="8"/>
-        <v>1052.5145234916913</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="AS12" s="4">
         <f t="shared" si="8"/>
-        <v>1063.0396687266082</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="AT12" s="4">
         <f t="shared" si="8"/>
-        <v>1073.6700654138742</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="AU12" s="4">
         <f t="shared" si="8"/>
-        <v>1084.406766068013</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="AV12" s="4">
         <f t="shared" si="8"/>
-        <v>1095.2508337286931</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="AW12" s="4">
         <f t="shared" si="8"/>
-        <v>1106.20334206598</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="AX12" s="4">
         <f t="shared" si="8"/>
-        <v>1117.2653754866399</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="AY12" s="4">
         <f t="shared" si="8"/>
-        <v>1128.4380292415062</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="AZ12" s="4">
         <f t="shared" si="8"/>
-        <v>1139.7224095339213</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="BA12" s="4">
         <f t="shared" si="8"/>
-        <v>1151.1196336292605</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="BB12" s="4">
         <f t="shared" si="8"/>
-        <v>1162.6308299655532</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="BC12" s="4">
         <f t="shared" si="8"/>
-        <v>1174.2571382652088</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="BD12" s="4">
         <f t="shared" si="8"/>
-        <v>1185.999709647861</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="BE12" s="4">
         <f t="shared" si="8"/>
-        <v>1197.8597067443395</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="BF12" s="4">
         <f t="shared" si="8"/>
-        <v>1209.8383038117829</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="BG12" s="4">
         <f t="shared" si="8"/>
-        <v>1221.9366868499008</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="BH12" s="4">
         <f t="shared" si="8"/>
-        <v>1234.1560537183998</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="BI12" s="4">
         <f t="shared" si="8"/>
-        <v>1246.4976142555838</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="BJ12" s="4">
         <f t="shared" si="8"/>
-        <v>1258.9625903981396</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="BK12" s="4">
         <f t="shared" si="8"/>
-        <v>1271.552216302121</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="BL12" s="4">
         <f t="shared" si="8"/>
-        <v>1284.2677384651422</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="BM12" s="4">
         <f t="shared" si="8"/>
-        <v>1297.1104158497935</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="BN12" s="4">
         <f t="shared" si="8"/>
-        <v>1310.0815200082914</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="BO12" s="4">
         <f t="shared" si="8"/>
-        <v>1323.1823352083743</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="BP12" s="4">
         <f t="shared" si="8"/>
-        <v>1336.414158560458</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="BQ12" s="4">
         <f t="shared" si="8"/>
-        <v>1349.7783001460625</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="BR12" s="4">
         <f t="shared" si="8"/>
-        <v>1363.2760831475232</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="BS12" s="4">
         <f t="shared" si="8"/>
-        <v>1376.9088439789984</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="BT12" s="4">
         <f t="shared" si="8"/>
-        <v>1390.6779324187885</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="BU12" s="4">
         <f t="shared" si="8"/>
-        <v>1404.5847117429764</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="BV12" s="4">
         <f t="shared" si="8"/>
-        <v>1418.6305588604062</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="BW12" s="4">
         <f t="shared" si="8"/>
-        <v>1432.8168644490102</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="BX12" s="4">
         <f t="shared" si="8"/>
-        <v>1447.1450330935002</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="BY12" s="4">
         <f t="shared" si="8"/>
-        <v>1461.6164834244353</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="BZ12" s="4">
         <f t="shared" si="8"/>
-        <v>1476.2326482586795</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="CA12" s="4">
         <f t="shared" si="8"/>
-        <v>1490.9949747412663</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="CB12" s="4">
         <f t="shared" si="8"/>
-        <v>1505.9049244886789</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="CC12" s="4">
         <f t="shared" si="8"/>
-        <v>1520.9639737335658</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="CD12" s="4">
         <f t="shared" si="8"/>
-        <v>1536.1736134709015</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="CE12" s="4">
         <f t="shared" si="8"/>
-        <v>1551.5353496056105</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="CF12" s="4">
         <f t="shared" si="8"/>
-        <v>1567.0507031016666</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="CG12" s="4">
         <f t="shared" si="8"/>
-        <v>1582.7212101326834</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="CH12" s="4">
         <f t="shared" si="8"/>
-        <v>1598.5484222340103</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="CI12" s="4">
         <f t="shared" si="8"/>
-        <v>1614.5339064563505</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="CJ12" s="4">
         <f t="shared" si="8"/>
-        <v>1630.679245520914</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="CK12" s="4">
         <f t="shared" si="8"/>
-        <v>1646.9860379761233</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="CL12" s="4">
         <f t="shared" si="8"/>
-        <v>1663.4558983558845</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="CM12" s="4">
         <f t="shared" si="8"/>
-        <v>1680.0904573394434</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="CN12" s="4">
         <f t="shared" si="8"/>
-        <v>1696.891361912838</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="CO12" s="4">
         <f t="shared" si="8"/>
-        <v>1713.8602755319664</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="CP12" s="4">
         <f t="shared" si="8"/>
-        <v>1730.9988782872861</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="CQ12" s="4">
         <f t="shared" si="8"/>
-        <v>1748.3088670701588</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="CR12" s="4">
         <f t="shared" si="8"/>
-        <v>1765.7919557408604</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="CS12" s="4">
         <f t="shared" si="8"/>
-        <v>1783.449875298269</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="CT12" s="4">
         <f t="shared" si="8"/>
-        <v>1801.2843740512517</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="CU12" s="4">
         <f t="shared" si="8"/>
-        <v>1819.2972177917643</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="CV12" s="4">
         <f t="shared" si="8"/>
-        <v>1837.490189969682</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="CW12" s="4">
         <f t="shared" si="8"/>
-        <v>1855.8650918693788</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="CX12" s="4">
         <f t="shared" si="8"/>
-        <v>1874.4237427880726</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="CY12" s="4">
         <f t="shared" si="8"/>
-        <v>1893.1679802159533</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="CZ12" s="4">
-        <f t="shared" ref="CZ12:DH12" si="9">CY12*(1+$AD$33)</f>
-        <v>1912.0996600181129</v>
+        <f t="shared" si="8"/>
+        <v>991.51629189119967</v>
       </c>
       <c r="DA12" s="4">
-        <f t="shared" si="9"/>
-        <v>1931.220656618294</v>
+        <f t="shared" si="8"/>
+        <v>991.51629189119967</v>
       </c>
       <c r="DB12" s="4">
-        <f t="shared" si="9"/>
-        <v>1950.532863184477</v>
+        <f t="shared" ref="DB12:DJ12" si="9">DA12*(1+$AF$33)</f>
+        <v>991.51629189119967</v>
       </c>
       <c r="DC12" s="4">
         <f t="shared" si="9"/>
-        <v>1970.0381918163218</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="DD12" s="4">
         <f t="shared" si="9"/>
-        <v>1989.738573734485</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="DE12" s="4">
         <f t="shared" si="9"/>
-        <v>2009.6359594718299</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="DF12" s="4">
         <f t="shared" si="9"/>
-        <v>2029.7323190665481</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="DG12" s="4">
         <f t="shared" si="9"/>
-        <v>2050.0296422572137</v>
+        <v>991.51629189119967</v>
       </c>
       <c r="DH12" s="4">
         <f t="shared" si="9"/>
-        <v>2070.529938679786</v>
-      </c>
-    </row>
-    <row r="13" spans="1:112" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+        <v>991.51629189119967</v>
+      </c>
+      <c r="DI12" s="4">
+        <f t="shared" si="9"/>
+        <v>991.51629189119967</v>
+      </c>
+      <c r="DJ12" s="4">
+        <f t="shared" si="9"/>
+        <v>991.51629189119967</v>
+      </c>
+    </row>
+    <row r="13" spans="1:114" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>15</v>
       </c>
@@ -2122,346 +2216,349 @@
         <f t="shared" si="6"/>
         <v>103.85899999999999</v>
       </c>
-      <c r="AB13" s="4">
+      <c r="W13" s="47">
+        <v>112.4</v>
+      </c>
+      <c r="AD13" s="4">
         <v>213.786</v>
       </c>
-      <c r="AC13" s="4">
+      <c r="AE13" s="4">
         <v>282.87599999999998</v>
       </c>
-      <c r="AD13" s="4">
+      <c r="AF13" s="4">
         <f>SUM(J13:M13)</f>
         <v>355.79499999999996</v>
       </c>
-      <c r="AE13" s="4">
+      <c r="AG13" s="4">
         <f>SUM(N13:Q13)</f>
         <v>415.82299999999998</v>
       </c>
-      <c r="AF13" s="4">
+      <c r="AH13" s="4">
         <f>SUM(R13:U13)</f>
         <v>385.40599999999995</v>
       </c>
-      <c r="AG13" s="41">
-        <f t="shared" ref="AG13:AL15" si="10">AF13*(1+$AA$32)</f>
-        <v>501.02779999999996</v>
-      </c>
-      <c r="AH13" s="4">
-        <f t="shared" si="10"/>
-        <v>651.33614</v>
-      </c>
-      <c r="AI13" s="4">
-        <f t="shared" si="10"/>
-        <v>846.73698200000001</v>
+      <c r="AI13" s="41">
+        <f t="shared" ref="AI13:AN15" si="10">AH13*(1+$AC$32)</f>
+        <v>462.48719999999992</v>
       </c>
       <c r="AJ13" s="4">
         <f t="shared" si="10"/>
-        <v>1100.7580766000001</v>
+        <v>554.9846399999999</v>
       </c>
       <c r="AK13" s="4">
         <f t="shared" si="10"/>
-        <v>1430.9854995800001</v>
+        <v>665.98156799999981</v>
       </c>
       <c r="AL13" s="4">
         <f t="shared" si="10"/>
-        <v>1860.2811494540001</v>
+        <v>799.17788159999975</v>
       </c>
       <c r="AM13" s="4">
-        <f>AL13*(1+$AA$33)</f>
-        <v>1897.4867724430801</v>
+        <f t="shared" si="10"/>
+        <v>959.01345791999961</v>
       </c>
       <c r="AN13" s="4">
-        <f t="shared" ref="AN13:CY13" si="11">AM13*(1+$AA$33)</f>
-        <v>1935.4365078919418</v>
+        <f t="shared" si="10"/>
+        <v>1150.8161495039994</v>
       </c>
       <c r="AO13" s="4">
-        <f t="shared" si="11"/>
-        <v>1974.1452380497806</v>
+        <f>AN13*(1+$AC$33)</f>
+        <v>1173.8324724940794</v>
       </c>
       <c r="AP13" s="4">
-        <f t="shared" si="11"/>
-        <v>2013.6281428107761</v>
+        <f t="shared" ref="AP13:DA13" si="11">AO13*(1+$AC$33)</f>
+        <v>1197.3091219439609</v>
       </c>
       <c r="AQ13" s="4">
         <f t="shared" si="11"/>
-        <v>2053.9007056669916</v>
+        <v>1221.2553043828402</v>
       </c>
       <c r="AR13" s="4">
         <f t="shared" si="11"/>
-        <v>2094.9787197803316</v>
+        <v>1245.680410470497</v>
       </c>
       <c r="AS13" s="4">
         <f t="shared" si="11"/>
-        <v>2136.8782941759382</v>
+        <v>1270.5940186799069</v>
       </c>
       <c r="AT13" s="4">
         <f t="shared" si="11"/>
-        <v>2179.6158600594572</v>
+        <v>1296.0058990535051</v>
       </c>
       <c r="AU13" s="4">
         <f t="shared" si="11"/>
-        <v>2223.2081772606462</v>
+        <v>1321.9260170345754</v>
       </c>
       <c r="AV13" s="4">
         <f t="shared" si="11"/>
-        <v>2267.6723408058592</v>
+        <v>1348.364537375267</v>
       </c>
       <c r="AW13" s="4">
         <f t="shared" si="11"/>
-        <v>2313.0257876219766</v>
+        <v>1375.3318281227723</v>
       </c>
       <c r="AX13" s="4">
         <f t="shared" si="11"/>
-        <v>2359.2863033744161</v>
+        <v>1402.8384646852278</v>
       </c>
       <c r="AY13" s="4">
         <f t="shared" si="11"/>
-        <v>2406.4720294419044</v>
+        <v>1430.8952339789323</v>
       </c>
       <c r="AZ13" s="4">
         <f t="shared" si="11"/>
-        <v>2454.6014700307423</v>
+        <v>1459.513138658511</v>
       </c>
       <c r="BA13" s="4">
         <f t="shared" si="11"/>
-        <v>2503.6934994313574</v>
+        <v>1488.7034014316812</v>
       </c>
       <c r="BB13" s="4">
         <f t="shared" si="11"/>
-        <v>2553.7673694199848</v>
+        <v>1518.4774694603148</v>
       </c>
       <c r="BC13" s="4">
         <f t="shared" si="11"/>
-        <v>2604.8427168083845</v>
+        <v>1548.847018849521</v>
       </c>
       <c r="BD13" s="4">
         <f t="shared" si="11"/>
-        <v>2656.9395711445522</v>
+        <v>1579.8239592265113</v>
       </c>
       <c r="BE13" s="4">
         <f t="shared" si="11"/>
-        <v>2710.0783625674435</v>
+        <v>1611.4204384110415</v>
       </c>
       <c r="BF13" s="4">
         <f t="shared" si="11"/>
-        <v>2764.2799298187924</v>
+        <v>1643.6488471792622</v>
       </c>
       <c r="BG13" s="4">
         <f t="shared" si="11"/>
-        <v>2819.5655284151685</v>
+        <v>1676.5218241228474</v>
       </c>
       <c r="BH13" s="4">
         <f t="shared" si="11"/>
-        <v>2875.9568389834717</v>
+        <v>1710.0522606053044</v>
       </c>
       <c r="BI13" s="4">
         <f t="shared" si="11"/>
-        <v>2933.4759757631414</v>
+        <v>1744.2533058174104</v>
       </c>
       <c r="BJ13" s="4">
         <f t="shared" si="11"/>
-        <v>2992.1454952784043</v>
+        <v>1779.1383719337587</v>
       </c>
       <c r="BK13" s="4">
         <f t="shared" si="11"/>
-        <v>3051.9884051839722</v>
+        <v>1814.7211393724338</v>
       </c>
       <c r="BL13" s="4">
         <f t="shared" si="11"/>
-        <v>3113.0281732876515</v>
+        <v>1851.0155621598824</v>
       </c>
       <c r="BM13" s="4">
         <f t="shared" si="11"/>
-        <v>3175.2887367534045</v>
+        <v>1888.0358734030801</v>
       </c>
       <c r="BN13" s="4">
         <f t="shared" si="11"/>
-        <v>3238.7945114884728</v>
+        <v>1925.7965908711417</v>
       </c>
       <c r="BO13" s="4">
         <f t="shared" si="11"/>
-        <v>3303.5704017182425</v>
+        <v>1964.3125226885645</v>
       </c>
       <c r="BP13" s="4">
         <f t="shared" si="11"/>
-        <v>3369.6418097526075</v>
+        <v>2003.5987731423359</v>
       </c>
       <c r="BQ13" s="4">
         <f t="shared" si="11"/>
-        <v>3437.0346459476596</v>
+        <v>2043.6707486051826</v>
       </c>
       <c r="BR13" s="4">
         <f t="shared" si="11"/>
-        <v>3505.7753388666129</v>
+        <v>2084.5441635772863</v>
       </c>
       <c r="BS13" s="4">
         <f t="shared" si="11"/>
-        <v>3575.8908456439453</v>
+        <v>2126.2350468488321</v>
       </c>
       <c r="BT13" s="4">
         <f t="shared" si="11"/>
-        <v>3647.4086625568243</v>
+        <v>2168.7597477858089</v>
       </c>
       <c r="BU13" s="4">
         <f t="shared" si="11"/>
-        <v>3720.356835807961</v>
+        <v>2212.1349427415253</v>
       </c>
       <c r="BV13" s="4">
         <f t="shared" si="11"/>
-        <v>3794.7639725241202</v>
+        <v>2256.3776415963557</v>
       </c>
       <c r="BW13" s="4">
         <f t="shared" si="11"/>
-        <v>3870.6592519746027</v>
+        <v>2301.5051944282827</v>
       </c>
       <c r="BX13" s="4">
         <f t="shared" si="11"/>
-        <v>3948.0724370140947</v>
+        <v>2347.5352983168486</v>
       </c>
       <c r="BY13" s="4">
         <f t="shared" si="11"/>
-        <v>4027.0338857543766</v>
+        <v>2394.4860042831856</v>
       </c>
       <c r="BZ13" s="4">
         <f t="shared" si="11"/>
-        <v>4107.574563469464</v>
+        <v>2442.3757243688492</v>
       </c>
       <c r="CA13" s="4">
         <f t="shared" si="11"/>
-        <v>4189.7260547388532</v>
+        <v>2491.2232388562261</v>
       </c>
       <c r="CB13" s="4">
         <f t="shared" si="11"/>
-        <v>4273.5205758336306</v>
+        <v>2541.0477036333505</v>
       </c>
       <c r="CC13" s="4">
         <f t="shared" si="11"/>
-        <v>4358.9909873503029</v>
+        <v>2591.8686577060175</v>
       </c>
       <c r="CD13" s="4">
         <f t="shared" si="11"/>
-        <v>4446.1708070973091</v>
+        <v>2643.7060308601381</v>
       </c>
       <c r="CE13" s="4">
         <f t="shared" si="11"/>
-        <v>4535.0942232392554</v>
+        <v>2696.5801514773407</v>
       </c>
       <c r="CF13" s="4">
         <f t="shared" si="11"/>
-        <v>4625.7961077040409</v>
+        <v>2750.5117545068874</v>
       </c>
       <c r="CG13" s="4">
         <f t="shared" si="11"/>
-        <v>4718.3120298581216</v>
+        <v>2805.5219895970254</v>
       </c>
       <c r="CH13" s="4">
         <f t="shared" si="11"/>
-        <v>4812.6782704552843</v>
+        <v>2861.6324293889661</v>
       </c>
       <c r="CI13" s="4">
         <f t="shared" si="11"/>
-        <v>4908.9318358643905</v>
+        <v>2918.8650779767454</v>
       </c>
       <c r="CJ13" s="4">
         <f t="shared" si="11"/>
-        <v>5007.1104725816786</v>
+        <v>2977.2423795362802</v>
       </c>
       <c r="CK13" s="4">
         <f t="shared" si="11"/>
-        <v>5107.2526820333123</v>
+        <v>3036.7872271270057</v>
       </c>
       <c r="CL13" s="4">
         <f t="shared" si="11"/>
-        <v>5209.3977356739788</v>
+        <v>3097.5229716695458</v>
       </c>
       <c r="CM13" s="4">
         <f t="shared" si="11"/>
-        <v>5313.5856903874583</v>
+        <v>3159.473431102937</v>
       </c>
       <c r="CN13" s="4">
         <f t="shared" si="11"/>
-        <v>5419.8574041952079</v>
+        <v>3222.6628997249959</v>
       </c>
       <c r="CO13" s="4">
         <f t="shared" si="11"/>
-        <v>5528.2545522791124</v>
+        <v>3287.1161577194957</v>
       </c>
       <c r="CP13" s="4">
         <f t="shared" si="11"/>
-        <v>5638.8196433246949</v>
+        <v>3352.8584808738856</v>
       </c>
       <c r="CQ13" s="4">
         <f t="shared" si="11"/>
-        <v>5751.5960361911884</v>
+        <v>3419.9156504913635</v>
       </c>
       <c r="CR13" s="4">
         <f t="shared" si="11"/>
-        <v>5866.627956915012</v>
+        <v>3488.3139635011908</v>
       </c>
       <c r="CS13" s="4">
         <f t="shared" si="11"/>
-        <v>5983.9605160533119</v>
+        <v>3558.0802427712147</v>
       </c>
       <c r="CT13" s="4">
         <f t="shared" si="11"/>
-        <v>6103.6397263743784</v>
+        <v>3629.2418476266389</v>
       </c>
       <c r="CU13" s="4">
         <f t="shared" si="11"/>
-        <v>6225.7125209018659</v>
+        <v>3701.8266845791718</v>
       </c>
       <c r="CV13" s="4">
         <f t="shared" si="11"/>
-        <v>6350.2267713199035</v>
+        <v>3775.8632182707552</v>
       </c>
       <c r="CW13" s="4">
         <f t="shared" si="11"/>
-        <v>6477.2313067463019</v>
+        <v>3851.3804826361702</v>
       </c>
       <c r="CX13" s="4">
         <f t="shared" si="11"/>
-        <v>6606.7759328812281</v>
+        <v>3928.4080922888938</v>
       </c>
       <c r="CY13" s="4">
         <f t="shared" si="11"/>
-        <v>6738.9114515388528</v>
+        <v>4006.9762541346718</v>
       </c>
       <c r="CZ13" s="4">
-        <f t="shared" ref="CZ13:DH13" si="12">CY13*(1+$AA$33)</f>
-        <v>6873.6896805696297</v>
+        <f t="shared" si="11"/>
+        <v>4087.1157792173653</v>
       </c>
       <c r="DA13" s="4">
-        <f t="shared" si="12"/>
-        <v>7011.1634741810221</v>
+        <f t="shared" si="11"/>
+        <v>4168.8580948017125</v>
       </c>
       <c r="DB13" s="4">
-        <f t="shared" si="12"/>
-        <v>7151.3867436646424</v>
+        <f t="shared" ref="DB13:DJ13" si="12">DA13*(1+$AC$33)</f>
+        <v>4252.235256697747</v>
       </c>
       <c r="DC13" s="4">
         <f t="shared" si="12"/>
-        <v>7294.4144785379358</v>
+        <v>4337.2799618317022</v>
       </c>
       <c r="DD13" s="4">
         <f t="shared" si="12"/>
-        <v>7440.3027681086951</v>
+        <v>4424.0255610683362</v>
       </c>
       <c r="DE13" s="4">
         <f t="shared" si="12"/>
-        <v>7589.1088234708695</v>
+        <v>4512.5060722897033</v>
       </c>
       <c r="DF13" s="4">
         <f t="shared" si="12"/>
-        <v>7740.8909999402867</v>
+        <v>4602.7561937354976</v>
       </c>
       <c r="DG13" s="4">
         <f t="shared" si="12"/>
-        <v>7895.7088199390928</v>
+        <v>4694.8113176102079</v>
       </c>
       <c r="DH13" s="4">
         <f t="shared" si="12"/>
-        <v>8053.6229963378746</v>
-      </c>
-    </row>
-    <row r="14" spans="1:112" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>4788.7075439624123</v>
+      </c>
+      <c r="DI13" s="4">
+        <f t="shared" si="12"/>
+        <v>4884.481694841661</v>
+      </c>
+      <c r="DJ13" s="4">
+        <f t="shared" si="12"/>
+        <v>4982.1713287384946</v>
+      </c>
+    </row>
+    <row r="14" spans="1:114" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>16</v>
       </c>
@@ -2521,28 +2618,31 @@
       <c r="V14" s="6">
         <v>55.517000000000003</v>
       </c>
-      <c r="AC14" s="25">
-        <f>(AC13-AB13)/AB13</f>
-        <v>0.32317364093065015</v>
-      </c>
-      <c r="AD14" s="25">
-        <f>(AD13-AC13)/AC13</f>
-        <v>0.25777725929382483</v>
+      <c r="W14" s="6">
+        <v>61.411999999999999</v>
       </c>
       <c r="AE14" s="25">
         <f>(AE13-AD13)/AD13</f>
-        <v>0.1687151309040319</v>
+        <v>0.32317364093065015</v>
       </c>
       <c r="AF14" s="25">
         <f>(AF13-AE13)/AE13</f>
+        <v>0.25777725929382483</v>
+      </c>
+      <c r="AG14" s="25">
+        <f>(AG13-AF13)/AF13</f>
+        <v>0.1687151309040319</v>
+      </c>
+      <c r="AH14" s="25">
+        <f>(AH13-AG13)/AG13</f>
         <v>-7.3148911916849316E-2</v>
       </c>
-      <c r="AG14" s="40">
-        <f>(AG13-AF13)/AF13</f>
-        <v>0.30000000000000004</v>
-      </c>
-    </row>
-    <row r="15" spans="1:112" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI14" s="40">
+        <f>(AI13-AH13)/AH13</f>
+        <v>0.19999999999999993</v>
+      </c>
+    </row>
+    <row r="15" spans="1:114" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -2555,7 +2655,7 @@
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
       <c r="J15" s="23">
-        <f t="shared" ref="J15:V15" si="13">J13-J14</f>
+        <f t="shared" ref="J15:W15" si="13">J13-J14</f>
         <v>20.613</v>
       </c>
       <c r="K15" s="23">
@@ -2606,349 +2706,353 @@
         <f t="shared" si="13"/>
         <v>48.341999999999992</v>
       </c>
-      <c r="AA15" s="6" t="s">
+      <c r="W15" s="23">
+        <f t="shared" si="13"/>
+        <v>50.988000000000007</v>
+      </c>
+      <c r="AC15" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="AB15" s="4">
+      <c r="AD15" s="4">
         <v>213.786</v>
       </c>
-      <c r="AC15" s="4">
+      <c r="AE15" s="4">
         <v>282.87599999999998</v>
       </c>
-      <c r="AD15" s="4">
+      <c r="AF15" s="4">
         <f>SUM(J12:M12)</f>
         <v>262.34699999999998</v>
       </c>
-      <c r="AE15" s="4">
+      <c r="AG15" s="4">
         <f>SUM(N12:Q12)</f>
         <v>276.714</v>
       </c>
-      <c r="AF15" s="4">
+      <c r="AH15" s="4">
         <f>SUM(R12:U12)</f>
         <v>349.98199999999997</v>
       </c>
-      <c r="AG15" s="41">
+      <c r="AI15" s="41">
         <f t="shared" si="10"/>
-        <v>454.97659999999996</v>
-      </c>
-      <c r="AH15" s="4">
-        <f t="shared" ref="AH15" si="14">AG15*(1+$AA$32)</f>
-        <v>591.46957999999995</v>
-      </c>
-      <c r="AI15" s="4">
-        <f t="shared" ref="AI15" si="15">AH15*(1+$AA$32)</f>
-        <v>768.91045399999996</v>
+        <v>419.97839999999997</v>
       </c>
       <c r="AJ15" s="4">
-        <f t="shared" ref="AJ15" si="16">AI15*(1+$AA$32)</f>
-        <v>999.5835902</v>
+        <f t="shared" ref="AJ15" si="14">AI15*(1+$AC$32)</f>
+        <v>503.97407999999996</v>
       </c>
       <c r="AK15" s="4">
-        <f t="shared" ref="AK15" si="17">AJ15*(1+$AA$32)</f>
-        <v>1299.4586672600001</v>
+        <f t="shared" ref="AK15" si="15">AJ15*(1+$AC$32)</f>
+        <v>604.76889599999993</v>
       </c>
       <c r="AL15" s="4">
-        <f t="shared" ref="AL15" si="18">AK15*(1+$AA$32)</f>
-        <v>1689.2962674380001</v>
+        <f t="shared" ref="AL15" si="16">AK15*(1+$AC$32)</f>
+        <v>725.72267519999991</v>
       </c>
       <c r="AM15" s="4">
-        <f>AL15*(1+$AA$33)</f>
-        <v>1723.0821927867601</v>
+        <f t="shared" ref="AM15" si="17">AL15*(1+$AC$32)</f>
+        <v>870.86721023999985</v>
       </c>
       <c r="AN15" s="4">
-        <f t="shared" ref="AN15:CY15" si="19">AM15*(1+$AA$33)</f>
-        <v>1757.5438366424953</v>
+        <f t="shared" ref="AN15" si="18">AM15*(1+$AC$32)</f>
+        <v>1045.0406522879998</v>
       </c>
       <c r="AO15" s="4">
-        <f t="shared" si="19"/>
-        <v>1792.6947133753451</v>
+        <f>AN15*(1+$AC$33)</f>
+        <v>1065.9414653337599</v>
       </c>
       <c r="AP15" s="4">
-        <f t="shared" si="19"/>
-        <v>1828.5486076428522</v>
+        <f t="shared" ref="AP15:DA15" si="19">AO15*(1+$AC$33)</f>
+        <v>1087.2602946404352</v>
       </c>
       <c r="AQ15" s="4">
         <f t="shared" si="19"/>
-        <v>1865.1195797957093</v>
+        <v>1109.005500533244</v>
       </c>
       <c r="AR15" s="4">
         <f t="shared" si="19"/>
-        <v>1902.4219713916236</v>
+        <v>1131.185610543909</v>
       </c>
       <c r="AS15" s="4">
         <f t="shared" si="19"/>
-        <v>1940.4704108194562</v>
+        <v>1153.8093227547872</v>
       </c>
       <c r="AT15" s="4">
         <f t="shared" si="19"/>
-        <v>1979.2798190358453</v>
+        <v>1176.8855092098829</v>
       </c>
       <c r="AU15" s="4">
         <f t="shared" si="19"/>
-        <v>2018.8654154165622</v>
+        <v>1200.4232193940807</v>
       </c>
       <c r="AV15" s="4">
         <f t="shared" si="19"/>
-        <v>2059.2427237248935</v>
+        <v>1224.4316837819622</v>
       </c>
       <c r="AW15" s="4">
         <f t="shared" si="19"/>
-        <v>2100.4275781993915</v>
+        <v>1248.9203174576014</v>
       </c>
       <c r="AX15" s="4">
         <f t="shared" si="19"/>
-        <v>2142.4361297633795</v>
+        <v>1273.8987238067534</v>
       </c>
       <c r="AY15" s="4">
         <f t="shared" si="19"/>
-        <v>2185.2848523586472</v>
+        <v>1299.3766982828886</v>
       </c>
       <c r="AZ15" s="4">
         <f t="shared" si="19"/>
-        <v>2228.9905494058203</v>
+        <v>1325.3642322485464</v>
       </c>
       <c r="BA15" s="4">
         <f t="shared" si="19"/>
-        <v>2273.5703603939369</v>
+        <v>1351.8715168935173</v>
       </c>
       <c r="BB15" s="4">
         <f t="shared" si="19"/>
-        <v>2319.0417676018155</v>
+        <v>1378.9089472313876</v>
       </c>
       <c r="BC15" s="4">
         <f t="shared" si="19"/>
-        <v>2365.4226029538518</v>
+        <v>1406.4871261760154</v>
       </c>
       <c r="BD15" s="4">
         <f t="shared" si="19"/>
-        <v>2412.7310550129287</v>
+        <v>1434.6168686995356</v>
       </c>
       <c r="BE15" s="4">
         <f t="shared" si="19"/>
-        <v>2460.9856761131873</v>
+        <v>1463.3092060735264</v>
       </c>
       <c r="BF15" s="4">
         <f t="shared" si="19"/>
-        <v>2510.205389635451</v>
+        <v>1492.575390194997</v>
       </c>
       <c r="BG15" s="4">
         <f t="shared" si="19"/>
-        <v>2560.4094974281602</v>
+        <v>1522.4268979988969</v>
       </c>
       <c r="BH15" s="4">
         <f t="shared" si="19"/>
-        <v>2611.6176873767236</v>
+        <v>1552.875435958875</v>
       </c>
       <c r="BI15" s="4">
         <f t="shared" si="19"/>
-        <v>2663.850041124258</v>
+        <v>1583.9329446780525</v>
       </c>
       <c r="BJ15" s="4">
         <f t="shared" si="19"/>
-        <v>2717.1270419467432</v>
+        <v>1615.6116035716136</v>
       </c>
       <c r="BK15" s="4">
         <f t="shared" si="19"/>
-        <v>2771.4695827856781</v>
+        <v>1647.923835643046</v>
       </c>
       <c r="BL15" s="4">
         <f t="shared" si="19"/>
-        <v>2826.8989744413916</v>
+        <v>1680.8823123559071</v>
       </c>
       <c r="BM15" s="4">
         <f t="shared" si="19"/>
-        <v>2883.4369539302193</v>
+        <v>1714.4999586030253</v>
       </c>
       <c r="BN15" s="4">
         <f t="shared" si="19"/>
-        <v>2941.1056930088239</v>
+        <v>1748.7899577750859</v>
       </c>
       <c r="BO15" s="4">
         <f t="shared" si="19"/>
-        <v>2999.9278068690005</v>
+        <v>1783.7657569305877</v>
       </c>
       <c r="BP15" s="4">
         <f t="shared" si="19"/>
-        <v>3059.9263630063806</v>
+        <v>1819.4410720691994</v>
       </c>
       <c r="BQ15" s="4">
         <f t="shared" si="19"/>
-        <v>3121.1248902665084</v>
+        <v>1855.8298935105834</v>
       </c>
       <c r="BR15" s="4">
         <f t="shared" si="19"/>
-        <v>3183.5473880718387</v>
+        <v>1892.9464913807951</v>
       </c>
       <c r="BS15" s="4">
         <f t="shared" si="19"/>
-        <v>3247.2183358332754</v>
+        <v>1930.805421208411</v>
       </c>
       <c r="BT15" s="4">
         <f t="shared" si="19"/>
-        <v>3312.1627025499411</v>
+        <v>1969.4215296325792</v>
       </c>
       <c r="BU15" s="4">
         <f t="shared" si="19"/>
-        <v>3378.40595660094</v>
+        <v>2008.809960225231</v>
       </c>
       <c r="BV15" s="4">
         <f t="shared" si="19"/>
-        <v>3445.9740757329587</v>
+        <v>2048.9861594297354</v>
       </c>
       <c r="BW15" s="4">
         <f t="shared" si="19"/>
-        <v>3514.893557247618</v>
+        <v>2089.9658826183299</v>
       </c>
       <c r="BX15" s="4">
         <f t="shared" si="19"/>
-        <v>3585.1914283925703</v>
+        <v>2131.7652002706964</v>
       </c>
       <c r="BY15" s="4">
         <f t="shared" si="19"/>
-        <v>3656.8952569604216</v>
+        <v>2174.4005042761105</v>
       </c>
       <c r="BZ15" s="4">
         <f t="shared" si="19"/>
-        <v>3730.0331620996303</v>
+        <v>2217.8885143616326</v>
       </c>
       <c r="CA15" s="4">
         <f t="shared" si="19"/>
-        <v>3804.6338253416229</v>
+        <v>2262.2462846488652</v>
       </c>
       <c r="CB15" s="4">
         <f t="shared" si="19"/>
-        <v>3880.7265018484554</v>
+        <v>2307.4912103418424</v>
       </c>
       <c r="CC15" s="4">
         <f t="shared" si="19"/>
-        <v>3958.3410318854244</v>
+        <v>2353.6410345486793</v>
       </c>
       <c r="CD15" s="4">
         <f t="shared" si="19"/>
-        <v>4037.5078525231329</v>
+        <v>2400.7138552396527</v>
       </c>
       <c r="CE15" s="4">
         <f t="shared" si="19"/>
-        <v>4118.2580095735957</v>
+        <v>2448.7281323444458</v>
       </c>
       <c r="CF15" s="4">
         <f t="shared" si="19"/>
-        <v>4200.6231697650674</v>
+        <v>2497.7026949913347</v>
       </c>
       <c r="CG15" s="4">
         <f t="shared" si="19"/>
-        <v>4284.6356331603683</v>
+        <v>2547.6567488911614</v>
       </c>
       <c r="CH15" s="4">
         <f t="shared" si="19"/>
-        <v>4370.3283458235755</v>
+        <v>2598.6098838689845</v>
       </c>
       <c r="CI15" s="4">
         <f t="shared" si="19"/>
-        <v>4457.7349127400475</v>
+        <v>2650.5820815463644</v>
       </c>
       <c r="CJ15" s="4">
         <f t="shared" si="19"/>
-        <v>4546.8896109948482</v>
+        <v>2703.5937231772918</v>
       </c>
       <c r="CK15" s="4">
         <f t="shared" si="19"/>
-        <v>4637.8274032147456</v>
+        <v>2757.6655976408379</v>
       </c>
       <c r="CL15" s="4">
         <f t="shared" si="19"/>
-        <v>4730.5839512790408</v>
+        <v>2812.8189095936546</v>
       </c>
       <c r="CM15" s="4">
         <f t="shared" si="19"/>
-        <v>4825.1956303046218</v>
+        <v>2869.0752877855275</v>
       </c>
       <c r="CN15" s="4">
         <f t="shared" si="19"/>
-        <v>4921.6995429107146</v>
+        <v>2926.4567935412383</v>
       </c>
       <c r="CO15" s="4">
         <f t="shared" si="19"/>
-        <v>5020.1335337689288</v>
+        <v>2984.9859294120633</v>
       </c>
       <c r="CP15" s="4">
         <f t="shared" si="19"/>
-        <v>5120.5362044443073</v>
+        <v>3044.6856480003048</v>
       </c>
       <c r="CQ15" s="4">
         <f t="shared" si="19"/>
-        <v>5222.9469285331934</v>
+        <v>3105.5793609603111</v>
       </c>
       <c r="CR15" s="4">
         <f t="shared" si="19"/>
-        <v>5327.4058671038574</v>
+        <v>3167.6909481795174</v>
       </c>
       <c r="CS15" s="4">
         <f t="shared" si="19"/>
-        <v>5433.953984445935</v>
+        <v>3231.0447671431079</v>
       </c>
       <c r="CT15" s="4">
         <f t="shared" si="19"/>
-        <v>5542.6330641348541</v>
+        <v>3295.6656624859702</v>
       </c>
       <c r="CU15" s="4">
         <f t="shared" si="19"/>
-        <v>5653.4857254175513</v>
+        <v>3361.5789757356897</v>
       </c>
       <c r="CV15" s="4">
         <f t="shared" si="19"/>
-        <v>5766.5554399259026</v>
+        <v>3428.8105552504035</v>
       </c>
       <c r="CW15" s="4">
         <f t="shared" si="19"/>
-        <v>5881.8865487244211</v>
+        <v>3497.3867663554115</v>
       </c>
       <c r="CX15" s="4">
         <f t="shared" si="19"/>
-        <v>5999.5242796989096</v>
+        <v>3567.3345016825197</v>
       </c>
       <c r="CY15" s="4">
         <f t="shared" si="19"/>
-        <v>6119.5147652928881</v>
+        <v>3638.6811917161699</v>
       </c>
       <c r="CZ15" s="4">
-        <f t="shared" ref="CZ15:DH15" si="20">CY15*(1+$AA$33)</f>
-        <v>6241.9050605987459</v>
+        <f t="shared" si="19"/>
+        <v>3711.4548155504935</v>
       </c>
       <c r="DA15" s="4">
-        <f t="shared" si="20"/>
-        <v>6366.7431618107212</v>
+        <f t="shared" si="19"/>
+        <v>3785.6839118615035</v>
       </c>
       <c r="DB15" s="4">
-        <f t="shared" si="20"/>
-        <v>6494.0780250469361</v>
+        <f t="shared" ref="DB15:DJ15" si="20">DA15*(1+$AC$33)</f>
+        <v>3861.3975900987334</v>
       </c>
       <c r="DC15" s="4">
         <f t="shared" si="20"/>
-        <v>6623.9595855478747</v>
+        <v>3938.625541900708</v>
       </c>
       <c r="DD15" s="4">
         <f t="shared" si="20"/>
-        <v>6756.4387772588325</v>
+        <v>4017.3980527387221</v>
       </c>
       <c r="DE15" s="4">
         <f t="shared" si="20"/>
-        <v>6891.5675528040092</v>
+        <v>4097.7460137934968</v>
       </c>
       <c r="DF15" s="4">
         <f t="shared" si="20"/>
-        <v>7029.3989038600894</v>
+        <v>4179.7009340693667</v>
       </c>
       <c r="DG15" s="4">
         <f t="shared" si="20"/>
-        <v>7169.9868819372914</v>
+        <v>4263.2949527507544</v>
       </c>
       <c r="DH15" s="4">
         <f t="shared" si="20"/>
-        <v>7313.3866195760374</v>
-      </c>
-    </row>
-    <row r="16" spans="1:112" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>4348.5608518057697</v>
+      </c>
+      <c r="DI15" s="4">
+        <f t="shared" si="20"/>
+        <v>4435.5320688418851</v>
+      </c>
+      <c r="DJ15" s="4">
+        <f t="shared" si="20"/>
+        <v>4524.242710218723</v>
+      </c>
+    </row>
+    <row r="16" spans="1:114" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>18</v>
       </c>
@@ -3006,17 +3110,20 @@
       <c r="V16" s="6">
         <v>19.766999999999999</v>
       </c>
-      <c r="AE16" s="25">
-        <f>(AE15-AD15)/AD15</f>
+      <c r="W16" s="6">
+        <v>20.934000000000001</v>
+      </c>
+      <c r="AG16" s="25">
+        <f>(AG15-AF15)/AF15</f>
         <v>5.4763347779848905E-2</v>
       </c>
-      <c r="AF16" s="25">
-        <f>(AF15-AE15)/AE15</f>
+      <c r="AH16" s="25">
+        <f>(AH15-AG15)/AG15</f>
         <v>0.26477879688053357</v>
       </c>
-      <c r="AG16" s="40"/>
-    </row>
-    <row r="17" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI16" s="40"/>
+    </row>
+    <row r="17" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>47</v>
       </c>
@@ -3071,9 +3178,12 @@
       <c r="V17" s="6">
         <v>11.782</v>
       </c>
-      <c r="AG17" s="42"/>
-    </row>
-    <row r="18" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="W17" s="6">
+        <v>12.263999999999999</v>
+      </c>
+      <c r="AI17" s="42"/>
+    </row>
+    <row r="18" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>48</v>
       </c>
@@ -3131,9 +3241,18 @@
       <c r="V18" s="6">
         <v>29.283999999999999</v>
       </c>
-      <c r="AG18" s="42"/>
-    </row>
-    <row r="19" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="W18" s="6">
+        <v>31.696999999999999</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>45877</v>
+      </c>
+      <c r="AD18" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="AI18" s="42"/>
+    </row>
+    <row r="19" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>65</v>
       </c>
@@ -3195,9 +3314,15 @@
         <f>3.259</f>
         <v>3.2589999999999999</v>
       </c>
-      <c r="AG19" s="42"/>
-    </row>
-    <row r="20" spans="1:33" s="6" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W19" s="6">
+        <v>3.3940000000000001</v>
+      </c>
+      <c r="AD19" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AI19" s="42"/>
+    </row>
+    <row r="20" spans="1:36" s="6" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
@@ -3210,7 +3335,7 @@
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
       <c r="J20" s="23">
-        <f t="shared" ref="J20:V20" si="21">SUM(J16:J19)</f>
+        <f t="shared" ref="J20:W20" si="21">SUM(J16:J19)</f>
         <v>33.208999999999996</v>
       </c>
       <c r="K20" s="23">
@@ -3261,9 +3386,13 @@
         <f t="shared" si="21"/>
         <v>64.091999999999999</v>
       </c>
-      <c r="AG20" s="42"/>
-    </row>
-    <row r="21" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="W20" s="23">
+        <f t="shared" si="21"/>
+        <v>68.289000000000001</v>
+      </c>
+      <c r="AI20" s="42"/>
+    </row>
+    <row r="21" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
@@ -3276,7 +3405,7 @@
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
       <c r="J21" s="23">
-        <f t="shared" ref="J21:V21" si="22">J15-J20</f>
+        <f t="shared" ref="J21:W21" si="22">J15-J20</f>
         <v>-12.595999999999997</v>
       </c>
       <c r="K21" s="23">
@@ -3327,12 +3456,16 @@
         <f t="shared" si="22"/>
         <v>-15.750000000000007</v>
       </c>
-      <c r="Z21" t="s">
+      <c r="W21" s="23">
+        <f t="shared" si="22"/>
+        <v>-17.300999999999995</v>
+      </c>
+      <c r="AB21" t="s">
         <v>67</v>
       </c>
-      <c r="AG21" s="42"/>
-    </row>
-    <row r="22" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI21" s="42"/>
+    </row>
+    <row r="22" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>21</v>
       </c>
@@ -3396,18 +3529,22 @@
         <f>-0.91-1.635-5.791</f>
         <v>-8.3360000000000003</v>
       </c>
-      <c r="Z22" s="6" t="s">
+      <c r="W22" s="6">
+        <f>-1.408+-1.381</f>
+        <v>-2.7889999999999997</v>
+      </c>
+      <c r="AB22" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="AA22" s="8" t="s">
+      <c r="AC22" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="AB22" s="6" t="s">
+      <c r="AD22" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="AG22" s="42"/>
-    </row>
-    <row r="23" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI22" s="42"/>
+    </row>
+    <row r="23" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>22</v>
       </c>
@@ -3420,7 +3557,7 @@
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
       <c r="J23" s="23">
-        <f t="shared" ref="J23:V23" si="23">J21+J22</f>
+        <f t="shared" ref="J23:W23" si="23">J21+J22</f>
         <v>-15.426999999999996</v>
       </c>
       <c r="K23" s="23">
@@ -3471,16 +3608,20 @@
         <f t="shared" si="23"/>
         <v>-24.086000000000006</v>
       </c>
-      <c r="Z23" s="6" t="s">
+      <c r="W23" s="23">
+        <f t="shared" si="23"/>
+        <v>-20.089999999999996</v>
+      </c>
+      <c r="AB23" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="AA23" s="45">
+      <c r="AC23" s="45">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="AB23" s="7"/>
-      <c r="AG23" s="42"/>
-    </row>
-    <row r="24" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD23" s="7"/>
+      <c r="AI23" s="42"/>
+    </row>
+    <row r="24" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>23</v>
       </c>
@@ -3542,16 +3683,20 @@
       <c r="V24" s="6">
         <v>-1.2809999999999999</v>
       </c>
-      <c r="Z24" s="6" t="s">
+      <c r="W24" s="6">
+        <f>-0.944</f>
+        <v>-0.94399999999999995</v>
+      </c>
+      <c r="AB24" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="AA24" s="1">
+      <c r="AC24" s="1">
         <v>1.76</v>
       </c>
-      <c r="AB24" s="7"/>
-      <c r="AG24" s="42"/>
-    </row>
-    <row r="25" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD24" s="7"/>
+      <c r="AI24" s="42"/>
+    </row>
+    <row r="25" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>24</v>
       </c>
@@ -3564,7 +3709,7 @@
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
       <c r="J25" s="23">
-        <f t="shared" ref="J25:V25" si="24">J23+J24</f>
+        <f t="shared" ref="J25:W25" si="24">J23+J24</f>
         <v>-15.436999999999996</v>
       </c>
       <c r="K25" s="23">
@@ -3615,18 +3760,22 @@
         <f t="shared" si="24"/>
         <v>-25.367000000000004</v>
       </c>
-      <c r="Z25" s="6" t="s">
+      <c r="W25" s="23">
+        <f t="shared" si="24"/>
+        <v>-21.033999999999995</v>
+      </c>
+      <c r="AB25" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="AA25" s="45">
+      <c r="AC25" s="45">
         <v>5.5E-2</v>
       </c>
-      <c r="AB25" s="7" t="s">
+      <c r="AD25" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="AG25" s="42"/>
-    </row>
-    <row r="26" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI25" s="42"/>
+    </row>
+    <row r="26" spans="1:36" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>25</v>
       </c>
@@ -3639,7 +3788,7 @@
       <c r="H26" s="9"/>
       <c r="I26" s="9"/>
       <c r="J26" s="23">
-        <f t="shared" ref="J26:V26" si="25">J25/J27</f>
+        <f t="shared" ref="J26:W26" si="25">J25/J27</f>
         <v>-0.57237671486837216</v>
       </c>
       <c r="K26" s="23">
@@ -3690,18 +3839,22 @@
         <f t="shared" si="25"/>
         <v>-0.63142828695176001</v>
       </c>
-      <c r="Z26" s="8" t="s">
+      <c r="W26" s="23">
+        <f t="shared" si="25"/>
+        <v>-0.51910167818361286</v>
+      </c>
+      <c r="AB26" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="AA26" s="45">
+      <c r="AC26" s="45">
         <v>0.02</v>
       </c>
-      <c r="AB26" s="9" t="s">
+      <c r="AD26" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="AG26" s="43"/>
-    </row>
-    <row r="27" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI26" s="43"/>
+    </row>
+    <row r="27" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
@@ -3754,33 +3907,36 @@
       <c r="V27" s="6">
         <v>40.173999999999999</v>
       </c>
-      <c r="Z27" s="6" t="s">
+      <c r="W27" s="6">
+        <v>40.520000000000003</v>
+      </c>
+      <c r="AB27" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="AA27" s="45">
+      <c r="AC27" s="45">
         <v>0.02</v>
       </c>
-      <c r="AB27" s="7" t="s">
+      <c r="AD27" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="AG27" s="42"/>
-    </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="Z28" s="37" t="s">
+      <c r="AI27" s="42"/>
+    </row>
+    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AB28" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="AA28" s="46">
-        <f>AA23+AA24*AA25+AA26+AA27</f>
+      <c r="AC28" s="46">
+        <f>AC23+AC24*AC25+AC26+AC27</f>
         <v>0.17879999999999999</v>
       </c>
-      <c r="AB28" s="1"/>
-    </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AD28" s="1"/>
+    </row>
+    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="37" t="s">
         <v>62</v>
       </c>
       <c r="N29" s="11">
-        <f t="shared" ref="N29:V30" si="26">+N12/J12-1</f>
+        <f t="shared" ref="N29:W30" si="26">+N12/J12-1</f>
         <v>0.16548278557591001</v>
       </c>
       <c r="O29" s="11">
@@ -3815,10 +3971,14 @@
         <f t="shared" si="26"/>
         <v>0.48215432477559128</v>
       </c>
-      <c r="AA29" s="1"/>
-      <c r="AB29" s="1"/>
-    </row>
-    <row r="30" spans="1:33" s="12" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="W29" s="11">
+        <f t="shared" si="26"/>
+        <v>0.43825975687779906</v>
+      </c>
+      <c r="AC29" s="1"/>
+      <c r="AD29" s="1"/>
+    </row>
+    <row r="30" spans="1:36" s="12" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>27</v>
       </c>
@@ -3870,9 +4030,13 @@
         <f t="shared" si="26"/>
         <v>-1.5526507862782757E-2</v>
       </c>
-      <c r="AG30" s="44"/>
-    </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="W30" s="11">
+        <f t="shared" si="26"/>
+        <v>0.43825975687779906</v>
+      </c>
+      <c r="AI30" s="44"/>
+    </row>
+    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>28</v>
       </c>
@@ -3909,7 +4073,7 @@
         <v>0.24821078114533499</v>
       </c>
       <c r="L31" s="13">
-        <f t="shared" ref="L31:V31" si="28">+L15/L13</f>
+        <f t="shared" ref="L31:W31" si="28">+L15/L13</f>
         <v>0.23077171839123842</v>
       </c>
       <c r="M31" s="13">
@@ -3952,22 +4116,32 @@
         <f t="shared" si="28"/>
         <v>0.46545797667992178</v>
       </c>
-    </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="Z32" s="14" t="s">
+      <c r="W31" s="13">
+        <f t="shared" si="28"/>
+        <v>0.45362989323843422</v>
+      </c>
+    </row>
+    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AB32" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="AA32" s="15">
-        <v>0.3</v>
-      </c>
-      <c r="AC32" s="14" t="s">
+      <c r="AC32" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="AE32" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="AD32" s="15">
+      <c r="AF32" s="15">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AH32" t="s">
+        <v>88</v>
+      </c>
+      <c r="AJ32" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="2:37" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -3980,21 +4154,28 @@
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
-      <c r="Z33" s="16" t="s">
+      <c r="AB33" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="AA33" s="17">
+      <c r="AC33" s="17">
         <v>0.02</v>
       </c>
-      <c r="AC33" s="16" t="s">
+      <c r="AE33" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="AD33" s="17">
-        <v>0.01</v>
-      </c>
-      <c r="AG33" s="42"/>
-    </row>
-    <row r="34" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AF33" s="17">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="16"/>
+      <c r="AI33" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="AJ33" s="51">
+        <v>5.8</v>
+      </c>
+      <c r="AK33" s="50"/>
+    </row>
+    <row r="34" spans="2:37" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
@@ -4007,21 +4188,28 @@
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
       <c r="M34" s="7"/>
-      <c r="Z34" s="16" t="s">
+      <c r="AB34" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="AA34" s="17">
+      <c r="AC34" s="17">
         <v>0.17</v>
       </c>
-      <c r="AC34" s="16" t="s">
+      <c r="AE34" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="AD34" s="17">
-        <v>0.17</v>
-      </c>
-      <c r="AG34" s="42"/>
-    </row>
-    <row r="35" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AF34" s="17">
+        <v>0.15</v>
+      </c>
+      <c r="AH34" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI34" s="49">
+        <v>1.08</v>
+      </c>
+      <c r="AJ34" s="50"/>
+      <c r="AK34" s="50"/>
+    </row>
+    <row r="35" spans="2:37" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
@@ -4034,23 +4222,30 @@
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
       <c r="M35" s="7"/>
-      <c r="Z35" s="16" t="s">
+      <c r="AB35" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="AA35" s="26">
-        <f>NPV(AA34,AB15:DH15)</f>
-        <v>4310.3538275688079</v>
-      </c>
-      <c r="AC35" s="16" t="s">
+      <c r="AC35" s="26">
+        <f>NPV(AC34,AD15:DJ15)</f>
+        <v>3171.492646761682</v>
+      </c>
+      <c r="AE35" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="AD35" s="26">
-        <f>NPV(AD34,AD12:DK12)</f>
-        <v>3517.6117155492348</v>
-      </c>
-      <c r="AG35" s="42"/>
-    </row>
-    <row r="36" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AF35" s="26">
+        <f>NPV(AF34,AF12:DM12)</f>
+        <v>4059.0747836699557</v>
+      </c>
+      <c r="AH35" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="AI35" s="49">
+        <v>4.24</v>
+      </c>
+      <c r="AJ35" s="50"/>
+      <c r="AK35" s="50"/>
+    </row>
+    <row r="36" spans="2:37" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
@@ -4072,23 +4267,30 @@
       <c r="S36" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="Z36" s="16" t="s">
+      <c r="AB36" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="AA36" s="19">
+      <c r="AC36" s="19">
         <f>V27</f>
         <v>40.173999999999999</v>
       </c>
-      <c r="AC36" s="16" t="s">
+      <c r="AE36" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="AD36" s="19">
-        <f>AA36</f>
+      <c r="AF36" s="19">
+        <f>AC36</f>
         <v>40.173999999999999</v>
       </c>
-      <c r="AG36" s="42"/>
-    </row>
-    <row r="37" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AH36" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI36" s="49">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="AJ36" s="50"/>
+      <c r="AK36" s="50"/>
+    </row>
+    <row r="37" spans="2:37" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
@@ -4101,23 +4303,30 @@
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
-      <c r="Z37" s="16" t="s">
+      <c r="AB37" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="AA37" s="20">
-        <f>AA35/AA36</f>
-        <v>107.29212494570638</v>
-      </c>
-      <c r="AC37" s="16" t="s">
+      <c r="AC37" s="20">
+        <f>AC35/AC36</f>
+        <v>78.943910159846723</v>
+      </c>
+      <c r="AE37" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="AD37" s="20">
-        <f>AD35/AD36</f>
-        <v>87.559409457590348</v>
-      </c>
-      <c r="AG37" s="42"/>
-    </row>
-    <row r="38" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AF37" s="20">
+        <f>AF35/AF36</f>
+        <v>101.0373570884143</v>
+      </c>
+      <c r="AH37" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AI37" s="49">
+        <v>10</v>
+      </c>
+      <c r="AJ37" s="50"/>
+      <c r="AK37" s="50"/>
+    </row>
+    <row r="38" spans="2:37" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
@@ -4130,23 +4339,31 @@
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
-      <c r="Z38" s="16" t="s">
+      <c r="AB38" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="AA38" s="15">
-        <f>(AA37-Main!L5)/Main!L5</f>
-        <v>0.62687073458235587</v>
-      </c>
-      <c r="AC38" s="16" t="s">
+      <c r="AC38" s="15">
+        <f>(AC37-Main!L5)/Main!L5</f>
+        <v>0.68936251144546823</v>
+      </c>
+      <c r="AE38" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="AD38" s="15">
-        <f>(AD37-Main!L5)/Main!L5</f>
-        <v>0.32766352475497112</v>
-      </c>
-      <c r="AG38" s="42"/>
-    </row>
-    <row r="39" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AF38" s="15">
+        <f>(AF37-Main!L5)/Main!L5</f>
+        <v>1.1621518743508303</v>
+      </c>
+      <c r="AH38" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI38" s="49">
+        <f>AVERAGE(AI34:AI37)</f>
+        <v>4.1150000000000002</v>
+      </c>
+      <c r="AJ38" s="50"/>
+      <c r="AK38" s="50"/>
+    </row>
+    <row r="39" spans="2:37" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
@@ -4159,23 +4376,26 @@
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
       <c r="M39" s="7"/>
-      <c r="Z39" s="16" t="s">
+      <c r="AB39" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="AA39" s="18">
-        <f>AA36*AA37</f>
-        <v>4310.3538275688079</v>
-      </c>
-      <c r="AC39" s="16" t="s">
+      <c r="AC39" s="18">
+        <f>AC36*AC37</f>
+        <v>3171.4926467616824</v>
+      </c>
+      <c r="AE39" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="AD39" s="18">
-        <f>AD36*AD37</f>
-        <v>3517.6117155492348</v>
-      </c>
-      <c r="AG39" s="42"/>
-    </row>
-    <row r="40" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AF39" s="18">
+        <f>AF36*AF37</f>
+        <v>4059.0747836699561</v>
+      </c>
+      <c r="AH39" s="16"/>
+      <c r="AI39" s="49"/>
+      <c r="AJ39" s="50"/>
+      <c r="AK39" s="50"/>
+    </row>
+    <row r="40" spans="2:37" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
@@ -4188,9 +4408,12 @@
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
       <c r="M40" s="7"/>
-      <c r="AG40" s="42"/>
-    </row>
-    <row r="41" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AH40" s="16"/>
+      <c r="AI40" s="49"/>
+      <c r="AJ40" s="50"/>
+      <c r="AK40" s="50"/>
+    </row>
+    <row r="41" spans="2:37" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
@@ -4203,14 +4426,17 @@
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
       <c r="M41" s="7"/>
-      <c r="AG41" s="42"/>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="Z42" s="47" t="s">
+      <c r="AH41" s="16"/>
+      <c r="AI41" s="49"/>
+      <c r="AJ41" s="50"/>
+      <c r="AK41" s="50"/>
+    </row>
+    <row r="42" spans="2:37" x14ac:dyDescent="0.25">
+      <c r="AB42" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="43" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:37" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
@@ -4223,12 +4449,12 @@
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
       <c r="M43" s="7"/>
-      <c r="Z43" s="6" t="s">
+      <c r="AB43" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="AG43" s="42"/>
-    </row>
-    <row r="44" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI43" s="42"/>
+    </row>
+    <row r="44" spans="2:37" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
@@ -4241,12 +4467,12 @@
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
       <c r="M44" s="7"/>
-      <c r="Z44" s="6" t="s">
+      <c r="AB44" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="AG44" s="42"/>
-    </row>
-    <row r="45" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI44" s="42"/>
+    </row>
+    <row r="45" spans="2:37" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
@@ -4259,9 +4485,9 @@
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
       <c r="M45" s="7"/>
-      <c r="AG45" s="42"/>
-    </row>
-    <row r="46" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI45" s="42"/>
+    </row>
+    <row r="46" spans="2:37" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
@@ -4274,9 +4500,9 @@
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
       <c r="M46" s="7"/>
-      <c r="AG46" s="42"/>
-    </row>
-    <row r="47" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI46" s="42"/>
+    </row>
+    <row r="47" spans="2:37" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
@@ -4289,9 +4515,9 @@
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
       <c r="M47" s="7"/>
-      <c r="AG47" s="42"/>
-    </row>
-    <row r="48" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI47" s="42"/>
+    </row>
+    <row r="48" spans="2:37" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
@@ -4304,9 +4530,9 @@
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
       <c r="M48" s="7"/>
-      <c r="AG48" s="42"/>
-    </row>
-    <row r="49" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI48" s="42"/>
+    </row>
+    <row r="49" spans="2:35" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
@@ -4319,9 +4545,9 @@
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
       <c r="M49" s="7"/>
-      <c r="AG49" s="42"/>
-    </row>
-    <row r="50" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI49" s="42"/>
+    </row>
+    <row r="50" spans="2:35" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
@@ -4334,9 +4560,9 @@
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
       <c r="M50" s="7"/>
-      <c r="AG50" s="42"/>
-    </row>
-    <row r="52" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI50" s="42"/>
+    </row>
+    <row r="52" spans="2:35" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
@@ -4349,9 +4575,9 @@
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
       <c r="M52" s="7"/>
-      <c r="AG52" s="42"/>
-    </row>
-    <row r="53" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI52" s="42"/>
+    </row>
+    <row r="53" spans="2:35" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
@@ -4364,9 +4590,9 @@
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
       <c r="M53" s="7"/>
-      <c r="AG53" s="42"/>
-    </row>
-    <row r="54" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI53" s="42"/>
+    </row>
+    <row r="54" spans="2:35" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
@@ -4379,9 +4605,9 @@
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
       <c r="M54" s="7"/>
-      <c r="AG54" s="42"/>
-    </row>
-    <row r="55" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI54" s="42"/>
+    </row>
+    <row r="55" spans="2:35" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
@@ -4394,9 +4620,9 @@
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
       <c r="M55" s="7"/>
-      <c r="AG55" s="42"/>
-    </row>
-    <row r="56" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI55" s="42"/>
+    </row>
+    <row r="56" spans="2:35" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
@@ -4409,9 +4635,9 @@
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
-      <c r="AG56" s="42"/>
-    </row>
-    <row r="57" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI56" s="42"/>
+    </row>
+    <row r="57" spans="2:35" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
@@ -4424,9 +4650,9 @@
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
       <c r="M57" s="7"/>
-      <c r="AG57" s="42"/>
-    </row>
-    <row r="58" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI57" s="42"/>
+    </row>
+    <row r="58" spans="2:35" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
@@ -4439,9 +4665,9 @@
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
       <c r="M58" s="7"/>
-      <c r="AG58" s="42"/>
-    </row>
-    <row r="59" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI58" s="42"/>
+    </row>
+    <row r="59" spans="2:35" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
@@ -4454,9 +4680,9 @@
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
       <c r="M59" s="7"/>
-      <c r="AG59" s="42"/>
-    </row>
-    <row r="60" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI59" s="42"/>
+    </row>
+    <row r="60" spans="2:35" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
@@ -4469,9 +4695,9 @@
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
       <c r="M60" s="7"/>
-      <c r="AG60" s="42"/>
-    </row>
-    <row r="61" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI60" s="42"/>
+    </row>
+    <row r="61" spans="2:35" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
@@ -4484,9 +4710,9 @@
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
       <c r="M61" s="7"/>
-      <c r="AG61" s="42"/>
-    </row>
-    <row r="62" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI61" s="42"/>
+    </row>
+    <row r="62" spans="2:35" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
@@ -4499,9 +4725,9 @@
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
       <c r="M62" s="7"/>
-      <c r="AG62" s="42"/>
-    </row>
-    <row r="63" spans="2:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI62" s="42"/>
+    </row>
+    <row r="63" spans="2:35" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B63" s="7"/>
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
@@ -4514,7 +4740,7 @@
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
       <c r="M63" s="7"/>
-      <c r="AG63" s="42"/>
+      <c r="AI63" s="42"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
